--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="Rc7f93158d90b4a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="Rb93687b09ba447cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H26"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,A5)</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(C8:C26,A5)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,D5)</x:f>
+        <x:f>COUNTIF(C8:C26,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C24,F5)</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIF(C8:C26,F5)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -640,319 +640,343 @@
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
-    <x:row r="13" ht="75" customHeight="1">
+    <x:row r="13" ht="109" customHeight="1">
       <x:c r="A13" s="7" t="str">
+        <x:v>CA-034.02</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>旧 Miyako 高举修正 UE 接入范围</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>旧袖部版本新增 Corrective_Shoulder_HighRaise_L/R，驱动依赖 Blender FK 四元数；该版本未做 FBX 导出或 UE 实机验证。9 月 30 日 White 已改用另一套新校服，尚无依据说明此旧分支仍要接入。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>确认旧服装分支是否仍属当前交付范围；若弃用可关闭此缺口，若继续使用则须核对 Morph Targets 和驱动，不能把它列为当前新校服损坏。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46294</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>旧服装说明的 UE 边界与最新 White 换装来源区别</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="7" t="str">
         <x:v>CA-001.07</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="str">
+      <x:c r="B14" s="7" t="str">
         <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="str">
+      <x:c r="C14" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
         <x:v>校园运行 25 秒、38 次采样中 30 人均使用新网格，移动且动画推进。聊天已最终交付，保存及效果图确认。</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="str">
+      <x:c r="E14" s="7" t="str">
         <x:v>本次有限时长运行不代替整理后全校功能回归。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="str">
+      <x:c r="G14" s="7" t="str">
         <x:v>94 帧交叠检查、25 秒运行及最终交付</x:v>
-      </x:c>
-      <x:c r="H13" s="16" t="str"/>
-    </x:row>
-    <x:row r="14" ht="92" customHeight="1">
-      <x:c r="A14" s="7" t="str">
-        <x:v>CA-006.05</x:v>
-      </x:c>
-      <x:c r="B14" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46293</x:v>
-      </x:c>
-      <x:c r="G14" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
     <x:row r="15" ht="92" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C15" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="75" customHeight="1">
+    <x:row r="16" ht="92" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-006.06</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
       </x:c>
       <x:c r="C16" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="75" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>CA-014.04</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
         <x:v>综合楼运行与逐级踏步验收记录</x:v>
-      </x:c>
-      <x:c r="H16" s="16" t="str"/>
-    </x:row>
-    <x:row r="17" ht="92" customHeight="1">
-      <x:c r="A17" s="7" t="str">
-        <x:v>CA-015.02</x:v>
-      </x:c>
-      <x:c r="B17" s="7" t="str">
-        <x:v>教学楼 A B 一至四层往返验收</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D17" s="7" t="str">
-        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
-      </x:c>
-      <x:c r="E17" s="7" t="str">
-        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G17" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
     <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>CA-016.02</x:v>
+        <x:v>CA-015.02</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+        <x:v>教学楼 A B 一至四层往返验收</x:v>
       </x:c>
       <x:c r="C18" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
       </x:c>
       <x:c r="F18" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str"/>
     </x:row>
-    <x:row r="19" ht="75" customHeight="1">
+    <x:row r="19" ht="92" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>CA-017.03</x:v>
+        <x:v>CA-016.02</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
       </x:c>
       <x:c r="C19" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="75" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
         <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
-      </x:c>
-      <x:c r="H19" s="16" t="str"/>
-    </x:row>
-    <x:row r="20" ht="92" customHeight="1">
-      <x:c r="A20" s="7" t="str">
-        <x:v>CA-019.03</x:v>
-      </x:c>
-      <x:c r="B20" s="7" t="str">
-        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
-      </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="str">
-        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
-      </x:c>
-      <x:c r="E20" s="7" t="str">
-        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46289</x:v>
-      </x:c>
-      <x:c r="G20" s="7" t="str">
-        <x:v>礼堂最终验证及完整重启复核</x:v>
       </x:c>
       <x:c r="H20" s="16" t="str"/>
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>CA-020.02</x:v>
+        <x:v>CA-019.03</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
+        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
       </x:c>
       <x:c r="C21" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
+        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
+        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
         <x:v>46289</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
+        <x:v>礼堂最终验证及完整重启复核</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="92" customHeight="1">
+      <x:c r="A22" s="7" t="str">
+        <x:v>CA-020.02</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H21" s="16" t="str"/>
-    </x:row>
-    <x:row r="22" ht="109" customHeight="1">
-      <x:c r="A22" s="7" t="str">
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="109" customHeight="1">
+      <x:c r="A23" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B22" s="7" t="str">
+      <x:c r="B23" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E23" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
+      <x:c r="F23" s="14" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="G22" s="7" t="str">
+      <x:c r="G23" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
-      </x:c>
-      <x:c r="H22" s="16" t="str"/>
-    </x:row>
-    <x:row r="23" ht="92" customHeight="1">
-      <x:c r="A23" s="7" t="str">
-        <x:v>CA-030.02</x:v>
-      </x:c>
-      <x:c r="B23" s="7" t="str">
-        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
-        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
-      </x:c>
-      <x:c r="E23" s="7" t="str">
-        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G23" s="7" t="str">
-        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
       <x:c r="A24" s="7" t="str">
+        <x:v>CA-030.02</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="92" customHeight="1">
+      <x:c r="A25" s="7" t="str">
         <x:v>CA-031.02</x:v>
       </x:c>
-      <x:c r="B24" s="7" t="str">
+      <x:c r="B25" s="7" t="str">
         <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
       </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
         <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="str">
+      <x:c r="E25" s="7" t="str">
         <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
+      <x:c r="F25" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G24" s="7" t="str">
+      <x:c r="G25" s="7" t="str">
         <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="str"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="1"/>
-      <x:c r="B25" s="1"/>
-      <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-      <x:c r="H25" s="1"/>
-    </x:row>
-    <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B26" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C26" s="21"/>
-      <x:c r="D26" s="21"/>
-      <x:c r="E26" s="21"/>
-      <x:c r="F26" s="21"/>
-      <x:c r="G26" s="21"/>
-      <x:c r="H26" s="21"/>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26" ht="92" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-033.02</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1"/>
@@ -964,11 +988,35 @@
       <x:c r="G27" s="1"/>
       <x:c r="H27" s="1"/>
     </x:row>
+    <x:row r="28" ht="34" customHeight="1">
+      <x:c r="A28" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B28" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C28" s="21"/>
+      <x:c r="D28" s="21"/>
+      <x:c r="E28" s="21"/>
+      <x:c r="F28" s="21"/>
+      <x:c r="G28" s="21"/>
+      <x:c r="H28" s="21"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="1"/>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B26:H26"/>
+    <x:mergeCell ref="B28:H28"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C24">
+  <x:conditionalFormatting sqref="C8:C26">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -980,13 +1028,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C24">
+    <x:dataValidation type="list" sqref="C8:C26">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5965cb327f9845e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef8acfec3bf49d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="Rb93687b09ba447cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R773d8e1bb6814caf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H33"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
+        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C26,A5)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF(C8:C33,A5)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C26,D5)</x:f>
+        <x:f>COUNTIF(C8:C33,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C26,F5)</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIF(C8:C33,F5)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -568,7 +568,7 @@
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
-    <x:row r="10" ht="75" customHeight="1">
+    <x:row r="10" ht="109" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>CA-010.02</x:v>
       </x:c>
@@ -579,16 +579,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>目录整理完成并通过静态引用与编辑器画面检查；尚未找到整理后覆盖第一人称出生、移动、各楼梯与入口的整体运行结果。</x:v>
+        <x:v>整理后已有 White 多次运行及 Shipping 诊断包进入 scene 的局部结果。Shipping 仅固定视点与短转向，未完成可重复行走路线；尚无第一人称出生、移动、跳跃、全部楼梯与入口的跨区域完整回归。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>按校园路线复查第一人称移动、跳跃、上下楼与建筑入口，关联当前主地图版本。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>Content 整理报告：未追加 PIE 回归</x:v>
+        <x:v>Content 整理验收范围、White 修复与 Shipping 路线限制</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
@@ -664,359 +664,527 @@
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
-    <x:row r="14" ht="75" customHeight="1">
+    <x:row r="14" ht="92" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>CA-001.07</x:v>
+        <x:v>CA-038.02</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>White 换装后 30 人运行与保存验收</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>scene 标准 Shipping 发布构建验收</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>校园运行 25 秒、38 次采样中 30 人均使用新网格，移动且动画推进。聊天已最终交付，保存及效果图确认。</x:v>
+        <x:v>独立副本的 Shipping 诊断包已进入 scene并采样，但标准完整 build/cook 流程失败。当前没有错误解决后的完整构建成功和启动回归结果。</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>本次有限时长运行不代替整理后全校功能回归。</x:v>
+        <x:v>需标准流程成功退出及同版本启动结果才能确认发布验收；诊断性能成绩 CA-037 保留，不等同发布成功。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>94 帧交叠检查、25 秒运行及最终交付</x:v>
+        <x:v>Shipping 报告第 2 节区分标准失败与诊断包成功</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
-    <x:row r="15" ht="92" customHeight="1">
+    <x:row r="15" ht="109" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>CA-006.05</x:v>
+        <x:v>CA-038.03</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>Shipping 实际显示帧率与渲染像素验收</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
+        <x:v>外部 CPU-only PresentMon 测得应用 Present 完成频率；GPU/display 完整追踪未产生有效 CSV。请求 1920×1080、100% ScreenPercentage，后缓冲实际尺寸未直接读取，截图尺寸不等于渲染像素数。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
+        <x:v>真实显示帧率和严格原生 1080p 尚无直接证据，需对应环境测量再判定；不把应用 FPS 当屏幕 FPS。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
+        <x:v>Shipping 报告第 1、3 节测量输入及显示链路限制</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="92" customHeight="1">
+    <x:row r="16" ht="75" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-040.10</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>综合楼新园路实际角色通行验收</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>已完成地面点采样和近景检查，但当前聊天及交付记录未提供角色沿新园路、后门台阶坡道实际行走的验证结果。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+        <x:v>确认是否已有角色实走记录；仅凭16处地面采样不能认定角色全路线通过。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>景观聊天与 validation 当前验收边界</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="75" customHeight="1">
+    <x:row r="17" ht="92" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-040.11</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>综合楼后方参考图严格一比一验收</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>主要布局已还原并保存；最终聊天明确树冠、花境轮廓和廊架细节仍有差异，尚未达到用户要求的严格一比一。单透视图无法确认不可见细节与绝对尺寸。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+        <x:v>需确认可见差异的后续处理或接受范围；现有交付不能作为严格一比一验收。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+        <x:v>景观最终结果与 completion fidelity_note</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
     <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>CA-015.02</x:v>
+        <x:v>CA-001.07</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>教学楼 A B 一至四层往返验收</x:v>
+        <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
       <x:c r="C18" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
+        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
+        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
       </x:c>
       <x:c r="F18" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
+        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str"/>
     </x:row>
     <x:row r="19" ht="92" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>CA-016.02</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C19" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
-    <x:row r="20" ht="75" customHeight="1">
+    <x:row r="20" ht="92" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>CA-017.03</x:v>
+        <x:v>CA-006.06</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
       </x:c>
       <x:c r="C20" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
       </x:c>
       <x:c r="H20" s="16" t="str"/>
     </x:row>
-    <x:row r="21" ht="92" customHeight="1">
+    <x:row r="21" ht="75" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>CA-019.03</x:v>
+        <x:v>CA-014.04</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
       </x:c>
       <x:c r="C21" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>46289</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>礼堂最终验证及完整重启复核</x:v>
+        <x:v>综合楼运行与逐级踏步验收记录</x:v>
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
       <x:c r="A22" s="7" t="str">
+        <x:v>CA-015.02</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>教学楼 A B 一至四层往返验收</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>教学楼运行及踏步验收记录</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="92" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-016.02</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="75" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="92" customHeight="1">
+      <x:c r="A25" s="7" t="str">
+        <x:v>CA-019.03</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>礼堂最终验证及完整重启复核</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26" ht="92" customHeight="1">
+      <x:c r="A26" s="7" t="str">
         <x:v>CA-020.02</x:v>
       </x:c>
-      <x:c r="B22" s="7" t="str">
+      <x:c r="B26" s="7" t="str">
         <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
         <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E26" s="7" t="str">
         <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
+      <x:c r="F26" s="14" t="n">
         <x:v>46289</x:v>
       </x:c>
-      <x:c r="G22" s="7" t="str">
+      <x:c r="G26" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H22" s="16" t="str"/>
-    </x:row>
-    <x:row r="23" ht="109" customHeight="1">
-      <x:c r="A23" s="7" t="str">
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="109" customHeight="1">
+      <x:c r="A27" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B23" s="7" t="str">
+      <x:c r="B27" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="str">
+      <x:c r="E27" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="n">
+      <x:c r="F27" s="14" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="G23" s="7" t="str">
+      <x:c r="G27" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
       </x:c>
-      <x:c r="H23" s="16" t="str"/>
-    </x:row>
-    <x:row r="24" ht="92" customHeight="1">
-      <x:c r="A24" s="7" t="str">
+      <x:c r="H27" s="16" t="str"/>
+    </x:row>
+    <x:row r="28" ht="92" customHeight="1">
+      <x:c r="A28" s="7" t="str">
         <x:v>CA-030.02</x:v>
       </x:c>
-      <x:c r="B24" s="7" t="str">
+      <x:c r="B28" s="7" t="str">
         <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
       </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
         <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="str">
+      <x:c r="E28" s="7" t="str">
         <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
+      <x:c r="F28" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="G24" s="7" t="str">
+      <x:c r="G28" s="7" t="str">
         <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="str"/>
-    </x:row>
-    <x:row r="25" ht="92" customHeight="1">
-      <x:c r="A25" s="7" t="str">
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="92" customHeight="1">
+      <x:c r="A29" s="7" t="str">
         <x:v>CA-031.02</x:v>
       </x:c>
-      <x:c r="B25" s="7" t="str">
+      <x:c r="B29" s="7" t="str">
         <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D25" s="7" t="str">
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
         <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="str">
+      <x:c r="E29" s="7" t="str">
         <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="n">
+      <x:c r="F29" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G25" s="7" t="str">
+      <x:c r="G29" s="7" t="str">
         <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
       </x:c>
-      <x:c r="H25" s="16" t="str"/>
-    </x:row>
-    <x:row r="26" ht="92" customHeight="1">
-      <x:c r="A26" s="7" t="str">
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="92" customHeight="1">
+      <x:c r="A30" s="7" t="str">
         <x:v>CA-033.02</x:v>
       </x:c>
-      <x:c r="B26" s="7" t="str">
+      <x:c r="B30" s="7" t="str">
         <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
       </x:c>
-      <x:c r="C26" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D26" s="7" t="str">
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
         <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="str">
+      <x:c r="E30" s="7" t="str">
         <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="n">
+      <x:c r="F30" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="G26" s="7" t="str">
+      <x:c r="G30" s="7" t="str">
         <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
       </x:c>
-      <x:c r="H26" s="16" t="str"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="1"/>
-      <x:c r="B27" s="1"/>
-      <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-      <x:c r="H27" s="1"/>
-    </x:row>
-    <x:row r="28" ht="34" customHeight="1">
-      <x:c r="A28" s="3" t="str">
+      <x:c r="H30" s="16" t="str"/>
+    </x:row>
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="7" t="str">
+        <x:v>CA-035.02</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>White 打开关卡与退出运行复发验收</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>map_opened 与 end_pie 均实际触发 refreshed：count=matched=30、skipped=0、positions_preserved=true；聊天最终确认重新打开及停止运行后正常站立。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>本次覆盖保存、打开关卡与退出运行复发条件；未来初始化逻辑变化后按该范围回归。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>map_hook_verified、end_pie_verified 及最终截图交付</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>CA-040.09</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>综合楼后方16处地面碰撞采样</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>validation traces 16/16 与最终交付</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="75" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>CA-041.03</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>scene远景设置保存与前景保护验收</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>verification 设置保存与前景、源资产校验</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B28" s="21" t="str">
+      <x:c r="B35" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C28" s="21"/>
-      <x:c r="D28" s="21"/>
-      <x:c r="E28" s="21"/>
-      <x:c r="F28" s="21"/>
-      <x:c r="G28" s="21"/>
-      <x:c r="H28" s="21"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="1"/>
-      <x:c r="B29" s="1"/>
-      <x:c r="C29" s="1"/>
-      <x:c r="D29" s="1"/>
-      <x:c r="E29" s="1"/>
-      <x:c r="F29" s="1"/>
-      <x:c r="G29" s="1"/>
-      <x:c r="H29" s="1"/>
+      <x:c r="C35" s="21"/>
+      <x:c r="D35" s="21"/>
+      <x:c r="E35" s="21"/>
+      <x:c r="F35" s="21"/>
+      <x:c r="G35" s="21"/>
+      <x:c r="H35" s="21"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B28:H28"/>
+    <x:mergeCell ref="B35:H35"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C26">
+  <x:conditionalFormatting sqref="C8:C33">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1028,13 +1196,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C26">
+    <x:dataValidation type="list" sqref="C8:C33">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef8acfec3bf49d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb585e2ce456642b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R773d8e1bb6814caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R86696633891b488a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H46"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,A5)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTIF(C8:C46,A5)</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,D5)</x:f>
+        <x:f>COUNTIF(C8:C46,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,F5)</x:f>
+        <x:f>COUNTIF(C8:C46,F5)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -544,7 +544,7 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="75" customHeight="1">
+    <x:row r="9" ht="109" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-010</x:v>
       </x:c>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>整理报告中的 PIE 状态为 not_run；9 月 30 日 White 局部运行验证不能覆盖迁移后的教学楼、教师楼和综合楼全部门交互。</x:v>
+        <x:v>资产整理后的原生门迁移保存重开通过，185门控制器与963挂接零件保留；四类门32项E/Y、联动、距离和动作测试通过，White教室自动开门亦通过。但未找到185门逐门实走验收，最新玩家为观察入口。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>在当前主地图验证 E 键、最近门、双门同步和开关阻挡，并记录整理后的结果。</x:v>
+        <x:v>按所需全校门验收范围核对未覆盖实例及观察入口；四类抽样通过不能等同全校逐门通过。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>整理验收缺口及后续角色局部验证</x:v>
+        <x:v>原生门32项回归与最新White门路线</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -579,16 +579,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>整理后已有 White 多次运行及 Shipping 诊断包进入 scene 的局部结果。Shipping 仅固定视点与短转向，未完成可重复行走路线；尚无第一人称出生、移动、跳跃、全部楼梯与入口的跨区域完整回归。</x:v>
+        <x:v>后续已有第一/第三人称输入和跳跃验证、食堂两侧真实往返、White12条跨建筑楼层路线与32次随机选点。当前scene已变为单White观察模式；没有同版本第一人称出生到全校楼梯入口的完整连续回归。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>按校园路线复查第一人称移动、跳跃、上下楼与建筑入口，关联当前主地图版本。</x:v>
+        <x:v>确认当前交付所需运行回归范围，以最新玩家入口和对应版本验收；不得沿用旧90人或发布包结果判定当前全场通过。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
-        <x:v>46297</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>Content 整理验收范围、White 修复与 Shipping 路线限制</x:v>
+        <x:v>原生人物、食堂路线与最新校园实走边界</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
@@ -664,99 +664,99 @@
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
-    <x:row r="14" ht="92" customHeight="1">
+    <x:row r="14" ht="109" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>CA-038.02</x:v>
+        <x:v>CA-038.03</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>scene 标准 Shipping 发布构建验收</x:v>
+        <x:v>Shipping 实际显示帧率与渲染像素验收</x:v>
       </x:c>
       <x:c r="C14" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>独立副本的 Shipping 诊断包已进入 scene并采样，但标准完整 build/cook 流程失败。当前没有错误解决后的完整构建成功和启动回归结果。</x:v>
+        <x:v>外部 CPU-only PresentMon 测得应用 Present 完成频率；GPU/display 完整追踪未产生有效 CSV。请求 1920×1080、100% ScreenPercentage，后缓冲实际尺寸未直接读取，截图尺寸不等于渲染像素数。</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>需标准流程成功退出及同版本启动结果才能确认发布验收；诊断性能成绩 CA-037 保留，不等同发布成功。</x:v>
+        <x:v>真实显示帧率和严格原生 1080p 尚无直接证据，需对应环境测量再判定；不把应用 FPS 当屏幕 FPS。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="n">
         <x:v>46297</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>Shipping 报告第 2 节区分标准失败与诊断包成功</x:v>
+        <x:v>Shipping 报告第 1、3 节测量输入及显示链路限制</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
-    <x:row r="15" ht="109" customHeight="1">
+    <x:row r="15" ht="75" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>CA-038.03</x:v>
+        <x:v>CA-040.10</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>Shipping 实际显示帧率与渲染像素验收</x:v>
+        <x:v>综合楼新园路实际角色通行验收</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>外部 CPU-only PresentMon 测得应用 Present 完成频率；GPU/display 完整追踪未产生有效 CSV。请求 1920×1080、100% ScreenPercentage，后缓冲实际尺寸未直接读取，截图尺寸不等于渲染像素数。</x:v>
+        <x:v>已完成地面点采样和近景检查，但当前聊天及交付记录未提供角色沿新园路、后门台阶坡道实际行走的验证结果。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>真实显示帧率和严格原生 1080p 尚无直接证据，需对应环境测量再判定；不把应用 FPS 当屏幕 FPS。</x:v>
+        <x:v>确认是否已有角色实走记录；仅凭16处地面采样不能认定角色全路线通过。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>46297</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>Shipping 报告第 1、3 节测量输入及显示链路限制</x:v>
+        <x:v>景观聊天与 validation 当前验收边界</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="75" customHeight="1">
+    <x:row r="16" ht="92" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>CA-040.10</x:v>
+        <x:v>CA-040.11</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>综合楼新园路实际角色通行验收</x:v>
+        <x:v>综合楼后方参考图严格一比一验收</x:v>
       </x:c>
       <x:c r="C16" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>已完成地面点采样和近景检查，但当前聊天及交付记录未提供角色沿新园路、后门台阶坡道实际行走的验证结果。</x:v>
+        <x:v>主要布局已还原并保存；最终聊天明确树冠、花境轮廓和廊架细节仍有差异，尚未达到用户要求的严格一比一。单透视图无法确认不可见细节与绝对尺寸。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>确认是否已有角色实走记录；仅凭16处地面采样不能认定角色全路线通过。</x:v>
+        <x:v>需确认可见差异的后续处理或接受范围；现有交付不能作为严格一比一验收。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>景观聊天与 validation 当前验收边界</x:v>
+        <x:v>景观最终结果与 completion fidelity_note</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
     <x:row r="17" ht="92" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>CA-040.11</x:v>
+        <x:v>CA-045.05</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>综合楼后方参考图严格一比一验收</x:v>
+        <x:v>当前观察摄像机手柄与门交互适用范围</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>主要布局已还原并保存；最终聊天明确树冠、花境轮廓和廊架细节仍有差异，尚未达到用户要求的严格一比一。单透视图无法确认不可见细节与绝对尺寸。</x:v>
+        <x:v>手柄和Y门交互验收对应10月3日人物控制器。10月4日scene已改为SpectatorPawn，现有验证只覆盖WASD、鼠标和观察移动，说明中E用于升降，未提供同版本手柄/Y门交互验证。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>需确认可见差异的后续处理或接受范围；现有交付不能作为严格一比一验收。</x:v>
+        <x:v>确认当前交付是否需要观察摄像机保持原手柄与门交互体验；据实际映射和测试判断，不能沿用旧人物结果。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>景观最终结果与 completion fidelity_note</x:v>
+        <x:v>观察模式说明与旧手柄验收版本差异</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
@@ -1098,93 +1098,405 @@
       </x:c>
       <x:c r="H31" s="16" t="str"/>
     </x:row>
-    <x:row r="32" ht="75" customHeight="1">
+    <x:row r="32" ht="109" customHeight="1">
       <x:c r="A32" s="7" t="str">
-        <x:v>CA-040.09</x:v>
+        <x:v>CA-038.02</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>综合楼后方16处地面碰撞采样</x:v>
+        <x:v>scene 标准 Shipping 发布构建验收</x:v>
       </x:c>
       <x:c r="C32" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D32" s="7" t="str">
-        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
+        <x:v>Win64 Shipping构建副本10月3日完整build/cook/stage/package成功退出0，非skipbuild/skipcook。新版CPP_InvertY包含C++与垂直反转，D3D12启动响应及正常退出检查passed，ZIP完整性通过，用户随后明确验证通过。</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
+        <x:v>完成范围为10月3日发布副本；原工程规则CA-038和后续源版本发布同步CA-046.02仍独立追踪。</x:v>
       </x:c>
       <x:c r="F32" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
-        <x:v>validation traces 16/16 与最终交付</x:v>
+        <x:v>Shipping成功构建、运行检查与用户直接验收</x:v>
       </x:c>
       <x:c r="H32" s="16" t="str"/>
     </x:row>
     <x:row r="33" ht="75" customHeight="1">
       <x:c r="A33" s="7" t="str">
-        <x:v>CA-041.03</x:v>
+        <x:v>CA-040.09</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v>scene远景设置保存与前景保护验收</x:v>
+        <x:v>综合楼后方16处地面碰撞采样</x:v>
       </x:c>
       <x:c r="C33" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D33" s="7" t="str">
-        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
+        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
       </x:c>
       <x:c r="E33" s="7" t="str">
-        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
+        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G33" s="7" t="str">
+        <x:v>validation traces 16/16 与最终交付</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34" ht="75" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>CA-041.03</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>scene远景设置保存与前景保护验收</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
         <x:v>verification 设置保存与前景、源资产校验</x:v>
       </x:c>
-      <x:c r="H33" s="16" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-    </x:row>
-    <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="3" t="str">
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="92" customHeight="1">
+      <x:c r="A35" s="7" t="str">
+        <x:v>CA-043.05</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="str">
+        <x:v>校园风动保存与实例合批完整性</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
+        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>风动保存回读与合批检查</x:v>
+      </x:c>
+      <x:c r="H35" s="16" t="str"/>
+    </x:row>
+    <x:row r="36" ht="75" customHeight="1">
+      <x:c r="A36" s="7" t="str">
+        <x:v>CA-044.03</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="str">
+        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D36" s="7" t="str">
+        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="str">
+        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="str">
+        <x:v>verification_report与最终保存交付</x:v>
+      </x:c>
+      <x:c r="H36" s="16" t="str"/>
+    </x:row>
+    <x:row r="37" ht="92" customHeight="1">
+      <x:c r="A37" s="7" t="str">
+        <x:v>CA-045.04</x:v>
+      </x:c>
+      <x:c r="B37" s="7" t="str">
+        <x:v>第一第三人称手柄模拟输入验收</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="str">
+        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="str">
+        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>模拟输入记录与用户新版验收</x:v>
+      </x:c>
+      <x:c r="H37" s="16" t="str"/>
+    </x:row>
+    <x:row r="38" ht="92" customHeight="1">
+      <x:c r="A38" s="7" t="str">
+        <x:v>CA-047.03</x:v>
+      </x:c>
+      <x:c r="B38" s="7" t="str">
+        <x:v>食堂两侧一至二层真实往返验收</x:v>
+      </x:c>
+      <x:c r="C38" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="str">
+        <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="str">
+        <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>playtest_final与White校园路线</x:v>
+      </x:c>
+      <x:c r="H38" s="16" t="str"/>
+    </x:row>
+    <x:row r="39" ht="75" customHeight="1">
+      <x:c r="A39" s="7" t="str">
+        <x:v>CA-048.02</x:v>
+      </x:c>
+      <x:c r="B39" s="7" t="str">
+        <x:v>行政楼植被清理重载与保留位置验收</x:v>
+      </x:c>
+      <x:c r="C39" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D39" s="7" t="str">
+        <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="str">
+        <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G39" s="7" t="str">
+        <x:v>reload_verification与重载效果</x:v>
+      </x:c>
+      <x:c r="H39" s="16" t="str"/>
+    </x:row>
+    <x:row r="40" ht="75" customHeight="1">
+      <x:c r="A40" s="7" t="str">
+        <x:v>CA-052.06</x:v>
+      </x:c>
+      <x:c r="B40" s="7" t="str">
+        <x:v>White十九组高度与蒙皮接触验收</x:v>
+      </x:c>
+      <x:c r="C40" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="str">
+        <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="str">
+        <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>qa_final_summary高度与接触结果</x:v>
+      </x:c>
+      <x:c r="H40" s="16" t="str"/>
+    </x:row>
+    <x:row r="41" ht="75" customHeight="1">
+      <x:c r="A41" s="7" t="str">
+        <x:v>CA-052.07</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="str">
+        <x:v>White自动休息冷却与中断恢复验收</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="str">
+        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="str">
+        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>qa_final_summary行为结果</x:v>
+      </x:c>
+      <x:c r="H41" s="16" t="str"/>
+    </x:row>
+    <x:row r="42" ht="75" customHeight="1">
+      <x:c r="A42" s="7" t="str">
+        <x:v>CA-052.08</x:v>
+      </x:c>
+      <x:c r="B42" s="7" t="str">
+        <x:v>White不安全休息表面拒绝验收</x:v>
+      </x:c>
+      <x:c r="C42" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="str">
+        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="str">
+        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>表面安全测试与限制</x:v>
+      </x:c>
+      <x:c r="H42" s="16" t="str"/>
+    </x:row>
+    <x:row r="43" ht="92" customHeight="1">
+      <x:c r="A43" s="7" t="str">
+        <x:v>CA-053.06</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="str">
+        <x:v>White完整体力循环与座位异常验收</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="str">
+        <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="str">
+        <x:v>临时测试角色已清理，后续唯一White续行另见CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>qa_stamina_result与最终交付</x:v>
+      </x:c>
+      <x:c r="H43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44" ht="92" customHeight="1">
+      <x:c r="A44" s="7" t="str">
+        <x:v>CA-053.09</x:v>
+      </x:c>
+      <x:c r="B44" s="7" t="str">
+        <x:v>唯一White十二条跨校园实走验收</x:v>
+      </x:c>
+      <x:c r="C44" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="str">
+        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="str">
+        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
+        <x:v>suite_result与final_result</x:v>
+      </x:c>
+      <x:c r="H44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="75" customHeight="1">
+      <x:c r="A45" s="7" t="str">
+        <x:v>CA-053.10</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="str">
+        <x:v>White全校园随机选点覆盖抽样</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="str">
+        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="str">
+        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>final_result随机覆盖与解释</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="92" customHeight="1">
+      <x:c r="A46" s="7" t="str">
+        <x:v>CA-054.02</x:v>
+      </x:c>
+      <x:c r="B46" s="7" t="str">
+        <x:v>唯一White与观察入口运行验收</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="str">
+        <x:v>移除89名后保存，正常PIE确认仅1个White、SpectatorPawn被玩家控制且无网格，观察移动/转向和White行走/体力消耗通过，108座椅保留。</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="str">
+        <x:v>当前人物数量见CA-002，不能将旧90人测试当当前人数。</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>WhiteSingle final_result与play_result</x:v>
+      </x:c>
+      <x:c r="H46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1"/>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1"/>
+      <x:c r="F47" s="1"/>
+      <x:c r="G47" s="1"/>
+      <x:c r="H47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="34" customHeight="1">
+      <x:c r="A48" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B35" s="21" t="str">
+      <x:c r="B48" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C35" s="21"/>
-      <x:c r="D35" s="21"/>
-      <x:c r="E35" s="21"/>
-      <x:c r="F35" s="21"/>
-      <x:c r="G35" s="21"/>
-      <x:c r="H35" s="21"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="1"/>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
+      <x:c r="C48" s="21"/>
+      <x:c r="D48" s="21"/>
+      <x:c r="E48" s="21"/>
+      <x:c r="F48" s="21"/>
+      <x:c r="G48" s="21"/>
+      <x:c r="H48" s="21"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B35:H35"/>
+    <x:mergeCell ref="B48:H48"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C33">
+  <x:conditionalFormatting sqref="C8:C46">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1196,13 +1508,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C33">
+    <x:dataValidation type="list" sqref="C8:C46">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb585e2ce456642b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0755ece13e184678"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R86696633891b488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R8b56f950ee36424b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H60"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C46,A5)</x:f>
-        <x:v>29</x:v>
+        <x:f>COUNTIF(C8:C60,A5)</x:f>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C46,D5)</x:f>
+        <x:f>COUNTIF(C8:C60,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C46,F5)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF(C8:C60,F5)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>资产整理后的原生门迁移保存重开通过，185门控制器与963挂接零件保留；四类门32项E/Y、联动、距离和动作测试通过，White教室自动开门亦通过。但未找到185门逐门实走验收，最新玩家为观察入口。</x:v>
+        <x:v>旧185控制器保存重开与四类门32项检查、White自动开门保留。高三楼新增120门扇/109交互组，328项运行及保存回读通过，旧185门未变。当前玩家已恢复第一人称，仍缺全校所有门同版本连续实走覆盖。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>按所需全校门验收范围核对未覆盖实例及观察入口；四类抽样通过不能等同全校逐门通过。</x:v>
+        <x:v>按所需全校范围核对未覆盖实例；高三门开关验收与29个厕位门洞不可通行分别见CA-056系列。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>原生门32项回归与最新White门路线</x:v>
+        <x:v>高三门新增验收与第一人称恢复</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -579,16 +579,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>后续已有第一/第三人称输入和跳跃验证、食堂两侧真实往返、White12条跨建筑楼层路线与32次随机选点。当前scene已变为单White观察模式；没有同版本第一人称出生到全校楼梯入口的完整连续回归。</x:v>
+        <x:v>资产整理后已有食堂两侧往返、White12条路线和32随机目标。10月4日默认第一人称恢复后的15项出生、碰撞移动及跳跃验收通过；仍没有同版本出生到全校楼梯入口的完整连续回归。</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>确认当前交付所需运行回归范围，以最新玩家入口和对应版本验收；不得沿用旧90人或发布包结果判定当前全场通过。</x:v>
+        <x:v>按当前第一人称交付版本与所需路线判断全场回归；局部运行通过不能代替所有区域覆盖。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>原生人物、食堂路线与最新校园实走边界</x:v>
+        <x:v>新增第一人称局部回归与历史跨楼路线</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
@@ -736,767 +736,1103 @@
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="92" customHeight="1">
+    <x:row r="17" ht="109" customHeight="1">
       <x:c r="A17" s="7" t="str">
         <x:v>CA-045.05</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>当前观察摄像机手柄与门交互适用范围</x:v>
+        <x:v>当前第一人称手柄与门交互回归范围</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>手柄和Y门交互验收对应10月3日人物控制器。10月4日scene已改为SpectatorPawn，现有验证只覆盖WASD、鼠标和观察移动，说明中E用于升降，未提供同版本手柄/Y门交互验证。</x:v>
+        <x:v>10月3日人物输入与E/Y模拟测试及用户新版确认保留。当前已从观察模式恢复第一人称；最新15项检查明确未测实体键盘、鼠标和手柄，也未测鼠标映射，不能将旧范围疑问直接视为当前输入故障。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>确认当前交付是否需要观察摄像机保持原手柄与门交互体验；据实际映射和测试判断，不能沿用旧人物结果。</x:v>
+        <x:v>确认当前交付所需手柄回归范围；缺同版本实体手柄/Y门交互证据，不再追问已替代的观察摄像机映射。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>观察模式说明与旧手柄验收版本差异</x:v>
+        <x:v>第一人称恢复及输入验证明确边界</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
     <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>CA-001.07</x:v>
+        <x:v>CA-063.06</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>White 换装后 30 人运行与保存验收</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>参考夜景水面碎波与树冠光感接受范围</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
+        <x:v>最新夜景最终结果明确：主要氛围完成，但水面碎波、树冠光感与参考仍有细节差异。后续白天修订要求保持夜景，不构成这些差异已解决的证据。</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
+        <x:v>确认是否接受当前细节差异，或决定后续对齐范围。</x:v>
       </x:c>
       <x:c r="F18" s="14" t="n">
-        <x:v>46296</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
+        <x:v>夜景最终聊天明确限制</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str"/>
     </x:row>
     <x:row r="19" ht="92" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>CA-006.05</x:v>
+        <x:v>CA-065.04</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
-      </x:c>
-      <x:c r="C19" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>十月五日脚本成品实际运行验收</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
+        <x:v>00:39脚本构建记录succeeded证明构建和文件检查通过；未找到此批成品的启动画面、响应、退出或玩法验收。10月4日FirstPerson包运行通过属于上一批。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
+        <x:v>确认是否已有此批实际运行验收；不启动游戏替代追踪。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
+        <x:v>脚本build-info与明确运行验收边界</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
     <x:row r="20" ht="92" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-001.07</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+        <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
       <x:c r="C20" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
       </x:c>
       <x:c r="H20" s="16" t="str"/>
     </x:row>
-    <x:row r="21" ht="75" customHeight="1">
+    <x:row r="21" ht="92" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C21" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
       <x:c r="A22" s="7" t="str">
+        <x:v>CA-006.06</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="75" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-014.04</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="92" customHeight="1">
+      <x:c r="A24" s="7" t="str">
         <x:v>CA-015.02</x:v>
       </x:c>
-      <x:c r="B22" s="7" t="str">
+      <x:c r="B24" s="7" t="str">
         <x:v>教学楼 A B 一至四层往返验收</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
         <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E24" s="7" t="str">
         <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G22" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
-      </x:c>
-      <x:c r="H22" s="16" t="str"/>
-    </x:row>
-    <x:row r="23" ht="92" customHeight="1">
-      <x:c r="A23" s="7" t="str">
-        <x:v>CA-016.02</x:v>
-      </x:c>
-      <x:c r="B23" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
-      </x:c>
-      <x:c r="E23" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G23" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
-      </x:c>
-      <x:c r="H23" s="16" t="str"/>
-    </x:row>
-    <x:row r="24" ht="75" customHeight="1">
-      <x:c r="A24" s="7" t="str">
-        <x:v>CA-017.03</x:v>
-      </x:c>
-      <x:c r="B24" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
-      </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
-      </x:c>
-      <x:c r="E24" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
       <x:c r="A25" s="7" t="str">
+        <x:v>CA-016.02</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26" ht="75" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="92" customHeight="1">
+      <x:c r="A27" s="7" t="str">
         <x:v>CA-019.03</x:v>
       </x:c>
-      <x:c r="B25" s="7" t="str">
+      <x:c r="B27" s="7" t="str">
         <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D25" s="7" t="str">
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
         <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="str">
+      <x:c r="E27" s="7" t="str">
         <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="n">
+      <x:c r="F27" s="14" t="n">
         <x:v>46289</x:v>
       </x:c>
-      <x:c r="G25" s="7" t="str">
+      <x:c r="G27" s="7" t="str">
         <x:v>礼堂最终验证及完整重启复核</x:v>
       </x:c>
-      <x:c r="H25" s="16" t="str"/>
-    </x:row>
-    <x:row r="26" ht="92" customHeight="1">
-      <x:c r="A26" s="7" t="str">
+      <x:c r="H27" s="16" t="str"/>
+    </x:row>
+    <x:row r="28" ht="92" customHeight="1">
+      <x:c r="A28" s="7" t="str">
         <x:v>CA-020.02</x:v>
       </x:c>
-      <x:c r="B26" s="7" t="str">
+      <x:c r="B28" s="7" t="str">
         <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
       </x:c>
-      <x:c r="C26" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D26" s="7" t="str">
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
         <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="str">
+      <x:c r="E28" s="7" t="str">
         <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="n">
+      <x:c r="F28" s="14" t="n">
         <x:v>46289</x:v>
       </x:c>
-      <x:c r="G26" s="7" t="str">
+      <x:c r="G28" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H26" s="16" t="str"/>
-    </x:row>
-    <x:row r="27" ht="109" customHeight="1">
-      <x:c r="A27" s="7" t="str">
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="109" customHeight="1">
+      <x:c r="A29" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B27" s="7" t="str">
+      <x:c r="B29" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C27" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D27" s="7" t="str">
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="str">
+      <x:c r="E29" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="n">
+      <x:c r="F29" s="14" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="G27" s="7" t="str">
+      <x:c r="G29" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
-      </x:c>
-      <x:c r="H27" s="16" t="str"/>
-    </x:row>
-    <x:row r="28" ht="92" customHeight="1">
-      <x:c r="A28" s="7" t="str">
-        <x:v>CA-030.02</x:v>
-      </x:c>
-      <x:c r="B28" s="7" t="str">
-        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
-      </x:c>
-      <x:c r="C28" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D28" s="7" t="str">
-        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
-      </x:c>
-      <x:c r="E28" s="7" t="str">
-        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G28" s="7" t="str">
-        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
-      </x:c>
-      <x:c r="H28" s="16" t="str"/>
-    </x:row>
-    <x:row r="29" ht="92" customHeight="1">
-      <x:c r="A29" s="7" t="str">
-        <x:v>CA-031.02</x:v>
-      </x:c>
-      <x:c r="B29" s="7" t="str">
-        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
-      </x:c>
-      <x:c r="C29" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
-        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
-      </x:c>
-      <x:c r="E29" s="7" t="str">
-        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G29" s="7" t="str">
-        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
       </x:c>
       <x:c r="H29" s="16" t="str"/>
     </x:row>
     <x:row r="30" ht="92" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>CA-033.02</x:v>
+        <x:v>CA-030.02</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
       </x:c>
       <x:c r="C30" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
-        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
-        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
       </x:c>
       <x:c r="F30" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
       <x:c r="H30" s="16" t="str"/>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
       <x:c r="A31" s="7" t="str">
+        <x:v>CA-031.02</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="92" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>CA-033.02</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="92" customHeight="1">
+      <x:c r="A33" s="7" t="str">
         <x:v>CA-035.02</x:v>
       </x:c>
-      <x:c r="B31" s="7" t="str">
+      <x:c r="B33" s="7" t="str">
         <x:v>White 打开关卡与退出运行复发验收</x:v>
       </x:c>
-      <x:c r="C31" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D31" s="7" t="str">
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
         <x:v>map_opened 与 end_pie 均实际触发 refreshed：count=matched=30、skipped=0、positions_preserved=true；聊天最终确认重新打开及停止运行后正常站立。</x:v>
       </x:c>
-      <x:c r="E31" s="7" t="str">
+      <x:c r="E33" s="7" t="str">
         <x:v>本次覆盖保存、打开关卡与退出运行复发条件；未来初始化逻辑变化后按该范围回归。</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="n">
+      <x:c r="F33" s="14" t="n">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="G31" s="7" t="str">
+      <x:c r="G33" s="7" t="str">
         <x:v>map_hook_verified、end_pie_verified 及最终截图交付</x:v>
       </x:c>
-      <x:c r="H31" s="16" t="str"/>
-    </x:row>
-    <x:row r="32" ht="109" customHeight="1">
-      <x:c r="A32" s="7" t="str">
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34" ht="109" customHeight="1">
+      <x:c r="A34" s="7" t="str">
         <x:v>CA-038.02</x:v>
       </x:c>
-      <x:c r="B32" s="7" t="str">
+      <x:c r="B34" s="7" t="str">
         <x:v>scene 标准 Shipping 发布构建验收</x:v>
       </x:c>
-      <x:c r="C32" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D32" s="7" t="str">
-        <x:v>Win64 Shipping构建副本10月3日完整build/cook/stage/package成功退出0，非skipbuild/skipcook。新版CPP_InvertY包含C++与垂直反转，D3D12启动响应及正常退出检查passed，ZIP完整性通过，用户随后明确验证通过。</x:v>
-      </x:c>
-      <x:c r="E32" s="7" t="str">
-        <x:v>完成范围为10月3日发布副本；原工程规则CA-038和后续源版本发布同步CA-046.02仍独立追踪。</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G32" s="7" t="str">
-        <x:v>Shipping成功构建、运行检查与用户直接验收</x:v>
-      </x:c>
-      <x:c r="H32" s="16" t="str"/>
-    </x:row>
-    <x:row r="33" ht="75" customHeight="1">
-      <x:c r="A33" s="7" t="str">
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>保留10月3日副本完整发布及用户验收。10月4日原工程Win64 Shipping完整构建退出0，第一人称包D3D12启动响应、实际画面及退出0通过。10月5日脚本build-info再次succeeded，但该包运行验收独立见CA-065.04。</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>阶段构建验收已完成；新脚本包运行与最新白天修订同步分别判断。</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>原工程完整Shipping构建与版本化验收</x:v>
+      </x:c>
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="75" customHeight="1">
+      <x:c r="A35" s="7" t="str">
         <x:v>CA-040.09</x:v>
       </x:c>
-      <x:c r="B33" s="7" t="str">
+      <x:c r="B35" s="7" t="str">
         <x:v>综合楼后方16处地面碰撞采样</x:v>
       </x:c>
-      <x:c r="C33" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D33" s="7" t="str">
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
         <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
       </x:c>
-      <x:c r="E33" s="7" t="str">
+      <x:c r="E35" s="7" t="str">
         <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G33" s="7" t="str">
-        <x:v>validation traces 16/16 与最终交付</x:v>
-      </x:c>
-      <x:c r="H33" s="16" t="str"/>
-    </x:row>
-    <x:row r="34" ht="75" customHeight="1">
-      <x:c r="A34" s="7" t="str">
-        <x:v>CA-041.03</x:v>
-      </x:c>
-      <x:c r="B34" s="7" t="str">
-        <x:v>scene远景设置保存与前景保护验收</x:v>
-      </x:c>
-      <x:c r="C34" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D34" s="7" t="str">
-        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
-      </x:c>
-      <x:c r="E34" s="7" t="str">
-        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G34" s="7" t="str">
-        <x:v>verification 设置保存与前景、源资产校验</x:v>
-      </x:c>
-      <x:c r="H34" s="16" t="str"/>
-    </x:row>
-    <x:row r="35" ht="92" customHeight="1">
-      <x:c r="A35" s="7" t="str">
-        <x:v>CA-043.05</x:v>
-      </x:c>
-      <x:c r="B35" s="7" t="str">
-        <x:v>校园风动保存与实例合批完整性</x:v>
-      </x:c>
-      <x:c r="C35" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="str">
-        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
-      </x:c>
-      <x:c r="E35" s="7" t="str">
-        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
       </x:c>
       <x:c r="F35" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G35" s="7" t="str">
-        <x:v>风动保存回读与合批检查</x:v>
+        <x:v>validation traces 16/16 与最终交付</x:v>
       </x:c>
       <x:c r="H35" s="16" t="str"/>
     </x:row>
     <x:row r="36" ht="75" customHeight="1">
       <x:c r="A36" s="7" t="str">
-        <x:v>CA-044.03</x:v>
+        <x:v>CA-041.03</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
-        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+        <x:v>scene远景设置保存与前景保护验收</x:v>
       </x:c>
       <x:c r="C36" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D36" s="7" t="str">
-        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
       </x:c>
       <x:c r="E36" s="7" t="str">
-        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
       </x:c>
       <x:c r="F36" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G36" s="7" t="str">
-        <x:v>verification_report与最终保存交付</x:v>
+        <x:v>verification 设置保存与前景、源资产校验</x:v>
       </x:c>
       <x:c r="H36" s="16" t="str"/>
     </x:row>
     <x:row r="37" ht="92" customHeight="1">
       <x:c r="A37" s="7" t="str">
-        <x:v>CA-045.04</x:v>
+        <x:v>CA-043.05</x:v>
       </x:c>
       <x:c r="B37" s="7" t="str">
-        <x:v>第一第三人称手柄模拟输入验收</x:v>
+        <x:v>校园风动保存与实例合批完整性</x:v>
       </x:c>
       <x:c r="C37" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D37" s="7" t="str">
-        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
       </x:c>
       <x:c r="E37" s="7" t="str">
-        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
       </x:c>
       <x:c r="F37" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G37" s="7" t="str">
-        <x:v>模拟输入记录与用户新版验收</x:v>
+        <x:v>风动保存回读与合批检查</x:v>
       </x:c>
       <x:c r="H37" s="16" t="str"/>
     </x:row>
-    <x:row r="38" ht="92" customHeight="1">
+    <x:row r="38" ht="75" customHeight="1">
       <x:c r="A38" s="7" t="str">
-        <x:v>CA-047.03</x:v>
+        <x:v>CA-044.03</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
-        <x:v>食堂两侧一至二层真实往返验收</x:v>
+        <x:v>跑道花坛修复碰撞与保存验收</x:v>
       </x:c>
       <x:c r="C38" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D38" s="7" t="str">
-        <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
+        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
       </x:c>
       <x:c r="E38" s="7" t="str">
-        <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
+        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
       </x:c>
       <x:c r="F38" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G38" s="7" t="str">
-        <x:v>playtest_final与White校园路线</x:v>
+        <x:v>verification_report与最终保存交付</x:v>
       </x:c>
       <x:c r="H38" s="16" t="str"/>
     </x:row>
-    <x:row r="39" ht="75" customHeight="1">
+    <x:row r="39" ht="92" customHeight="1">
       <x:c r="A39" s="7" t="str">
-        <x:v>CA-048.02</x:v>
+        <x:v>CA-045.04</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
-        <x:v>行政楼植被清理重载与保留位置验收</x:v>
+        <x:v>第一第三人称手柄模拟输入验收</x:v>
       </x:c>
       <x:c r="C39" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D39" s="7" t="str">
-        <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
+        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
       </x:c>
       <x:c r="E39" s="7" t="str">
-        <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
+        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
       </x:c>
       <x:c r="F39" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G39" s="7" t="str">
-        <x:v>reload_verification与重载效果</x:v>
+        <x:v>模拟输入记录与用户新版验收</x:v>
       </x:c>
       <x:c r="H39" s="16" t="str"/>
     </x:row>
-    <x:row r="40" ht="75" customHeight="1">
+    <x:row r="40" ht="92" customHeight="1">
       <x:c r="A40" s="7" t="str">
-        <x:v>CA-052.06</x:v>
+        <x:v>CA-047.03</x:v>
       </x:c>
       <x:c r="B40" s="7" t="str">
-        <x:v>White十九组高度与蒙皮接触验收</x:v>
+        <x:v>食堂两侧一至二层真实往返验收</x:v>
       </x:c>
       <x:c r="C40" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D40" s="7" t="str">
-        <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
+        <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
       </x:c>
       <x:c r="E40" s="7" t="str">
-        <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
+        <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
       </x:c>
       <x:c r="F40" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G40" s="7" t="str">
-        <x:v>qa_final_summary高度与接触结果</x:v>
+        <x:v>playtest_final与White校园路线</x:v>
       </x:c>
       <x:c r="H40" s="16" t="str"/>
     </x:row>
     <x:row r="41" ht="75" customHeight="1">
       <x:c r="A41" s="7" t="str">
-        <x:v>CA-052.07</x:v>
+        <x:v>CA-048.02</x:v>
       </x:c>
       <x:c r="B41" s="7" t="str">
-        <x:v>White自动休息冷却与中断恢复验收</x:v>
+        <x:v>行政楼植被清理重载与保留位置验收</x:v>
       </x:c>
       <x:c r="C41" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D41" s="7" t="str">
-        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+        <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
       </x:c>
       <x:c r="E41" s="7" t="str">
-        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+        <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
       </x:c>
       <x:c r="F41" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G41" s="7" t="str">
-        <x:v>qa_final_summary行为结果</x:v>
+        <x:v>reload_verification与重载效果</x:v>
       </x:c>
       <x:c r="H41" s="16" t="str"/>
     </x:row>
     <x:row r="42" ht="75" customHeight="1">
       <x:c r="A42" s="7" t="str">
-        <x:v>CA-052.08</x:v>
+        <x:v>CA-052.06</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
-        <x:v>White不安全休息表面拒绝验收</x:v>
+        <x:v>White十九组高度与蒙皮接触验收</x:v>
       </x:c>
       <x:c r="C42" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D42" s="7" t="str">
-        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+        <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
       </x:c>
       <x:c r="E42" s="7" t="str">
-        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+        <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
       </x:c>
       <x:c r="F42" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G42" s="7" t="str">
+        <x:v>qa_final_summary高度与接触结果</x:v>
+      </x:c>
+      <x:c r="H42" s="16" t="str"/>
+    </x:row>
+    <x:row r="43" ht="75" customHeight="1">
+      <x:c r="A43" s="7" t="str">
+        <x:v>CA-052.07</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="str">
+        <x:v>White自动休息冷却与中断恢复验收</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="str">
+        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="str">
+        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>qa_final_summary行为结果</x:v>
+      </x:c>
+      <x:c r="H43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44" ht="75" customHeight="1">
+      <x:c r="A44" s="7" t="str">
+        <x:v>CA-052.08</x:v>
+      </x:c>
+      <x:c r="B44" s="7" t="str">
+        <x:v>White不安全休息表面拒绝验收</x:v>
+      </x:c>
+      <x:c r="C44" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="str">
+        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="str">
+        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
         <x:v>表面安全测试与限制</x:v>
       </x:c>
-      <x:c r="H42" s="16" t="str"/>
-    </x:row>
-    <x:row r="43" ht="92" customHeight="1">
-      <x:c r="A43" s="7" t="str">
+      <x:c r="H44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="92" customHeight="1">
+      <x:c r="A45" s="7" t="str">
         <x:v>CA-053.06</x:v>
       </x:c>
-      <x:c r="B43" s="7" t="str">
+      <x:c r="B45" s="7" t="str">
         <x:v>White完整体力循环与座位异常验收</x:v>
       </x:c>
-      <x:c r="C43" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D43" s="7" t="str">
+      <x:c r="C45" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="str">
         <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
       </x:c>
-      <x:c r="E43" s="7" t="str">
+      <x:c r="E45" s="7" t="str">
         <x:v>临时测试角色已清理，后续唯一White续行另见CA-053.09。</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G43" s="7" t="str">
-        <x:v>qa_stamina_result与最终交付</x:v>
-      </x:c>
-      <x:c r="H43" s="16" t="str"/>
-    </x:row>
-    <x:row r="44" ht="92" customHeight="1">
-      <x:c r="A44" s="7" t="str">
-        <x:v>CA-053.09</x:v>
-      </x:c>
-      <x:c r="B44" s="7" t="str">
-        <x:v>唯一White十二条跨校园实走验收</x:v>
-      </x:c>
-      <x:c r="C44" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D44" s="7" t="str">
-        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
-      </x:c>
-      <x:c r="E44" s="7" t="str">
-        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G44" s="7" t="str">
-        <x:v>suite_result与final_result</x:v>
-      </x:c>
-      <x:c r="H44" s="16" t="str"/>
-    </x:row>
-    <x:row r="45" ht="75" customHeight="1">
-      <x:c r="A45" s="7" t="str">
-        <x:v>CA-053.10</x:v>
-      </x:c>
-      <x:c r="B45" s="7" t="str">
-        <x:v>White全校园随机选点覆盖抽样</x:v>
-      </x:c>
-      <x:c r="C45" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D45" s="7" t="str">
-        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
-      </x:c>
-      <x:c r="E45" s="7" t="str">
-        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
       </x:c>
       <x:c r="F45" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G45" s="7" t="str">
-        <x:v>final_result随机覆盖与解释</x:v>
+        <x:v>qa_stamina_result与最终交付</x:v>
       </x:c>
       <x:c r="H45" s="16" t="str"/>
     </x:row>
     <x:row r="46" ht="92" customHeight="1">
       <x:c r="A46" s="7" t="str">
-        <x:v>CA-054.02</x:v>
+        <x:v>CA-053.09</x:v>
       </x:c>
       <x:c r="B46" s="7" t="str">
-        <x:v>唯一White与观察入口运行验收</x:v>
+        <x:v>唯一White十二条跨校园实走验收</x:v>
       </x:c>
       <x:c r="C46" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D46" s="7" t="str">
-        <x:v>移除89名后保存，正常PIE确认仅1个White、SpectatorPawn被玩家控制且无网格，观察移动/转向和White行走/体力消耗通过，108座椅保留。</x:v>
+        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
       </x:c>
       <x:c r="E46" s="7" t="str">
-        <x:v>当前人物数量见CA-002，不能将旧90人测试当当前人数。</x:v>
+        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
       </x:c>
       <x:c r="F46" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G46" s="7" t="str">
-        <x:v>WhiteSingle final_result与play_result</x:v>
+        <x:v>suite_result与final_result</x:v>
       </x:c>
       <x:c r="H46" s="16" t="str"/>
     </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="1"/>
-      <x:c r="B47" s="1"/>
-      <x:c r="C47" s="1"/>
-      <x:c r="D47" s="1"/>
-      <x:c r="E47" s="1"/>
-      <x:c r="F47" s="1"/>
-      <x:c r="G47" s="1"/>
-      <x:c r="H47" s="1"/>
-    </x:row>
-    <x:row r="48" ht="34" customHeight="1">
-      <x:c r="A48" s="3" t="str">
+    <x:row r="47" ht="75" customHeight="1">
+      <x:c r="A47" s="7" t="str">
+        <x:v>CA-053.10</x:v>
+      </x:c>
+      <x:c r="B47" s="7" t="str">
+        <x:v>White全校园随机选点覆盖抽样</x:v>
+      </x:c>
+      <x:c r="C47" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="str">
+        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="str">
+        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
+        <x:v>final_result随机覆盖与解释</x:v>
+      </x:c>
+      <x:c r="H47" s="16" t="str"/>
+    </x:row>
+    <x:row r="48" ht="92" customHeight="1">
+      <x:c r="A48" s="7" t="str">
+        <x:v>CA-054.02</x:v>
+      </x:c>
+      <x:c r="B48" s="7" t="str">
+        <x:v>唯一White与观察入口阶段运行验收</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="str">
+        <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="str">
+        <x:v>当前入口运行检查见CA-055；单White指学生实例，不把玩家角色误算为新增学生。</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
+        <x:v>原观察验证与后续第一人称运行结果</x:v>
+      </x:c>
+      <x:c r="H48" s="16" t="str"/>
+    </x:row>
+    <x:row r="49" ht="109" customHeight="1">
+      <x:c r="A49" s="7" t="str">
+        <x:v>CA-055</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="str">
+        <x:v>第一人称默认出生与十五项运行验收</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="str">
+        <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="str">
+        <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>startup_runtime_report与新包画面</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="75" customHeight="1">
+      <x:c r="A50" s="7" t="str">
+        <x:v>CA-056.02</x:v>
+      </x:c>
+      <x:c r="B50" s="7" t="str">
+        <x:v>高三楼门三百二十八项运行验收</x:v>
+      </x:c>
+      <x:c r="C50" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="str">
+        <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="str">
+        <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G50" s="7" t="str">
+        <x:v>runtime_verification与completion</x:v>
+      </x:c>
+      <x:c r="H50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="58" customHeight="1">
+      <x:c r="A51" s="7" t="str">
+        <x:v>CA-056.03</x:v>
+      </x:c>
+      <x:c r="B51" s="7" t="str">
+        <x:v>高三门保存回读与原门保护验收</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="str">
+        <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="str">
+        <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G51" s="7" t="str">
+        <x:v>persisted_verification</x:v>
+      </x:c>
+      <x:c r="H51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="75" customHeight="1">
+      <x:c r="A52" s="7" t="str">
+        <x:v>CA-057.04</x:v>
+      </x:c>
+      <x:c r="B52" s="7" t="str">
+        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
+      </x:c>
+      <x:c r="C52" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="str">
+        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="str">
+        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G52" s="7" t="str">
+        <x:v>V2 verification</x:v>
+      </x:c>
+      <x:c r="H52" s="16" t="str"/>
+    </x:row>
+    <x:row r="53" ht="75" customHeight="1">
+      <x:c r="A53" s="7" t="str">
+        <x:v>CA-058.03</x:v>
+      </x:c>
+      <x:c r="B53" s="7" t="str">
+        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
+      </x:c>
+      <x:c r="C53" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="str">
+        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="str">
+        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G53" s="7" t="str">
+        <x:v>遮阳棚verification</x:v>
+      </x:c>
+      <x:c r="H53" s="16" t="str"/>
+    </x:row>
+    <x:row r="54" ht="58" customHeight="1">
+      <x:c r="A54" s="7" t="str">
+        <x:v>CA-059.03</x:v>
+      </x:c>
+      <x:c r="B54" s="7" t="str">
+        <x:v>棕榈落地树干碰撞与通道检查</x:v>
+      </x:c>
+      <x:c r="C54" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="str">
+        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="str">
+        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
+        <x:v>palms_verification</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str"/>
+    </x:row>
+    <x:row r="55" ht="75" customHeight="1">
+      <x:c r="A55" s="7" t="str">
+        <x:v>CA-060.03</x:v>
+      </x:c>
+      <x:c r="B55" s="7" t="str">
+        <x:v>校训朝向字距屋顶贴合检查</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D55" s="7" t="str">
+        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="str">
+        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G55" s="7" t="str">
+        <x:v>verification与final_save</x:v>
+      </x:c>
+      <x:c r="H55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="75" customHeight="1">
+      <x:c r="A56" s="7" t="str">
+        <x:v>CA-061.02</x:v>
+      </x:c>
+      <x:c r="B56" s="7" t="str">
+        <x:v>大纲整理场景属性与实例保护验收</x:v>
+      </x:c>
+      <x:c r="C56" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="str">
+        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="str">
+        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G56" s="7" t="str">
+        <x:v>大纲verification</x:v>
+      </x:c>
+      <x:c r="H56" s="16" t="str"/>
+    </x:row>
+    <x:row r="57" ht="75" customHeight="1">
+      <x:c r="A57" s="7" t="str">
+        <x:v>CA-063.05</x:v>
+      </x:c>
+      <x:c r="B57" s="7" t="str">
+        <x:v>参考夜景保存与模拟运行检查</x:v>
+      </x:c>
+      <x:c r="C57" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D57" s="7" t="str">
+        <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="str">
+        <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="str">
+        <x:v>final_verified与runtime_verified</x:v>
+      </x:c>
+      <x:c r="H57" s="16" t="str"/>
+    </x:row>
+    <x:row r="58" ht="75" customHeight="1">
+      <x:c r="A58" s="7" t="str">
+        <x:v>CA-064.07</x:v>
+      </x:c>
+      <x:c r="B58" s="7" t="str">
+        <x:v>三轮昼夜切换原夜景参数还原</x:v>
+      </x:c>
+      <x:c r="C58" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D58" s="7" t="str">
+        <x:v>三轮切换均白天零灯、夜间300灯原值精确恢复，night_environment_exact=true；原夜空shader哈希一致、捕获分支保留。</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="str">
+        <x:v>通过的是参数、材质分支和灯光还原；不将数值一致扩大为每像素全视角一致。</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G58" s="7" t="str">
+        <x:v>Daylight scene_verified三轮结果</x:v>
+      </x:c>
+      <x:c r="H58" s="16" t="str"/>
+    </x:row>
+    <x:row r="59" ht="92" customHeight="1">
+      <x:c r="A59" s="7" t="str">
+        <x:v>CA-064.08</x:v>
+      </x:c>
+      <x:c r="B59" s="7" t="str">
+        <x:v>昼夜九项自动化环境回归</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="str">
+        <x:v>最新Automation index为succeeded9、failed0、warnings0、notRun0，覆盖时钟、日出兜底、禁灯/日落、夜景缓存及环境过渡；早期4/7项为阶段历史。</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="str">
+        <x:v>测试跑于编辑器；最新发布包范围仍见CA-046.03。</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
+        <x:v>最新自动化index与最终聊天</x:v>
+      </x:c>
+      <x:c r="H59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="92" customHeight="1">
+      <x:c r="A60" s="7" t="str">
+        <x:v>CA-065.03</x:v>
+      </x:c>
+      <x:c r="B60" s="7" t="str">
+        <x:v>一键脚本原工程完整构建交付</x:v>
+      </x:c>
+      <x:c r="C60" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="str">
+        <x:v>聊天中未执行完整打包，随后build-info提供实际运行：00:32开始、00:39:21 succeeded，原工程Win64 Shipping完整build/cook/stage/package，生成Windows/CampusAuto.exe。</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="str">
+        <x:v>明确以保存构建记录补充聊天；运行及后续白天修订分别见CA-065.04、CA-046.03。</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G60" s="7" t="str">
+        <x:v>ScenePackages build-info实际成功记录</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="34" customHeight="1">
+      <x:c r="A62" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B48" s="21" t="str">
+      <x:c r="B62" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C48" s="21"/>
-      <x:c r="D48" s="21"/>
-      <x:c r="E48" s="21"/>
-      <x:c r="F48" s="21"/>
-      <x:c r="G48" s="21"/>
-      <x:c r="H48" s="21"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="1"/>
-      <x:c r="B49" s="1"/>
-      <x:c r="C49" s="1"/>
-      <x:c r="D49" s="1"/>
-      <x:c r="E49" s="1"/>
-      <x:c r="F49" s="1"/>
-      <x:c r="G49" s="1"/>
-      <x:c r="H49" s="1"/>
+      <x:c r="C62" s="21"/>
+      <x:c r="D62" s="21"/>
+      <x:c r="E62" s="21"/>
+      <x:c r="F62" s="21"/>
+      <x:c r="G62" s="21"/>
+      <x:c r="H62" s="21"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B48:H48"/>
+    <x:mergeCell ref="B62:H62"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C46">
+  <x:conditionalFormatting sqref="C8:C60">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1508,13 +1844,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C46">
+    <x:dataValidation type="list" sqref="C8:C60">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0755ece13e184678"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R403528f2aabf4bde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R8b56f950ee36424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R655ac8adf41149b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H60"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H64"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
+        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C60,A5)</x:f>
-        <x:v>41</x:v>
+        <x:f>COUNTIF(C8:C64,A5)</x:f>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C60,D5)</x:f>
+        <x:f>COUNTIF(C8:C64,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C60,F5)</x:f>
+        <x:f>COUNTIF(C8:C64,F5)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -784,7 +784,7 @@
       </x:c>
       <x:c r="H18" s="16" t="str"/>
     </x:row>
-    <x:row r="19" ht="92" customHeight="1">
+    <x:row r="19" ht="109" customHeight="1">
       <x:c r="A19" s="7" t="str">
         <x:v>CA-065.04</x:v>
       </x:c>
@@ -795,10 +795,10 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>00:39脚本构建记录succeeded证明构建和文件检查通过；未找到此批成品的启动画面、响应、退出或玩法验收。10月4日FirstPerson包运行通过属于上一批。</x:v>
+        <x:v>原00:39成品以及新增10:02、11:54、16:45、18:23成品均有构建成功记录；本轮未找到这些批次的启动画面、响应、退出或玩法验收。编辑器材质A/B和昼夜测试不能代替Shipping运行。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>确认是否已有此批实际运行验收；不启动游戏替代追踪。</x:v>
+        <x:v>核对具体包的实际运行记录；不启动游戏替代追踪。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
         <x:v>46300</x:v>
@@ -1722,7 +1722,7 @@
       </x:c>
       <x:c r="H57" s="16" t="str"/>
     </x:row>
-    <x:row r="58" ht="75" customHeight="1">
+    <x:row r="58" ht="92" customHeight="1">
       <x:c r="A58" s="7" t="str">
         <x:v>CA-064.07</x:v>
       </x:c>
@@ -1733,10 +1733,10 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D58" s="7" t="str">
-        <x:v>三轮切换均白天零灯、夜间300灯原值精确恢复，night_environment_exact=true；原夜空shader哈希一致、捕获分支保留。</x:v>
+        <x:v>初版三轮昼夜300灯精确还原保留。最新黄昏检查17:00至22:00各阶段，22:00全部300灯恢复原亮度，night_restored_exactly=true；正午零灯规则仍通过。</x:v>
       </x:c>
       <x:c r="E58" s="7" t="str">
-        <x:v>通过的是参数、材质分支和灯光还原；不将数值一致扩大为每像素全视角一致。</x:v>
+        <x:v>原夜空已因月升月落按用户要求修改，不再声称当前夜空shader与旧版完全一致；只认定各阶段参数验收。</x:v>
       </x:c>
       <x:c r="F58" s="14" t="n">
         <x:v>46300</x:v>
@@ -1751,16 +1751,16 @@
         <x:v>CA-064.08</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
-        <x:v>昼夜九项自动化环境回归</x:v>
+        <x:v>当前昼夜十六项自动化环境回归</x:v>
       </x:c>
       <x:c r="C59" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D59" s="7" t="str">
-        <x:v>最新Automation index为succeeded9、failed0、warnings0、notRun0，覆盖时钟、日出兜底、禁灯/日落、夜景缓存及环境过渡；早期4/7项为阶段历史。</x:v>
+        <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
       </x:c>
       <x:c r="E59" s="7" t="str">
-        <x:v>测试跑于编辑器；最新发布包范围仍见CA-046.03。</x:v>
+        <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
       </x:c>
       <x:c r="F59" s="14" t="n">
         <x:v>46300</x:v>
@@ -1770,7 +1770,7 @@
       </x:c>
       <x:c r="H59" s="16" t="str"/>
     </x:row>
-    <x:row r="60" ht="92" customHeight="1">
+    <x:row r="60" ht="109" customHeight="1">
       <x:c r="A60" s="7" t="str">
         <x:v>CA-065.03</x:v>
       </x:c>
@@ -1781,10 +1781,10 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D60" s="7" t="str">
-        <x:v>聊天中未执行完整打包，随后build-info提供实际运行：00:32开始、00:39:21 succeeded，原工程Win64 Shipping完整build/cook/stage/package，生成Windows/CampusAuto.exe。</x:v>
+        <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
       </x:c>
       <x:c r="E60" s="7" t="str">
-        <x:v>明确以保存构建记录补充聊天；运行及后续白天修订分别见CA-065.04、CA-046.03。</x:v>
+        <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
       </x:c>
       <x:c r="F60" s="14" t="n">
         <x:v>46300</x:v>
@@ -1794,45 +1794,141 @@
       </x:c>
       <x:c r="H60" s="16" t="str"/>
     </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="1"/>
-      <x:c r="B61" s="1"/>
-      <x:c r="C61" s="1"/>
-      <x:c r="D61" s="1"/>
-      <x:c r="E61" s="1"/>
-      <x:c r="F61" s="1"/>
-      <x:c r="G61" s="1"/>
-      <x:c r="H61" s="1"/>
-    </x:row>
-    <x:row r="62" ht="34" customHeight="1">
-      <x:c r="A62" s="3" t="str">
+    <x:row r="61" ht="92" customHeight="1">
+      <x:c r="A61" s="7" t="str">
+        <x:v>CA-066.02</x:v>
+      </x:c>
+      <x:c r="B61" s="7" t="str">
+        <x:v>时间面板调时暂停与保存基准检查</x:v>
+      </x:c>
+      <x:c r="C61" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D61" s="7" t="str">
+        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="str">
+        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G61" s="7" t="str">
+        <x:v>面板实操及夜景恢复检查</x:v>
+      </x:c>
+      <x:c r="H61" s="16" t="str"/>
+    </x:row>
+    <x:row r="62" ht="75" customHeight="1">
+      <x:c r="A62" s="7" t="str">
+        <x:v>CA-068.02</x:v>
+      </x:c>
+      <x:c r="B62" s="7" t="str">
+        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
+      </x:c>
+      <x:c r="C62" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D62" s="7" t="str">
+        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="str">
+        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G62" s="7" t="str">
+        <x:v>月亮运行796帧与重载报告</x:v>
+      </x:c>
+      <x:c r="H62" s="16" t="str"/>
+    </x:row>
+    <x:row r="63" ht="75" customHeight="1">
+      <x:c r="A63" s="7" t="str">
+        <x:v>CA-070.04</x:v>
+      </x:c>
+      <x:c r="B63" s="7" t="str">
+        <x:v>教学楼材质合批镜像与门结构保持</x:v>
+      </x:c>
+      <x:c r="C63" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D63" s="7" t="str">
+        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="str">
+        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G63" s="7" t="str">
+        <x:v>真实材质与纯色门结构验证</x:v>
+      </x:c>
+      <x:c r="H63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="92" customHeight="1">
+      <x:c r="A64" s="7" t="str">
+        <x:v>CA-071.05</x:v>
+      </x:c>
+      <x:c r="B64" s="7" t="str">
+        <x:v>草地全量朝向坐标材质及保存检查</x:v>
+      </x:c>
+      <x:c r="C64" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="str">
+        <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="str">
+        <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
+        <x:v>草地全量检查和67秒保存回执</x:v>
+      </x:c>
+      <x:c r="H64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+    </x:row>
+    <x:row r="66" ht="34" customHeight="1">
+      <x:c r="A66" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B62" s="21" t="str">
+      <x:c r="B66" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C62" s="21"/>
-      <x:c r="D62" s="21"/>
-      <x:c r="E62" s="21"/>
-      <x:c r="F62" s="21"/>
-      <x:c r="G62" s="21"/>
-      <x:c r="H62" s="21"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="1"/>
-      <x:c r="B63" s="1"/>
-      <x:c r="C63" s="1"/>
-      <x:c r="D63" s="1"/>
-      <x:c r="E63" s="1"/>
-      <x:c r="F63" s="1"/>
-      <x:c r="G63" s="1"/>
-      <x:c r="H63" s="1"/>
+      <x:c r="C66" s="21"/>
+      <x:c r="D66" s="21"/>
+      <x:c r="E66" s="21"/>
+      <x:c r="F66" s="21"/>
+      <x:c r="G66" s="21"/>
+      <x:c r="H66" s="21"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="1"/>
+      <x:c r="B67" s="1"/>
+      <x:c r="C67" s="1"/>
+      <x:c r="D67" s="1"/>
+      <x:c r="E67" s="1"/>
+      <x:c r="F67" s="1"/>
+      <x:c r="G67" s="1"/>
+      <x:c r="H67" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B62:H62"/>
+    <x:mergeCell ref="B66:H66"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C60">
+  <x:conditionalFormatting sqref="C8:C64">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1844,13 +1940,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C60">
+    <x:dataValidation type="list" sqref="C8:C64">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R403528f2aabf4bde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31f6c9cc469a463d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R655ac8adf41149b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="Re7609947bcd648c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H64"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H70"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C64,A5)</x:f>
-        <x:v>45</x:v>
+        <x:f>COUNTIF(C8:C70,A5)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C64,D5)</x:f>
+        <x:f>COUNTIF(C8:C70,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C64,F5)</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(C8:C70,F5)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -789,1146 +789,1290 @@
         <x:v>CA-065.04</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>十月五日脚本成品实际运行验收</x:v>
+        <x:v>脚本各批Shipping成品实际运行验收</x:v>
       </x:c>
       <x:c r="C19" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>原00:39成品以及新增10:02、11:54、16:45、18:23成品均有构建成功记录；本轮未找到这些批次的启动画面、响应、退出或玩法验收。编辑器材质A/B和昼夜测试不能代替Shipping运行。</x:v>
+        <x:v>10月5日5批构建及10月6日10:08、11:07、17:54成品均有succeeded记录；未找到这些具体包的启动画面、响应、退出或玩法验收。150人和天气编辑器运行通过不能替代Shipping实测。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>核对具体包的实际运行记录；不启动游戏替代追踪。</x:v>
+        <x:v>按具体发布包核对运行记录；最新已构建150人和天气，仍缺对应成品实机验收，不由追踪任务启动游戏。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>46300</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>脚本build-info与明确运行验收边界</x:v>
+        <x:v>新增三批build-info及聊天运行范围</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
     <x:row r="20" ht="92" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>CA-001.07</x:v>
+        <x:v>CA-072.05</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>White 换装后 30 人运行与保存验收</x:v>
-      </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>150人低体力休息抽查的座位限制</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
+        <x:v>强制低体力抽查3人，2人完成坐下、恢复体力并续走原目标；1人反复选到被地面或站立空间检查拒绝的现有座位，120秒超时，原换座重试行为保留。</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
+        <x:v>需确认该座位限制是否接受或另有后续通过记录；2人通过不能替代第3人的关闭证据。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46296</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
+        <x:v>最终交付明确2通过1超时</x:v>
       </x:c>
       <x:c r="H20" s="16" t="str"/>
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>CA-006.05</x:v>
+        <x:v>CA-001.07</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
+        <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
       <x:c r="C21" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
+        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
+        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
+        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C22" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H22" s="16" t="str"/>
     </x:row>
-    <x:row r="23" ht="75" customHeight="1">
+    <x:row r="23" ht="92" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-006.06</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
       </x:c>
       <x:c r="C23" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="75" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-014.04</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
         <x:v>综合楼运行与逐级踏步验收记录</x:v>
-      </x:c>
-      <x:c r="H23" s="16" t="str"/>
-    </x:row>
-    <x:row r="24" ht="92" customHeight="1">
-      <x:c r="A24" s="7" t="str">
-        <x:v>CA-015.02</x:v>
-      </x:c>
-      <x:c r="B24" s="7" t="str">
-        <x:v>教学楼 A B 一至四层往返验收</x:v>
-      </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
-        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
-      </x:c>
-      <x:c r="E24" s="7" t="str">
-        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G24" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>CA-016.02</x:v>
+        <x:v>CA-015.02</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+        <x:v>教学楼 A B 一至四层往返验收</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
-    <x:row r="26" ht="75" customHeight="1">
+    <x:row r="26" ht="92" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>CA-017.03</x:v>
+        <x:v>CA-016.02</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="75" customHeight="1">
+      <x:c r="A27" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
         <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
-      </x:c>
-      <x:c r="H26" s="16" t="str"/>
-    </x:row>
-    <x:row r="27" ht="92" customHeight="1">
-      <x:c r="A27" s="7" t="str">
-        <x:v>CA-019.03</x:v>
-      </x:c>
-      <x:c r="B27" s="7" t="str">
-        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
-      </x:c>
-      <x:c r="C27" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D27" s="7" t="str">
-        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
-      </x:c>
-      <x:c r="E27" s="7" t="str">
-        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="n">
-        <x:v>46289</x:v>
-      </x:c>
-      <x:c r="G27" s="7" t="str">
-        <x:v>礼堂最终验证及完整重启复核</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>CA-020.02</x:v>
+        <x:v>CA-019.03</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
+        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
       </x:c>
       <x:c r="C28" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
+        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
-        <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
+        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
       </x:c>
       <x:c r="F28" s="14" t="n">
         <x:v>46289</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
+        <x:v>礼堂最终验证及完整重启复核</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="92" customHeight="1">
+      <x:c r="A29" s="7" t="str">
+        <x:v>CA-020.02</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="str">
+        <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
+        <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="n">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H28" s="16" t="str"/>
-    </x:row>
-    <x:row r="29" ht="109" customHeight="1">
-      <x:c r="A29" s="7" t="str">
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="109" customHeight="1">
+      <x:c r="A30" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B29" s="7" t="str">
+      <x:c r="B30" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C29" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="str">
+      <x:c r="E30" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="n">
+      <x:c r="F30" s="14" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="G29" s="7" t="str">
+      <x:c r="G30" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
-      </x:c>
-      <x:c r="H29" s="16" t="str"/>
-    </x:row>
-    <x:row r="30" ht="92" customHeight="1">
-      <x:c r="A30" s="7" t="str">
-        <x:v>CA-030.02</x:v>
-      </x:c>
-      <x:c r="B30" s="7" t="str">
-        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
-      </x:c>
-      <x:c r="C30" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="str">
-        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
-      </x:c>
-      <x:c r="E30" s="7" t="str">
-        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G30" s="7" t="str">
-        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
       <x:c r="H30" s="16" t="str"/>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>CA-031.02</x:v>
+        <x:v>CA-030.02</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
+        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
       </x:c>
       <x:c r="C31" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
+        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
-        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
+        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>46292</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
+        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
       <x:c r="H31" s="16" t="str"/>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
       <x:c r="A32" s="7" t="str">
-        <x:v>CA-033.02</x:v>
+        <x:v>CA-031.02</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
       </x:c>
       <x:c r="C32" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D32" s="7" t="str">
-        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
       </x:c>
       <x:c r="F32" s="14" t="n">
-        <x:v>46292</x:v>
+        <x:v>46291</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
-        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
       </x:c>
       <x:c r="H32" s="16" t="str"/>
     </x:row>
     <x:row r="33" ht="92" customHeight="1">
       <x:c r="A33" s="7" t="str">
+        <x:v>CA-033.02</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34" ht="92" customHeight="1">
+      <x:c r="A34" s="7" t="str">
         <x:v>CA-035.02</x:v>
       </x:c>
-      <x:c r="B33" s="7" t="str">
+      <x:c r="B34" s="7" t="str">
         <x:v>White 打开关卡与退出运行复发验收</x:v>
       </x:c>
-      <x:c r="C33" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D33" s="7" t="str">
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
         <x:v>map_opened 与 end_pie 均实际触发 refreshed：count=matched=30、skipped=0、positions_preserved=true；聊天最终确认重新打开及停止运行后正常站立。</x:v>
       </x:c>
-      <x:c r="E33" s="7" t="str">
+      <x:c r="E34" s="7" t="str">
         <x:v>本次覆盖保存、打开关卡与退出运行复发条件；未来初始化逻辑变化后按该范围回归。</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="n">
+      <x:c r="F34" s="14" t="n">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="G33" s="7" t="str">
+      <x:c r="G34" s="7" t="str">
         <x:v>map_hook_verified、end_pie_verified 及最终截图交付</x:v>
       </x:c>
-      <x:c r="H33" s="16" t="str"/>
-    </x:row>
-    <x:row r="34" ht="109" customHeight="1">
-      <x:c r="A34" s="7" t="str">
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="109" customHeight="1">
+      <x:c r="A35" s="7" t="str">
         <x:v>CA-038.02</x:v>
       </x:c>
-      <x:c r="B34" s="7" t="str">
+      <x:c r="B35" s="7" t="str">
         <x:v>scene 标准 Shipping 发布构建验收</x:v>
       </x:c>
-      <x:c r="C34" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D34" s="7" t="str">
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
         <x:v>保留10月3日副本完整发布及用户验收。10月4日原工程Win64 Shipping完整构建退出0，第一人称包D3D12启动响应、实际画面及退出0通过。10月5日脚本build-info再次succeeded，但该包运行验收独立见CA-065.04。</x:v>
       </x:c>
-      <x:c r="E34" s="7" t="str">
+      <x:c r="E35" s="7" t="str">
         <x:v>阶段构建验收已完成；新脚本包运行与最新白天修订同步分别判断。</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="n">
+      <x:c r="F35" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="G34" s="7" t="str">
+      <x:c r="G35" s="7" t="str">
         <x:v>原工程完整Shipping构建与版本化验收</x:v>
-      </x:c>
-      <x:c r="H34" s="16" t="str"/>
-    </x:row>
-    <x:row r="35" ht="75" customHeight="1">
-      <x:c r="A35" s="7" t="str">
-        <x:v>CA-040.09</x:v>
-      </x:c>
-      <x:c r="B35" s="7" t="str">
-        <x:v>综合楼后方16处地面碰撞采样</x:v>
-      </x:c>
-      <x:c r="C35" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="str">
-        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
-      </x:c>
-      <x:c r="E35" s="7" t="str">
-        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G35" s="7" t="str">
-        <x:v>validation traces 16/16 与最终交付</x:v>
       </x:c>
       <x:c r="H35" s="16" t="str"/>
     </x:row>
     <x:row r="36" ht="75" customHeight="1">
       <x:c r="A36" s="7" t="str">
-        <x:v>CA-041.03</x:v>
+        <x:v>CA-040.09</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
-        <x:v>scene远景设置保存与前景保护验收</x:v>
+        <x:v>综合楼后方16处地面碰撞采样</x:v>
       </x:c>
       <x:c r="C36" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D36" s="7" t="str">
-        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
+        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
       </x:c>
       <x:c r="E36" s="7" t="str">
-        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
+        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
       </x:c>
       <x:c r="F36" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G36" s="7" t="str">
-        <x:v>verification 设置保存与前景、源资产校验</x:v>
+        <x:v>validation traces 16/16 与最终交付</x:v>
       </x:c>
       <x:c r="H36" s="16" t="str"/>
     </x:row>
-    <x:row r="37" ht="92" customHeight="1">
+    <x:row r="37" ht="75" customHeight="1">
       <x:c r="A37" s="7" t="str">
-        <x:v>CA-043.05</x:v>
+        <x:v>CA-041.03</x:v>
       </x:c>
       <x:c r="B37" s="7" t="str">
-        <x:v>校园风动保存与实例合批完整性</x:v>
+        <x:v>scene远景设置保存与前景保护验收</x:v>
       </x:c>
       <x:c r="C37" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D37" s="7" t="str">
-        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
       </x:c>
       <x:c r="E37" s="7" t="str">
-        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
       </x:c>
       <x:c r="F37" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G37" s="7" t="str">
-        <x:v>风动保存回读与合批检查</x:v>
+        <x:v>verification 设置保存与前景、源资产校验</x:v>
       </x:c>
       <x:c r="H37" s="16" t="str"/>
     </x:row>
-    <x:row r="38" ht="75" customHeight="1">
+    <x:row r="38" ht="92" customHeight="1">
       <x:c r="A38" s="7" t="str">
-        <x:v>CA-044.03</x:v>
+        <x:v>CA-043.05</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
-        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+        <x:v>校园风动保存与实例合批完整性</x:v>
       </x:c>
       <x:c r="C38" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D38" s="7" t="str">
-        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
       </x:c>
       <x:c r="E38" s="7" t="str">
-        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
+        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
       </x:c>
       <x:c r="F38" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G38" s="7" t="str">
-        <x:v>verification_report与最终保存交付</x:v>
+        <x:v>风动保存回读与合批检查</x:v>
       </x:c>
       <x:c r="H38" s="16" t="str"/>
     </x:row>
-    <x:row r="39" ht="92" customHeight="1">
+    <x:row r="39" ht="75" customHeight="1">
       <x:c r="A39" s="7" t="str">
-        <x:v>CA-045.04</x:v>
+        <x:v>CA-044.03</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
-        <x:v>第一第三人称手柄模拟输入验收</x:v>
+        <x:v>跑道花坛修复碰撞与保存验收</x:v>
       </x:c>
       <x:c r="C39" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D39" s="7" t="str">
-        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
       </x:c>
       <x:c r="E39" s="7" t="str">
-        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
       </x:c>
       <x:c r="F39" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G39" s="7" t="str">
-        <x:v>模拟输入记录与用户新版验收</x:v>
+        <x:v>verification_report与最终保存交付</x:v>
       </x:c>
       <x:c r="H39" s="16" t="str"/>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
       <x:c r="A40" s="7" t="str">
+        <x:v>CA-045.04</x:v>
+      </x:c>
+      <x:c r="B40" s="7" t="str">
+        <x:v>第一第三人称手柄模拟输入验收</x:v>
+      </x:c>
+      <x:c r="C40" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="str">
+        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="str">
+        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>模拟输入记录与用户新版验收</x:v>
+      </x:c>
+      <x:c r="H40" s="16" t="str"/>
+    </x:row>
+    <x:row r="41" ht="92" customHeight="1">
+      <x:c r="A41" s="7" t="str">
+        <x:v>CA-046.05</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="str">
+        <x:v>150人及最终天气版本Shipping构建</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="str">
+        <x:v>150人10月6日10:57交付后11:00–11:07完整Shipping成功；最终天气15:40交付后17:47–17:54再构建成功，build-info指向原工程scene，exe存在。</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="str">
+        <x:v>构建成功不等于成品玩法、实际帧率或长时天气验收，见CA-065.04。</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>后续完整构建状态与版本时序</x:v>
+      </x:c>
+      <x:c r="H41" s="16" t="str"/>
+    </x:row>
+    <x:row r="42" ht="92" customHeight="1">
+      <x:c r="A42" s="7" t="str">
         <x:v>CA-047.03</x:v>
       </x:c>
-      <x:c r="B40" s="7" t="str">
+      <x:c r="B42" s="7" t="str">
         <x:v>食堂两侧一至二层真实往返验收</x:v>
       </x:c>
-      <x:c r="C40" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D40" s="7" t="str">
+      <x:c r="C42" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="str">
         <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
       </x:c>
-      <x:c r="E40" s="7" t="str">
+      <x:c r="E42" s="7" t="str">
         <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
       </x:c>
-      <x:c r="F40" s="14" t="n">
+      <x:c r="F42" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G40" s="7" t="str">
+      <x:c r="G42" s="7" t="str">
         <x:v>playtest_final与White校园路线</x:v>
-      </x:c>
-      <x:c r="H40" s="16" t="str"/>
-    </x:row>
-    <x:row r="41" ht="75" customHeight="1">
-      <x:c r="A41" s="7" t="str">
-        <x:v>CA-048.02</x:v>
-      </x:c>
-      <x:c r="B41" s="7" t="str">
-        <x:v>行政楼植被清理重载与保留位置验收</x:v>
-      </x:c>
-      <x:c r="C41" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D41" s="7" t="str">
-        <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
-      </x:c>
-      <x:c r="E41" s="7" t="str">
-        <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G41" s="7" t="str">
-        <x:v>reload_verification与重载效果</x:v>
-      </x:c>
-      <x:c r="H41" s="16" t="str"/>
-    </x:row>
-    <x:row r="42" ht="75" customHeight="1">
-      <x:c r="A42" s="7" t="str">
-        <x:v>CA-052.06</x:v>
-      </x:c>
-      <x:c r="B42" s="7" t="str">
-        <x:v>White十九组高度与蒙皮接触验收</x:v>
-      </x:c>
-      <x:c r="C42" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D42" s="7" t="str">
-        <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
-      </x:c>
-      <x:c r="E42" s="7" t="str">
-        <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G42" s="7" t="str">
-        <x:v>qa_final_summary高度与接触结果</x:v>
       </x:c>
       <x:c r="H42" s="16" t="str"/>
     </x:row>
     <x:row r="43" ht="75" customHeight="1">
       <x:c r="A43" s="7" t="str">
-        <x:v>CA-052.07</x:v>
+        <x:v>CA-048.02</x:v>
       </x:c>
       <x:c r="B43" s="7" t="str">
-        <x:v>White自动休息冷却与中断恢复验收</x:v>
+        <x:v>行政楼植被清理重载与保留位置验收</x:v>
       </x:c>
       <x:c r="C43" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D43" s="7" t="str">
-        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+        <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
       </x:c>
       <x:c r="E43" s="7" t="str">
-        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+        <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
       </x:c>
       <x:c r="F43" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G43" s="7" t="str">
-        <x:v>qa_final_summary行为结果</x:v>
+        <x:v>reload_verification与重载效果</x:v>
       </x:c>
       <x:c r="H43" s="16" t="str"/>
     </x:row>
     <x:row r="44" ht="75" customHeight="1">
       <x:c r="A44" s="7" t="str">
-        <x:v>CA-052.08</x:v>
+        <x:v>CA-052.06</x:v>
       </x:c>
       <x:c r="B44" s="7" t="str">
-        <x:v>White不安全休息表面拒绝验收</x:v>
+        <x:v>White十九组高度与蒙皮接触验收</x:v>
       </x:c>
       <x:c r="C44" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D44" s="7" t="str">
-        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+        <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
       </x:c>
       <x:c r="E44" s="7" t="str">
-        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+        <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
       </x:c>
       <x:c r="F44" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G44" s="7" t="str">
+        <x:v>qa_final_summary高度与接触结果</x:v>
+      </x:c>
+      <x:c r="H44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="75" customHeight="1">
+      <x:c r="A45" s="7" t="str">
+        <x:v>CA-052.07</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="str">
+        <x:v>White自动休息冷却与中断恢复验收</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="str">
+        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="str">
+        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>qa_final_summary行为结果</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="75" customHeight="1">
+      <x:c r="A46" s="7" t="str">
+        <x:v>CA-052.08</x:v>
+      </x:c>
+      <x:c r="B46" s="7" t="str">
+        <x:v>White不安全休息表面拒绝验收</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="str">
+        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="str">
+        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
         <x:v>表面安全测试与限制</x:v>
       </x:c>
-      <x:c r="H44" s="16" t="str"/>
-    </x:row>
-    <x:row r="45" ht="92" customHeight="1">
-      <x:c r="A45" s="7" t="str">
+      <x:c r="H46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="92" customHeight="1">
+      <x:c r="A47" s="7" t="str">
         <x:v>CA-053.06</x:v>
       </x:c>
-      <x:c r="B45" s="7" t="str">
+      <x:c r="B47" s="7" t="str">
         <x:v>White完整体力循环与座位异常验收</x:v>
       </x:c>
-      <x:c r="C45" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D45" s="7" t="str">
+      <x:c r="C47" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="str">
         <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
       </x:c>
-      <x:c r="E45" s="7" t="str">
-        <x:v>临时测试角色已清理，后续唯一White续行另见CA-053.09。</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G45" s="7" t="str">
+      <x:c r="E47" s="7" t="str">
+        <x:v>保留该阶段临时角色验收；最新150人休息抽查2人通过、1人超时，见CA-072.05。</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
         <x:v>qa_stamina_result与最终交付</x:v>
-      </x:c>
-      <x:c r="H45" s="16" t="str"/>
-    </x:row>
-    <x:row r="46" ht="92" customHeight="1">
-      <x:c r="A46" s="7" t="str">
-        <x:v>CA-053.09</x:v>
-      </x:c>
-      <x:c r="B46" s="7" t="str">
-        <x:v>唯一White十二条跨校园实走验收</x:v>
-      </x:c>
-      <x:c r="C46" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D46" s="7" t="str">
-        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
-      </x:c>
-      <x:c r="E46" s="7" t="str">
-        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G46" s="7" t="str">
-        <x:v>suite_result与final_result</x:v>
-      </x:c>
-      <x:c r="H46" s="16" t="str"/>
-    </x:row>
-    <x:row r="47" ht="75" customHeight="1">
-      <x:c r="A47" s="7" t="str">
-        <x:v>CA-053.10</x:v>
-      </x:c>
-      <x:c r="B47" s="7" t="str">
-        <x:v>White全校园随机选点覆盖抽样</x:v>
-      </x:c>
-      <x:c r="C47" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D47" s="7" t="str">
-        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
-      </x:c>
-      <x:c r="E47" s="7" t="str">
-        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G47" s="7" t="str">
-        <x:v>final_result随机覆盖与解释</x:v>
       </x:c>
       <x:c r="H47" s="16" t="str"/>
     </x:row>
     <x:row r="48" ht="92" customHeight="1">
       <x:c r="A48" s="7" t="str">
-        <x:v>CA-054.02</x:v>
+        <x:v>CA-053.09</x:v>
       </x:c>
       <x:c r="B48" s="7" t="str">
-        <x:v>唯一White与观察入口阶段运行验收</x:v>
+        <x:v>唯一White十二条跨校园实走验收</x:v>
       </x:c>
       <x:c r="C48" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D48" s="7" t="str">
-        <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
+        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
       </x:c>
       <x:c r="E48" s="7" t="str">
-        <x:v>当前入口运行检查见CA-055；单White指学生实例，不把玩家角色误算为新增学生。</x:v>
+        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
       </x:c>
       <x:c r="F48" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G48" s="7" t="str">
-        <x:v>原观察验证与后续第一人称运行结果</x:v>
+        <x:v>suite_result与final_result</x:v>
       </x:c>
       <x:c r="H48" s="16" t="str"/>
     </x:row>
-    <x:row r="49" ht="109" customHeight="1">
+    <x:row r="49" ht="75" customHeight="1">
       <x:c r="A49" s="7" t="str">
-        <x:v>CA-055</x:v>
+        <x:v>CA-053.10</x:v>
       </x:c>
       <x:c r="B49" s="7" t="str">
-        <x:v>第一人称默认出生与十五项运行验收</x:v>
+        <x:v>White全校园随机选点覆盖抽样</x:v>
       </x:c>
       <x:c r="C49" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D49" s="7" t="str">
-        <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
+        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
       </x:c>
       <x:c r="E49" s="7" t="str">
-        <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
+        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
       </x:c>
       <x:c r="F49" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G49" s="7" t="str">
-        <x:v>startup_runtime_report与新包画面</x:v>
+        <x:v>final_result随机覆盖与解释</x:v>
       </x:c>
       <x:c r="H49" s="16" t="str"/>
     </x:row>
-    <x:row r="50" ht="75" customHeight="1">
+    <x:row r="50" ht="92" customHeight="1">
       <x:c r="A50" s="7" t="str">
-        <x:v>CA-056.02</x:v>
+        <x:v>CA-054.02</x:v>
       </x:c>
       <x:c r="B50" s="7" t="str">
-        <x:v>高三楼门三百二十八项运行验收</x:v>
+        <x:v>唯一White与观察入口阶段运行验收</x:v>
       </x:c>
       <x:c r="C50" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D50" s="7" t="str">
-        <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
+        <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
       </x:c>
       <x:c r="E50" s="7" t="str">
-        <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
+        <x:v>本项保留人数精简和观察入口阶段验收；当前学生人数见CA-002、第一人称入口见CA-055。</x:v>
       </x:c>
       <x:c r="F50" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G50" s="7" t="str">
-        <x:v>runtime_verification与completion</x:v>
+        <x:v>原观察验证与后续第一人称运行结果</x:v>
       </x:c>
       <x:c r="H50" s="16" t="str"/>
     </x:row>
-    <x:row r="51" ht="58" customHeight="1">
+    <x:row r="51" ht="109" customHeight="1">
       <x:c r="A51" s="7" t="str">
-        <x:v>CA-056.03</x:v>
+        <x:v>CA-055</x:v>
       </x:c>
       <x:c r="B51" s="7" t="str">
-        <x:v>高三门保存回读与原门保护验收</x:v>
+        <x:v>第一人称默认出生与十五项运行验收</x:v>
       </x:c>
       <x:c r="C51" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D51" s="7" t="str">
-        <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
+        <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
       </x:c>
       <x:c r="E51" s="7" t="str">
-        <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
+        <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
       </x:c>
       <x:c r="F51" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G51" s="7" t="str">
-        <x:v>persisted_verification</x:v>
+        <x:v>startup_runtime_report与新包画面</x:v>
       </x:c>
       <x:c r="H51" s="16" t="str"/>
     </x:row>
     <x:row r="52" ht="75" customHeight="1">
       <x:c r="A52" s="7" t="str">
-        <x:v>CA-057.04</x:v>
+        <x:v>CA-056.02</x:v>
       </x:c>
       <x:c r="B52" s="7" t="str">
-        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
+        <x:v>高三楼门三百二十八项运行验收</x:v>
       </x:c>
       <x:c r="C52" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D52" s="7" t="str">
-        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
+        <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
       </x:c>
       <x:c r="E52" s="7" t="str">
-        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
+        <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
       </x:c>
       <x:c r="F52" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G52" s="7" t="str">
-        <x:v>V2 verification</x:v>
+        <x:v>runtime_verification与completion</x:v>
       </x:c>
       <x:c r="H52" s="16" t="str"/>
     </x:row>
-    <x:row r="53" ht="75" customHeight="1">
+    <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" s="7" t="str">
-        <x:v>CA-058.03</x:v>
+        <x:v>CA-056.03</x:v>
       </x:c>
       <x:c r="B53" s="7" t="str">
-        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
+        <x:v>高三门保存回读与原门保护验收</x:v>
       </x:c>
       <x:c r="C53" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D53" s="7" t="str">
-        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
+        <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
       </x:c>
       <x:c r="E53" s="7" t="str">
-        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
+        <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
       </x:c>
       <x:c r="F53" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G53" s="7" t="str">
-        <x:v>遮阳棚verification</x:v>
+        <x:v>persisted_verification</x:v>
       </x:c>
       <x:c r="H53" s="16" t="str"/>
     </x:row>
-    <x:row r="54" ht="58" customHeight="1">
+    <x:row r="54" ht="75" customHeight="1">
       <x:c r="A54" s="7" t="str">
-        <x:v>CA-059.03</x:v>
+        <x:v>CA-057.04</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
-        <x:v>棕榈落地树干碰撞与通道检查</x:v>
+        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
       </x:c>
       <x:c r="C54" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D54" s="7" t="str">
-        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
+        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
       </x:c>
       <x:c r="E54" s="7" t="str">
-        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
+        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
       </x:c>
       <x:c r="F54" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G54" s="7" t="str">
-        <x:v>palms_verification</x:v>
+        <x:v>V2 verification</x:v>
       </x:c>
       <x:c r="H54" s="16" t="str"/>
     </x:row>
     <x:row r="55" ht="75" customHeight="1">
       <x:c r="A55" s="7" t="str">
-        <x:v>CA-060.03</x:v>
+        <x:v>CA-058.03</x:v>
       </x:c>
       <x:c r="B55" s="7" t="str">
-        <x:v>校训朝向字距屋顶贴合检查</x:v>
+        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
       </x:c>
       <x:c r="C55" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D55" s="7" t="str">
-        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
+        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
       </x:c>
       <x:c r="E55" s="7" t="str">
-        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
+        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
       </x:c>
       <x:c r="F55" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G55" s="7" t="str">
-        <x:v>verification与final_save</x:v>
+        <x:v>遮阳棚verification</x:v>
       </x:c>
       <x:c r="H55" s="16" t="str"/>
     </x:row>
-    <x:row r="56" ht="75" customHeight="1">
+    <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" s="7" t="str">
-        <x:v>CA-061.02</x:v>
+        <x:v>CA-059.03</x:v>
       </x:c>
       <x:c r="B56" s="7" t="str">
-        <x:v>大纲整理场景属性与实例保护验收</x:v>
+        <x:v>棕榈落地树干碰撞与通道检查</x:v>
       </x:c>
       <x:c r="C56" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D56" s="7" t="str">
-        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
       </x:c>
       <x:c r="E56" s="7" t="str">
-        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
       </x:c>
       <x:c r="F56" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G56" s="7" t="str">
-        <x:v>大纲verification</x:v>
+        <x:v>palms_verification</x:v>
       </x:c>
       <x:c r="H56" s="16" t="str"/>
     </x:row>
     <x:row r="57" ht="75" customHeight="1">
       <x:c r="A57" s="7" t="str">
-        <x:v>CA-063.05</x:v>
+        <x:v>CA-060.03</x:v>
       </x:c>
       <x:c r="B57" s="7" t="str">
-        <x:v>参考夜景保存与模拟运行检查</x:v>
+        <x:v>校训朝向字距屋顶贴合检查</x:v>
       </x:c>
       <x:c r="C57" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D57" s="7" t="str">
-        <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
+        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
       </x:c>
       <x:c r="E57" s="7" t="str">
-        <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
+        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
       </x:c>
       <x:c r="F57" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G57" s="7" t="str">
+        <x:v>verification与final_save</x:v>
+      </x:c>
+      <x:c r="H57" s="16" t="str"/>
+    </x:row>
+    <x:row r="58" ht="75" customHeight="1">
+      <x:c r="A58" s="7" t="str">
+        <x:v>CA-061.02</x:v>
+      </x:c>
+      <x:c r="B58" s="7" t="str">
+        <x:v>大纲整理场景属性与实例保护验收</x:v>
+      </x:c>
+      <x:c r="C58" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D58" s="7" t="str">
+        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="str">
+        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G58" s="7" t="str">
+        <x:v>大纲verification</x:v>
+      </x:c>
+      <x:c r="H58" s="16" t="str"/>
+    </x:row>
+    <x:row r="59" ht="75" customHeight="1">
+      <x:c r="A59" s="7" t="str">
+        <x:v>CA-063.05</x:v>
+      </x:c>
+      <x:c r="B59" s="7" t="str">
+        <x:v>参考夜景保存与模拟运行检查</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="str">
+        <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="str">
+        <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
         <x:v>final_verified与runtime_verified</x:v>
       </x:c>
-      <x:c r="H57" s="16" t="str"/>
-    </x:row>
-    <x:row r="58" ht="92" customHeight="1">
-      <x:c r="A58" s="7" t="str">
+      <x:c r="H59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="92" customHeight="1">
+      <x:c r="A60" s="7" t="str">
         <x:v>CA-064.07</x:v>
       </x:c>
-      <x:c r="B58" s="7" t="str">
+      <x:c r="B60" s="7" t="str">
         <x:v>三轮昼夜切换原夜景参数还原</x:v>
       </x:c>
-      <x:c r="C58" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D58" s="7" t="str">
+      <x:c r="C60" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="str">
         <x:v>初版三轮昼夜300灯精确还原保留。最新黄昏检查17:00至22:00各阶段，22:00全部300灯恢复原亮度，night_restored_exactly=true；正午零灯规则仍通过。</x:v>
       </x:c>
-      <x:c r="E58" s="7" t="str">
+      <x:c r="E60" s="7" t="str">
         <x:v>原夜空已因月升月落按用户要求修改，不再声称当前夜空shader与旧版完全一致；只认定各阶段参数验收。</x:v>
-      </x:c>
-      <x:c r="F58" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G58" s="7" t="str">
-        <x:v>Daylight scene_verified三轮结果</x:v>
-      </x:c>
-      <x:c r="H58" s="16" t="str"/>
-    </x:row>
-    <x:row r="59" ht="92" customHeight="1">
-      <x:c r="A59" s="7" t="str">
-        <x:v>CA-064.08</x:v>
-      </x:c>
-      <x:c r="B59" s="7" t="str">
-        <x:v>当前昼夜十六项自动化环境回归</x:v>
-      </x:c>
-      <x:c r="C59" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D59" s="7" t="str">
-        <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
-      </x:c>
-      <x:c r="E59" s="7" t="str">
-        <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
-      </x:c>
-      <x:c r="F59" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G59" s="7" t="str">
-        <x:v>最新自动化index与最终聊天</x:v>
-      </x:c>
-      <x:c r="H59" s="16" t="str"/>
-    </x:row>
-    <x:row r="60" ht="109" customHeight="1">
-      <x:c r="A60" s="7" t="str">
-        <x:v>CA-065.03</x:v>
-      </x:c>
-      <x:c r="B60" s="7" t="str">
-        <x:v>一键脚本原工程完整构建交付</x:v>
-      </x:c>
-      <x:c r="C60" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D60" s="7" t="str">
-        <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
-      </x:c>
-      <x:c r="E60" s="7" t="str">
-        <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
       </x:c>
       <x:c r="F60" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G60" s="7" t="str">
-        <x:v>ScenePackages build-info实际成功记录</x:v>
+        <x:v>Daylight scene_verified三轮结果</x:v>
       </x:c>
       <x:c r="H60" s="16" t="str"/>
     </x:row>
     <x:row r="61" ht="92" customHeight="1">
       <x:c r="A61" s="7" t="str">
-        <x:v>CA-066.02</x:v>
+        <x:v>CA-064.08</x:v>
       </x:c>
       <x:c r="B61" s="7" t="str">
-        <x:v>时间面板调时暂停与保存基准检查</x:v>
+        <x:v>当前昼夜十六项自动化环境回归</x:v>
       </x:c>
       <x:c r="C61" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D61" s="7" t="str">
-        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
+        <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
       </x:c>
       <x:c r="E61" s="7" t="str">
-        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
+        <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
       </x:c>
       <x:c r="F61" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G61" s="7" t="str">
-        <x:v>面板实操及夜景恢复检查</x:v>
+        <x:v>最新自动化index与最终聊天</x:v>
       </x:c>
       <x:c r="H61" s="16" t="str"/>
     </x:row>
-    <x:row r="62" ht="75" customHeight="1">
+    <x:row r="62" ht="109" customHeight="1">
       <x:c r="A62" s="7" t="str">
-        <x:v>CA-068.02</x:v>
+        <x:v>CA-065.03</x:v>
       </x:c>
       <x:c r="B62" s="7" t="str">
-        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
+        <x:v>一键脚本原工程完整构建交付</x:v>
       </x:c>
       <x:c r="C62" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D62" s="7" t="str">
-        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
+        <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
       </x:c>
       <x:c r="E62" s="7" t="str">
-        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
+        <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
       </x:c>
       <x:c r="F62" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G62" s="7" t="str">
-        <x:v>月亮运行796帧与重载报告</x:v>
+        <x:v>ScenePackages build-info实际成功记录</x:v>
       </x:c>
       <x:c r="H62" s="16" t="str"/>
     </x:row>
-    <x:row r="63" ht="75" customHeight="1">
+    <x:row r="63" ht="92" customHeight="1">
       <x:c r="A63" s="7" t="str">
-        <x:v>CA-070.04</x:v>
+        <x:v>CA-066.02</x:v>
       </x:c>
       <x:c r="B63" s="7" t="str">
-        <x:v>教学楼材质合批镜像与门结构保持</x:v>
+        <x:v>时间面板调时暂停与保存基准检查</x:v>
       </x:c>
       <x:c r="C63" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D63" s="7" t="str">
-        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
+        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
       </x:c>
       <x:c r="E63" s="7" t="str">
-        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
+        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
       </x:c>
       <x:c r="F63" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G63" s="7" t="str">
+        <x:v>面板实操及夜景恢复检查</x:v>
+      </x:c>
+      <x:c r="H63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="75" customHeight="1">
+      <x:c r="A64" s="7" t="str">
+        <x:v>CA-068.02</x:v>
+      </x:c>
+      <x:c r="B64" s="7" t="str">
+        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
+      </x:c>
+      <x:c r="C64" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="str">
+        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="str">
+        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
+        <x:v>月亮运行796帧与重载报告</x:v>
+      </x:c>
+      <x:c r="H64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65" ht="75" customHeight="1">
+      <x:c r="A65" s="7" t="str">
+        <x:v>CA-070.04</x:v>
+      </x:c>
+      <x:c r="B65" s="7" t="str">
+        <x:v>教学楼材质合批镜像与门结构保持</x:v>
+      </x:c>
+      <x:c r="C65" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="str">
+        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="str">
+        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G65" s="7" t="str">
         <x:v>真实材质与纯色门结构验证</x:v>
       </x:c>
-      <x:c r="H63" s="16" t="str"/>
-    </x:row>
-    <x:row r="64" ht="92" customHeight="1">
-      <x:c r="A64" s="7" t="str">
+      <x:c r="H65" s="16" t="str"/>
+    </x:row>
+    <x:row r="66" ht="92" customHeight="1">
+      <x:c r="A66" s="7" t="str">
         <x:v>CA-071.05</x:v>
       </x:c>
-      <x:c r="B64" s="7" t="str">
+      <x:c r="B66" s="7" t="str">
         <x:v>草地全量朝向坐标材质及保存检查</x:v>
       </x:c>
-      <x:c r="C64" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D64" s="7" t="str">
+      <x:c r="C66" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="str">
         <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
       </x:c>
-      <x:c r="E64" s="7" t="str">
+      <x:c r="E66" s="7" t="str">
         <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
       </x:c>
-      <x:c r="F64" s="14" t="n">
+      <x:c r="F66" s="14" t="n">
         <x:v>46301</x:v>
       </x:c>
-      <x:c r="G64" s="7" t="str">
+      <x:c r="G66" s="7" t="str">
         <x:v>草地全量检查和67秒保存回执</x:v>
       </x:c>
-      <x:c r="H64" s="16" t="str"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="1"/>
-      <x:c r="B65" s="1"/>
-      <x:c r="C65" s="1"/>
-      <x:c r="D65" s="1"/>
-      <x:c r="E65" s="1"/>
-      <x:c r="F65" s="1"/>
-      <x:c r="G65" s="1"/>
-      <x:c r="H65" s="1"/>
-    </x:row>
-    <x:row r="66" ht="34" customHeight="1">
-      <x:c r="A66" s="3" t="str">
+      <x:c r="H66" s="16" t="str"/>
+    </x:row>
+    <x:row r="67" ht="92" customHeight="1">
+      <x:c r="A67" s="7" t="str">
+        <x:v>CA-072.04</x:v>
+      </x:c>
+      <x:c r="B67" s="7" t="str">
+        <x:v>150名White运行移动与行为保留</x:v>
+      </x:c>
+      <x:c r="C67" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D67" s="7" t="str">
+        <x:v>运行全程150名White、控制器完整且导航目标非部分路径；150人全部移动并选择巡游目标，观察到体力消耗，保留设置及动画策略检查均通过。平均位移约29.81m，最小约2.80m。</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="str">
+        <x:v>完成该被动观察样本；不替代全校园逐路线、长期互相穿透和全体休息验证。</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G67" s="7" t="str">
+        <x:v>150人运行QA与最终保存确认</x:v>
+      </x:c>
+      <x:c r="H67" s="16" t="str"/>
+    </x:row>
+    <x:row r="68" ht="92" customHeight="1">
+      <x:c r="A68" s="7" t="str">
+        <x:v>CA-073.07</x:v>
+      </x:c>
+      <x:c r="B68" s="7" t="str">
+        <x:v>天气昼夜屋顶与停雨运行检查</x:v>
+      </x:c>
+      <x:c r="C68" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D68" s="7" t="str">
+        <x:v>正午阴天、正午降雨、夜间降雨、停雨4阶段运行errors为空、passed=true；停雨仍湿润后渐干，屋顶与室外304帧检查通过，材质重载无绑定错误。</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="str">
+        <x:v>屋顶边缘未全量检查；此项不等于发布包全路线实测。</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G68" s="7" t="str">
+        <x:v>天气运行和宽屋顶验证范围</x:v>
+      </x:c>
+      <x:c r="H68" s="16" t="str"/>
+    </x:row>
+    <x:row r="69" ht="92" customHeight="1">
+      <x:c r="A69" s="7" t="str">
+        <x:v>CA-073.08</x:v>
+      </x:c>
+      <x:c r="B69" s="7" t="str">
+        <x:v>最终阴雨调度及昼夜自动化回归</x:v>
+      </x:c>
+      <x:c r="C69" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D69" s="7" t="str">
+        <x:v>最终编译成功，最新自动化24项通过、0失败、0警告、0未运行；覆盖随机时长上限、中途反向、材质参数连续和昼夜联动。初版20项仅保留阶段依据。</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="str">
+        <x:v>测试不等于实际连续运行30分钟；随机时长上限已有多组参数自动化验证。</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G69" s="7" t="str">
+        <x:v>最终Automation报告24通过0失败</x:v>
+      </x:c>
+      <x:c r="H69" s="16" t="str"/>
+    </x:row>
+    <x:row r="70" ht="92" customHeight="1">
+      <x:c r="A70" s="7" t="str">
+        <x:v>CA-073.09</x:v>
+      </x:c>
+      <x:c r="B70" s="7" t="str">
+        <x:v>天气按钮点击与完整渐变播放</x:v>
+      </x:c>
+      <x:c r="C70" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D70" s="7" t="str">
+        <x:v>实际点击后的雨量、云层、湿度连续变化，最终点击报告passed=true，保存时长30秒，观测约38.2秒至过渡完成；详情切换反向、恢复及重启预览检查errors为空。</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="str">
+        <x:v>编辑器预览已验；Shipping按钮适用范围与成品运行另按版本判断。</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G70" s="7" t="str">
+        <x:v>按钮点击、反向及最终预览状态</x:v>
+      </x:c>
+      <x:c r="H70" s="16" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="1"/>
+      <x:c r="B71" s="1"/>
+      <x:c r="C71" s="1"/>
+      <x:c r="D71" s="1"/>
+      <x:c r="E71" s="1"/>
+      <x:c r="F71" s="1"/>
+      <x:c r="G71" s="1"/>
+      <x:c r="H71" s="1"/>
+    </x:row>
+    <x:row r="72" ht="34" customHeight="1">
+      <x:c r="A72" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B66" s="21" t="str">
+      <x:c r="B72" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C66" s="21"/>
-      <x:c r="D66" s="21"/>
-      <x:c r="E66" s="21"/>
-      <x:c r="F66" s="21"/>
-      <x:c r="G66" s="21"/>
-      <x:c r="H66" s="21"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="1"/>
-      <x:c r="B67" s="1"/>
-      <x:c r="C67" s="1"/>
-      <x:c r="D67" s="1"/>
-      <x:c r="E67" s="1"/>
-      <x:c r="F67" s="1"/>
-      <x:c r="G67" s="1"/>
-      <x:c r="H67" s="1"/>
+      <x:c r="C72" s="21"/>
+      <x:c r="D72" s="21"/>
+      <x:c r="E72" s="21"/>
+      <x:c r="F72" s="21"/>
+      <x:c r="G72" s="21"/>
+      <x:c r="H72" s="21"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="1"/>
+      <x:c r="B73" s="1"/>
+      <x:c r="C73" s="1"/>
+      <x:c r="D73" s="1"/>
+      <x:c r="E73" s="1"/>
+      <x:c r="F73" s="1"/>
+      <x:c r="G73" s="1"/>
+      <x:c r="H73" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B66:H66"/>
+    <x:mergeCell ref="B72:H72"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C64">
+  <x:conditionalFormatting sqref="C8:C70">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1940,13 +2084,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C64">
+    <x:dataValidation type="list" sqref="C8:C70">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31f6c9cc469a463d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a0d206cc1894ca4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="Re7609947bcd648c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R44f47bae12a6419f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -192,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H70"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H80"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +470,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C70,A5)</x:f>
-        <x:v>50</x:v>
+        <x:f>COUNTIF(C8:C80,A5)</x:f>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C70,D5)</x:f>
+        <x:f>COUNTIF(C8:C80,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C70,F5)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF(C8:C80,F5)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -536,8 +542,8 @@
       <x:c r="E8" s="7" t="str">
         <x:v>确认独立 Man 动作库是否仍属于当前验收范围；不能用男学生 Walk、Idle 通过结果代替它的确认。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>46282</x:v>
+      <x:c r="F8" s="14" t="d">
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
         <x:v>独立 Man 历史 QA 对象与范围</x:v>
@@ -560,8 +566,8 @@
       <x:c r="E9" s="7" t="str">
         <x:v>按所需全校范围核对未覆盖实例；高三门开关验收与29个厕位门洞不可通行分别见CA-056系列。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F9" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>高三门新增验收与第一人称恢复</x:v>
@@ -584,8 +590,8 @@
       <x:c r="E10" s="7" t="str">
         <x:v>按当前第一人称交付版本与所需路线判断全场回归；局部运行通过不能代替所有区域覆盖。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F10" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>新增第一人称局部回归与历史跨楼路线</x:v>
@@ -608,8 +614,8 @@
       <x:c r="E11" s="7" t="str">
         <x:v>确认是否补做行政庭院的真实角色通行验收；地面点检查不能作为角色行走通过依据。</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46290</x:v>
+      <x:c r="F11" s="14" t="d">
+        <x:v>2026-09-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
         <x:v>行政庭院完成记录明确保留的验收边界</x:v>
@@ -632,8 +638,8 @@
       <x:c r="E12" s="7" t="str">
         <x:v>确认是否补做简单碰撞及角色路线验收；按实际通口检查衔接。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
-        <x:v>46287</x:v>
+      <x:c r="F12" s="14" t="d">
+        <x:v>2026-09-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>道路完成记录与碰撞分析的验收边界</x:v>
@@ -656,8 +662,8 @@
       <x:c r="E13" s="7" t="str">
         <x:v>确认旧服装分支是否仍属当前交付范围；若弃用可关闭此缺口，若继续使用则须核对 Morph Targets 和驱动，不能把它列为当前新校服损坏。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>46294</x:v>
+      <x:c r="F13" s="14" t="d">
+        <x:v>2026-09-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>旧服装说明的 UE 边界与最新 White 换装来源区别</x:v>
@@ -680,8 +686,8 @@
       <x:c r="E14" s="7" t="str">
         <x:v>真实显示帧率和严格原生 1080p 尚无直接证据，需对应环境测量再判定；不把应用 FPS 当屏幕 FPS。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F14" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>Shipping 报告第 1、3 节测量输入及显示链路限制</x:v>
@@ -704,8 +710,8 @@
       <x:c r="E15" s="7" t="str">
         <x:v>确认是否已有角色实走记录；仅凭16处地面采样不能认定角色全路线通过。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F15" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
         <x:v>景观聊天与 validation 当前验收边界</x:v>
@@ -728,8 +734,8 @@
       <x:c r="E16" s="7" t="str">
         <x:v>需确认可见差异的后续处理或接受范围；现有交付不能作为严格一比一验收。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F16" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>景观最终结果与 completion fidelity_note</x:v>
@@ -752,8 +758,8 @@
       <x:c r="E17" s="7" t="str">
         <x:v>确认当前交付所需手柄回归范围；缺同版本实体手柄/Y门交互证据，不再追问已替代的观察摄像机映射。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F17" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>第一人称恢复及输入验证明确边界</x:v>
@@ -776,8 +782,8 @@
       <x:c r="E18" s="7" t="str">
         <x:v>确认是否接受当前细节差异，或决定后续对齐范围。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
         <x:v>夜景最终聊天明确限制</x:v>
@@ -795,16 +801,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>10月5日5批构建及10月6日10:08、11:07、17:54成品均有succeeded记录；未找到这些具体包的启动画面、响应、退出或玩法验收。150人和天气编辑器运行通过不能替代Shipping实测。</x:v>
+        <x:v>已知10月5日5批、10月6日3批及10月9日00:03共9批Shipping构建成功。最新包包含此前开关和晴雨修订的构建时序证据，但早于食堂写实改造；仍未发现这些具体包的启动、响应、退出或玩法运行验收。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>按具体发布包核对运行记录；最新已构建150人和天气，仍缺对应成品实机验收，不由追踪任务启动游戏。</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>按具体包核对实机记录；最新食堂改造未由00:03包覆盖，编辑器预览与自动化不能替代成品验收。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>新增三批build-info及聊天运行范围</x:v>
+        <x:v>新增Shipping成功及最新实现先后范围</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
@@ -824,8 +830,8 @@
       <x:c r="E20" s="7" t="str">
         <x:v>需确认该座位限制是否接受或另有后续通过记录；2人通过不能替代第3人的关闭证据。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F20" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>最终交付明确2通过1超时</x:v>
@@ -834,1245 +840,1485 @@
     </x:row>
     <x:row r="21" ht="92" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>CA-001.07</x:v>
+        <x:v>CA-075.06</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>White 换装后 30 人运行与保存验收</x:v>
-      </x:c>
-      <x:c r="C21" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>雨天参考图严格一比一验收</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
+        <x:v>雨景主要氛围、动态云、涟漪和暖光已保存，但最终答复明确光照与材质细节仍有差异，尚未达到严格一比一。后续晴空恢复没有关闭该差异。</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46296</x:v>
+        <x:v>需确认可接受的差异或后续对齐结果；不把实现保存计作整体一比一验收。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
+        <x:v>雨景最终答复明确未达到严格一比一</x:v>
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
-    <x:row r="22" ht="92" customHeight="1">
+    <x:row r="22" ht="75" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>CA-006.05</x:v>
+        <x:v>CA-076.10</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
-      </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>食堂广场参考照片严格还原验收</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
+        <x:v>最终交付明确只是参考风格材质与光照改造：树冠叶片与树干、玻璃反射、建筑内部细节仍有差异，前景学生未复现，未达照片级1:1。</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>需确认可接受范围或后续对齐交付；不能用810处材质绑定通过关闭整体还原验收。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
+        <x:v>最终聊天和DELIVERY还原范围</x:v>
       </x:c>
       <x:c r="H22" s="16" t="str"/>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-076.11</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>食堂新材质后的完整昼夜晴雨回归</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>本轮源说明保留昼夜天气接口，final_preview只记录10:30晴天四个天气参数归零。10月8日四组合与27测试早于10月9日新材质保存，尚无新绑定版本雨景、夜景与往返恢复记录。</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>核对新材质同版本的昼夜晴雨回归或接受范围；不由追踪任务启动编辑器验证。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>final_preview与先后版本范围对照</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
-    <x:row r="24" ht="75" customHeight="1">
+    <x:row r="24" ht="92" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-001.07</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+        <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
       <x:c r="C24" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46293</x:v>
+        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>CA-015.02</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>教学楼 A B 一至四层往返验收</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>CA-016.02</x:v>
+        <x:v>CA-006.06</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
     <x:row r="27" ht="75" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>CA-017.03</x:v>
+        <x:v>CA-014.04</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
       </x:c>
       <x:c r="C27" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="n">
-        <x:v>46291</x:v>
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+        <x:v>综合楼运行与逐级踏步验收记录</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>CA-019.03</x:v>
+        <x:v>CA-015.02</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
+        <x:v>教学楼 A B 一至四层往返验收</x:v>
       </x:c>
       <x:c r="C28" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
+        <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
-        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="n">
-        <x:v>46289</x:v>
+        <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
-        <x:v>礼堂最终验证及完整重启复核</x:v>
+        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H28" s="16" t="str"/>
     </x:row>
     <x:row r="29" ht="92" customHeight="1">
       <x:c r="A29" s="7" t="str">
+        <x:v>CA-016.02</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="str">
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
+      <x:c r="A30" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+      </x:c>
+      <x:c r="H30" s="16" t="str"/>
+    </x:row>
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="7" t="str">
+        <x:v>CA-019.03</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="d">
+        <x:v>2026-09-24T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>礼堂最终验证及完整重启复核</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="92" customHeight="1">
+      <x:c r="A32" s="7" t="str">
         <x:v>CA-020.02</x:v>
       </x:c>
-      <x:c r="B29" s="7" t="str">
+      <x:c r="B32" s="7" t="str">
         <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
       </x:c>
-      <x:c r="C29" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
         <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="str">
+      <x:c r="E32" s="7" t="str">
         <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="n">
-        <x:v>46289</x:v>
-      </x:c>
-      <x:c r="G29" s="7" t="str">
+      <x:c r="F32" s="14" t="d">
+        <x:v>2026-09-24T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H29" s="16" t="str"/>
-    </x:row>
-    <x:row r="30" ht="109" customHeight="1">
-      <x:c r="A30" s="7" t="str">
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="109" customHeight="1">
+      <x:c r="A33" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B30" s="7" t="str">
+      <x:c r="B33" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C30" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="str">
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="str">
+      <x:c r="E33" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="n">
-        <x:v>46287</x:v>
-      </x:c>
-      <x:c r="G30" s="7" t="str">
+      <x:c r="F33" s="14" t="d">
+        <x:v>2026-09-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
-      </x:c>
-      <x:c r="H30" s="16" t="str"/>
-    </x:row>
-    <x:row r="31" ht="92" customHeight="1">
-      <x:c r="A31" s="7" t="str">
-        <x:v>CA-030.02</x:v>
-      </x:c>
-      <x:c r="B31" s="7" t="str">
-        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
-      </x:c>
-      <x:c r="C31" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D31" s="7" t="str">
-        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
-      </x:c>
-      <x:c r="E31" s="7" t="str">
-        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G31" s="7" t="str">
-        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
-      </x:c>
-      <x:c r="H31" s="16" t="str"/>
-    </x:row>
-    <x:row r="32" ht="92" customHeight="1">
-      <x:c r="A32" s="7" t="str">
-        <x:v>CA-031.02</x:v>
-      </x:c>
-      <x:c r="B32" s="7" t="str">
-        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
-      </x:c>
-      <x:c r="C32" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D32" s="7" t="str">
-        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
-      </x:c>
-      <x:c r="E32" s="7" t="str">
-        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="n">
-        <x:v>46291</x:v>
-      </x:c>
-      <x:c r="G32" s="7" t="str">
-        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
-      </x:c>
-      <x:c r="H32" s="16" t="str"/>
-    </x:row>
-    <x:row r="33" ht="92" customHeight="1">
-      <x:c r="A33" s="7" t="str">
-        <x:v>CA-033.02</x:v>
-      </x:c>
-      <x:c r="B33" s="7" t="str">
-        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
-      </x:c>
-      <x:c r="C33" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D33" s="7" t="str">
-        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
-      </x:c>
-      <x:c r="E33" s="7" t="str">
-        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G33" s="7" t="str">
-        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
       </x:c>
       <x:c r="H33" s="16" t="str"/>
     </x:row>
     <x:row r="34" ht="92" customHeight="1">
       <x:c r="A34" s="7" t="str">
+        <x:v>CA-030.02</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
+      </x:c>
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="92" customHeight="1">
+      <x:c r="A35" s="7" t="str">
+        <x:v>CA-031.02</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="str">
+        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
+        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
+      </x:c>
+      <x:c r="H35" s="16" t="str"/>
+    </x:row>
+    <x:row r="36" ht="92" customHeight="1">
+      <x:c r="A36" s="7" t="str">
+        <x:v>CA-033.02</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="str">
+        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D36" s="7" t="str">
+        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="str">
+        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="str">
+        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+      </x:c>
+      <x:c r="H36" s="16" t="str"/>
+    </x:row>
+    <x:row r="37" ht="92" customHeight="1">
+      <x:c r="A37" s="7" t="str">
         <x:v>CA-035.02</x:v>
       </x:c>
-      <x:c r="B34" s="7" t="str">
+      <x:c r="B37" s="7" t="str">
         <x:v>White 打开关卡与退出运行复发验收</x:v>
       </x:c>
-      <x:c r="C34" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D34" s="7" t="str">
+      <x:c r="C37" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="str">
         <x:v>map_opened 与 end_pie 均实际触发 refreshed：count=matched=30、skipped=0、positions_preserved=true；聊天最终确认重新打开及停止运行后正常站立。</x:v>
       </x:c>
-      <x:c r="E34" s="7" t="str">
+      <x:c r="E37" s="7" t="str">
         <x:v>本次覆盖保存、打开关卡与退出运行复发条件；未来初始化逻辑变化后按该范围回归。</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="n">
-        <x:v>46296</x:v>
-      </x:c>
-      <x:c r="G34" s="7" t="str">
+      <x:c r="F37" s="14" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
         <x:v>map_hook_verified、end_pie_verified 及最终截图交付</x:v>
       </x:c>
-      <x:c r="H34" s="16" t="str"/>
-    </x:row>
-    <x:row r="35" ht="109" customHeight="1">
-      <x:c r="A35" s="7" t="str">
+      <x:c r="H37" s="16" t="str"/>
+    </x:row>
+    <x:row r="38" ht="109" customHeight="1">
+      <x:c r="A38" s="7" t="str">
         <x:v>CA-038.02</x:v>
       </x:c>
-      <x:c r="B35" s="7" t="str">
+      <x:c r="B38" s="7" t="str">
         <x:v>scene 标准 Shipping 发布构建验收</x:v>
       </x:c>
-      <x:c r="C35" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="str">
+      <x:c r="C38" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="str">
         <x:v>保留10月3日副本完整发布及用户验收。10月4日原工程Win64 Shipping完整构建退出0，第一人称包D3D12启动响应、实际画面及退出0通过。10月5日脚本build-info再次succeeded，但该包运行验收独立见CA-065.04。</x:v>
       </x:c>
-      <x:c r="E35" s="7" t="str">
+      <x:c r="E38" s="7" t="str">
         <x:v>阶段构建验收已完成；新脚本包运行与最新白天修订同步分别判断。</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G35" s="7" t="str">
+      <x:c r="F38" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
         <x:v>原工程完整Shipping构建与版本化验收</x:v>
-      </x:c>
-      <x:c r="H35" s="16" t="str"/>
-    </x:row>
-    <x:row r="36" ht="75" customHeight="1">
-      <x:c r="A36" s="7" t="str">
-        <x:v>CA-040.09</x:v>
-      </x:c>
-      <x:c r="B36" s="7" t="str">
-        <x:v>综合楼后方16处地面碰撞采样</x:v>
-      </x:c>
-      <x:c r="C36" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D36" s="7" t="str">
-        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
-      </x:c>
-      <x:c r="E36" s="7" t="str">
-        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G36" s="7" t="str">
-        <x:v>validation traces 16/16 与最终交付</x:v>
-      </x:c>
-      <x:c r="H36" s="16" t="str"/>
-    </x:row>
-    <x:row r="37" ht="75" customHeight="1">
-      <x:c r="A37" s="7" t="str">
-        <x:v>CA-041.03</x:v>
-      </x:c>
-      <x:c r="B37" s="7" t="str">
-        <x:v>scene远景设置保存与前景保护验收</x:v>
-      </x:c>
-      <x:c r="C37" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D37" s="7" t="str">
-        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
-      </x:c>
-      <x:c r="E37" s="7" t="str">
-        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G37" s="7" t="str">
-        <x:v>verification 设置保存与前景、源资产校验</x:v>
-      </x:c>
-      <x:c r="H37" s="16" t="str"/>
-    </x:row>
-    <x:row r="38" ht="92" customHeight="1">
-      <x:c r="A38" s="7" t="str">
-        <x:v>CA-043.05</x:v>
-      </x:c>
-      <x:c r="B38" s="7" t="str">
-        <x:v>校园风动保存与实例合批完整性</x:v>
-      </x:c>
-      <x:c r="C38" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D38" s="7" t="str">
-        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
-      </x:c>
-      <x:c r="E38" s="7" t="str">
-        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G38" s="7" t="str">
-        <x:v>风动保存回读与合批检查</x:v>
       </x:c>
       <x:c r="H38" s="16" t="str"/>
     </x:row>
     <x:row r="39" ht="75" customHeight="1">
       <x:c r="A39" s="7" t="str">
-        <x:v>CA-044.03</x:v>
+        <x:v>CA-040.09</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
-        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+        <x:v>综合楼后方16处地面碰撞采样</x:v>
       </x:c>
       <x:c r="C39" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D39" s="7" t="str">
-        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+        <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
       </x:c>
       <x:c r="E39" s="7" t="str">
-        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G39" s="7" t="str">
-        <x:v>verification_report与最终保存交付</x:v>
+        <x:v>validation traces 16/16 与最终交付</x:v>
       </x:c>
       <x:c r="H39" s="16" t="str"/>
     </x:row>
-    <x:row r="40" ht="92" customHeight="1">
+    <x:row r="40" ht="75" customHeight="1">
       <x:c r="A40" s="7" t="str">
-        <x:v>CA-045.04</x:v>
+        <x:v>CA-041.03</x:v>
       </x:c>
       <x:c r="B40" s="7" t="str">
-        <x:v>第一第三人称手柄模拟输入验收</x:v>
+        <x:v>scene远景设置保存与前景保护验收</x:v>
       </x:c>
       <x:c r="C40" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D40" s="7" t="str">
-        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
       </x:c>
       <x:c r="E40" s="7" t="str">
-        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="n">
-        <x:v>46298</x:v>
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G40" s="7" t="str">
-        <x:v>模拟输入记录与用户新版验收</x:v>
+        <x:v>verification 设置保存与前景、源资产校验</x:v>
       </x:c>
       <x:c r="H40" s="16" t="str"/>
     </x:row>
     <x:row r="41" ht="92" customHeight="1">
       <x:c r="A41" s="7" t="str">
+        <x:v>CA-043.05</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="str">
+        <x:v>校园风动保存与实例合批完整性</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="str">
+        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="str">
+        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>风动保存回读与合批检查</x:v>
+      </x:c>
+      <x:c r="H41" s="16" t="str"/>
+    </x:row>
+    <x:row r="42" ht="75" customHeight="1">
+      <x:c r="A42" s="7" t="str">
+        <x:v>CA-044.03</x:v>
+      </x:c>
+      <x:c r="B42" s="7" t="str">
+        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+      </x:c>
+      <x:c r="C42" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="str">
+        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="str">
+        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>verification_report与最终保存交付</x:v>
+      </x:c>
+      <x:c r="H42" s="16" t="str"/>
+    </x:row>
+    <x:row r="43" ht="92" customHeight="1">
+      <x:c r="A43" s="7" t="str">
+        <x:v>CA-045.04</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="str">
+        <x:v>第一第三人称手柄模拟输入验收</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="str">
+        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="str">
+        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>模拟输入记录与用户新版验收</x:v>
+      </x:c>
+      <x:c r="H43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44" ht="92" customHeight="1">
+      <x:c r="A44" s="7" t="str">
         <x:v>CA-046.05</x:v>
       </x:c>
-      <x:c r="B41" s="7" t="str">
+      <x:c r="B44" s="7" t="str">
         <x:v>150人及最终天气版本Shipping构建</x:v>
       </x:c>
-      <x:c r="C41" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D41" s="7" t="str">
+      <x:c r="C44" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="str">
         <x:v>150人10月6日10:57交付后11:00–11:07完整Shipping成功；最终天气15:40交付后17:47–17:54再构建成功，build-info指向原工程scene，exe存在。</x:v>
       </x:c>
-      <x:c r="E41" s="7" t="str">
+      <x:c r="E44" s="7" t="str">
         <x:v>构建成功不等于成品玩法、实际帧率或长时天气验收，见CA-065.04。</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="G41" s="7" t="str">
+      <x:c r="F44" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
         <x:v>后续完整构建状态与版本时序</x:v>
       </x:c>
-      <x:c r="H41" s="16" t="str"/>
-    </x:row>
-    <x:row r="42" ht="92" customHeight="1">
-      <x:c r="A42" s="7" t="str">
+      <x:c r="H44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="92" customHeight="1">
+      <x:c r="A45" s="7" t="str">
+        <x:v>CA-046.06</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="str">
+        <x:v>五栋楼开关与晴雨修订后Shipping构建</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="str">
+        <x:v>原工程scene于10月8日23:54至10月9日00:03完整Shipping构建succeeded，晚于开关和晴空恢复交付；exe路径有效。该包早于10月9日食堂写实改造。</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="str">
+        <x:v>仅确认构建时序，不能认定包含后续食堂材质；具体包实际运行见CA-065.04。</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>新build-info成功状态与交付时序</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="92" customHeight="1">
+      <x:c r="A46" s="7" t="str">
         <x:v>CA-047.03</x:v>
       </x:c>
-      <x:c r="B42" s="7" t="str">
+      <x:c r="B46" s="7" t="str">
         <x:v>食堂两侧一至二层真实往返验收</x:v>
       </x:c>
-      <x:c r="C42" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D42" s="7" t="str">
+      <x:c r="C46" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="str">
         <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
       </x:c>
-      <x:c r="E42" s="7" t="str">
+      <x:c r="E46" s="7" t="str">
         <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
       </x:c>
-      <x:c r="F42" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G42" s="7" t="str">
+      <x:c r="F46" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
         <x:v>playtest_final与White校园路线</x:v>
       </x:c>
-      <x:c r="H42" s="16" t="str"/>
-    </x:row>
-    <x:row r="43" ht="75" customHeight="1">
-      <x:c r="A43" s="7" t="str">
+      <x:c r="H46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="75" customHeight="1">
+      <x:c r="A47" s="7" t="str">
         <x:v>CA-048.02</x:v>
       </x:c>
-      <x:c r="B43" s="7" t="str">
+      <x:c r="B47" s="7" t="str">
         <x:v>行政楼植被清理重载与保留位置验收</x:v>
       </x:c>
-      <x:c r="C43" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D43" s="7" t="str">
+      <x:c r="C47" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="str">
         <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
       </x:c>
-      <x:c r="E43" s="7" t="str">
+      <x:c r="E47" s="7" t="str">
         <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
       </x:c>
-      <x:c r="F43" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G43" s="7" t="str">
+      <x:c r="F47" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
         <x:v>reload_verification与重载效果</x:v>
       </x:c>
-      <x:c r="H43" s="16" t="str"/>
-    </x:row>
-    <x:row r="44" ht="75" customHeight="1">
-      <x:c r="A44" s="7" t="str">
+      <x:c r="H47" s="16" t="str"/>
+    </x:row>
+    <x:row r="48" ht="75" customHeight="1">
+      <x:c r="A48" s="7" t="str">
         <x:v>CA-052.06</x:v>
       </x:c>
-      <x:c r="B44" s="7" t="str">
+      <x:c r="B48" s="7" t="str">
         <x:v>White十九组高度与蒙皮接触验收</x:v>
       </x:c>
-      <x:c r="C44" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D44" s="7" t="str">
+      <x:c r="C48" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="str">
         <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
       </x:c>
-      <x:c r="E44" s="7" t="str">
+      <x:c r="E48" s="7" t="str">
         <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
       </x:c>
-      <x:c r="F44" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G44" s="7" t="str">
+      <x:c r="F48" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
         <x:v>qa_final_summary高度与接触结果</x:v>
-      </x:c>
-      <x:c r="H44" s="16" t="str"/>
-    </x:row>
-    <x:row r="45" ht="75" customHeight="1">
-      <x:c r="A45" s="7" t="str">
-        <x:v>CA-052.07</x:v>
-      </x:c>
-      <x:c r="B45" s="7" t="str">
-        <x:v>White自动休息冷却与中断恢复验收</x:v>
-      </x:c>
-      <x:c r="C45" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D45" s="7" t="str">
-        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
-      </x:c>
-      <x:c r="E45" s="7" t="str">
-        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G45" s="7" t="str">
-        <x:v>qa_final_summary行为结果</x:v>
-      </x:c>
-      <x:c r="H45" s="16" t="str"/>
-    </x:row>
-    <x:row r="46" ht="75" customHeight="1">
-      <x:c r="A46" s="7" t="str">
-        <x:v>CA-052.08</x:v>
-      </x:c>
-      <x:c r="B46" s="7" t="str">
-        <x:v>White不安全休息表面拒绝验收</x:v>
-      </x:c>
-      <x:c r="C46" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D46" s="7" t="str">
-        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
-      </x:c>
-      <x:c r="E46" s="7" t="str">
-        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G46" s="7" t="str">
-        <x:v>表面安全测试与限制</x:v>
-      </x:c>
-      <x:c r="H46" s="16" t="str"/>
-    </x:row>
-    <x:row r="47" ht="92" customHeight="1">
-      <x:c r="A47" s="7" t="str">
-        <x:v>CA-053.06</x:v>
-      </x:c>
-      <x:c r="B47" s="7" t="str">
-        <x:v>White完整体力循环与座位异常验收</x:v>
-      </x:c>
-      <x:c r="C47" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D47" s="7" t="str">
-        <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
-      </x:c>
-      <x:c r="E47" s="7" t="str">
-        <x:v>保留该阶段临时角色验收；最新150人休息抽查2人通过、1人超时，见CA-072.05。</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="G47" s="7" t="str">
-        <x:v>qa_stamina_result与最终交付</x:v>
-      </x:c>
-      <x:c r="H47" s="16" t="str"/>
-    </x:row>
-    <x:row r="48" ht="92" customHeight="1">
-      <x:c r="A48" s="7" t="str">
-        <x:v>CA-053.09</x:v>
-      </x:c>
-      <x:c r="B48" s="7" t="str">
-        <x:v>唯一White十二条跨校园实走验收</x:v>
-      </x:c>
-      <x:c r="C48" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D48" s="7" t="str">
-        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
-      </x:c>
-      <x:c r="E48" s="7" t="str">
-        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
-      </x:c>
-      <x:c r="F48" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G48" s="7" t="str">
-        <x:v>suite_result与final_result</x:v>
       </x:c>
       <x:c r="H48" s="16" t="str"/>
     </x:row>
     <x:row r="49" ht="75" customHeight="1">
       <x:c r="A49" s="7" t="str">
+        <x:v>CA-052.07</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="str">
+        <x:v>White自动休息冷却与中断恢复验收</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="str">
+        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="str">
+        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>qa_final_summary行为结果</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="75" customHeight="1">
+      <x:c r="A50" s="7" t="str">
+        <x:v>CA-052.08</x:v>
+      </x:c>
+      <x:c r="B50" s="7" t="str">
+        <x:v>White不安全休息表面拒绝验收</x:v>
+      </x:c>
+      <x:c r="C50" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="str">
+        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="str">
+        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G50" s="7" t="str">
+        <x:v>表面安全测试与限制</x:v>
+      </x:c>
+      <x:c r="H50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="92" customHeight="1">
+      <x:c r="A51" s="7" t="str">
+        <x:v>CA-053.06</x:v>
+      </x:c>
+      <x:c r="B51" s="7" t="str">
+        <x:v>White完整体力循环与座位异常验收</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="str">
+        <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="str">
+        <x:v>保留该阶段临时角色验收；最新150人休息抽查2人通过、1人超时，见CA-072.05。</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G51" s="7" t="str">
+        <x:v>qa_stamina_result与最终交付</x:v>
+      </x:c>
+      <x:c r="H51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="92" customHeight="1">
+      <x:c r="A52" s="7" t="str">
+        <x:v>CA-053.09</x:v>
+      </x:c>
+      <x:c r="B52" s="7" t="str">
+        <x:v>唯一White十二条跨校园实走验收</x:v>
+      </x:c>
+      <x:c r="C52" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="str">
+        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="str">
+        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G52" s="7" t="str">
+        <x:v>suite_result与final_result</x:v>
+      </x:c>
+      <x:c r="H52" s="16" t="str"/>
+    </x:row>
+    <x:row r="53" ht="75" customHeight="1">
+      <x:c r="A53" s="7" t="str">
         <x:v>CA-053.10</x:v>
       </x:c>
-      <x:c r="B49" s="7" t="str">
+      <x:c r="B53" s="7" t="str">
         <x:v>White全校园随机选点覆盖抽样</x:v>
       </x:c>
-      <x:c r="C49" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D49" s="7" t="str">
+      <x:c r="C53" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="str">
         <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
       </x:c>
-      <x:c r="E49" s="7" t="str">
+      <x:c r="E53" s="7" t="str">
         <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
       </x:c>
-      <x:c r="F49" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G49" s="7" t="str">
+      <x:c r="F53" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G53" s="7" t="str">
         <x:v>final_result随机覆盖与解释</x:v>
       </x:c>
-      <x:c r="H49" s="16" t="str"/>
-    </x:row>
-    <x:row r="50" ht="92" customHeight="1">
-      <x:c r="A50" s="7" t="str">
+      <x:c r="H53" s="16" t="str"/>
+    </x:row>
+    <x:row r="54" ht="92" customHeight="1">
+      <x:c r="A54" s="7" t="str">
         <x:v>CA-054.02</x:v>
       </x:c>
-      <x:c r="B50" s="7" t="str">
+      <x:c r="B54" s="7" t="str">
         <x:v>唯一White与观察入口阶段运行验收</x:v>
       </x:c>
-      <x:c r="C50" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D50" s="7" t="str">
+      <x:c r="C54" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="str">
         <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
       </x:c>
-      <x:c r="E50" s="7" t="str">
+      <x:c r="E54" s="7" t="str">
         <x:v>本项保留人数精简和观察入口阶段验收；当前学生人数见CA-002、第一人称入口见CA-055。</x:v>
       </x:c>
-      <x:c r="F50" s="14" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="G50" s="7" t="str">
+      <x:c r="F54" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
         <x:v>原观察验证与后续第一人称运行结果</x:v>
       </x:c>
-      <x:c r="H50" s="16" t="str"/>
-    </x:row>
-    <x:row r="51" ht="109" customHeight="1">
-      <x:c r="A51" s="7" t="str">
+      <x:c r="H54" s="16" t="str"/>
+    </x:row>
+    <x:row r="55" ht="109" customHeight="1">
+      <x:c r="A55" s="7" t="str">
         <x:v>CA-055</x:v>
       </x:c>
-      <x:c r="B51" s="7" t="str">
+      <x:c r="B55" s="7" t="str">
         <x:v>第一人称默认出生与十五项运行验收</x:v>
       </x:c>
-      <x:c r="C51" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D51" s="7" t="str">
+      <x:c r="C55" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D55" s="7" t="str">
         <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
       </x:c>
-      <x:c r="E51" s="7" t="str">
+      <x:c r="E55" s="7" t="str">
         <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
       </x:c>
-      <x:c r="F51" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G51" s="7" t="str">
+      <x:c r="F55" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G55" s="7" t="str">
         <x:v>startup_runtime_report与新包画面</x:v>
       </x:c>
-      <x:c r="H51" s="16" t="str"/>
-    </x:row>
-    <x:row r="52" ht="75" customHeight="1">
-      <x:c r="A52" s="7" t="str">
+      <x:c r="H55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="75" customHeight="1">
+      <x:c r="A56" s="7" t="str">
         <x:v>CA-056.02</x:v>
       </x:c>
-      <x:c r="B52" s="7" t="str">
+      <x:c r="B56" s="7" t="str">
         <x:v>高三楼门三百二十八项运行验收</x:v>
       </x:c>
-      <x:c r="C52" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D52" s="7" t="str">
+      <x:c r="C56" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="str">
         <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
       </x:c>
-      <x:c r="E52" s="7" t="str">
+      <x:c r="E56" s="7" t="str">
         <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
       </x:c>
-      <x:c r="F52" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G52" s="7" t="str">
+      <x:c r="F56" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G56" s="7" t="str">
         <x:v>runtime_verification与completion</x:v>
       </x:c>
-      <x:c r="H52" s="16" t="str"/>
-    </x:row>
-    <x:row r="53" ht="58" customHeight="1">
-      <x:c r="A53" s="7" t="str">
+      <x:c r="H56" s="16" t="str"/>
+    </x:row>
+    <x:row r="57" ht="58" customHeight="1">
+      <x:c r="A57" s="7" t="str">
         <x:v>CA-056.03</x:v>
       </x:c>
-      <x:c r="B53" s="7" t="str">
+      <x:c r="B57" s="7" t="str">
         <x:v>高三门保存回读与原门保护验收</x:v>
       </x:c>
-      <x:c r="C53" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D53" s="7" t="str">
+      <x:c r="C57" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D57" s="7" t="str">
         <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
       </x:c>
-      <x:c r="E53" s="7" t="str">
+      <x:c r="E57" s="7" t="str">
         <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
       </x:c>
-      <x:c r="F53" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G53" s="7" t="str">
+      <x:c r="F57" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="str">
         <x:v>persisted_verification</x:v>
-      </x:c>
-      <x:c r="H53" s="16" t="str"/>
-    </x:row>
-    <x:row r="54" ht="75" customHeight="1">
-      <x:c r="A54" s="7" t="str">
-        <x:v>CA-057.04</x:v>
-      </x:c>
-      <x:c r="B54" s="7" t="str">
-        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
-      </x:c>
-      <x:c r="C54" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D54" s="7" t="str">
-        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
-      </x:c>
-      <x:c r="E54" s="7" t="str">
-        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
-      </x:c>
-      <x:c r="F54" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G54" s="7" t="str">
-        <x:v>V2 verification</x:v>
-      </x:c>
-      <x:c r="H54" s="16" t="str"/>
-    </x:row>
-    <x:row r="55" ht="75" customHeight="1">
-      <x:c r="A55" s="7" t="str">
-        <x:v>CA-058.03</x:v>
-      </x:c>
-      <x:c r="B55" s="7" t="str">
-        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
-      </x:c>
-      <x:c r="C55" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D55" s="7" t="str">
-        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
-      </x:c>
-      <x:c r="E55" s="7" t="str">
-        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
-      </x:c>
-      <x:c r="F55" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G55" s="7" t="str">
-        <x:v>遮阳棚verification</x:v>
-      </x:c>
-      <x:c r="H55" s="16" t="str"/>
-    </x:row>
-    <x:row r="56" ht="58" customHeight="1">
-      <x:c r="A56" s="7" t="str">
-        <x:v>CA-059.03</x:v>
-      </x:c>
-      <x:c r="B56" s="7" t="str">
-        <x:v>棕榈落地树干碰撞与通道检查</x:v>
-      </x:c>
-      <x:c r="C56" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D56" s="7" t="str">
-        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
-      </x:c>
-      <x:c r="E56" s="7" t="str">
-        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
-      </x:c>
-      <x:c r="F56" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G56" s="7" t="str">
-        <x:v>palms_verification</x:v>
-      </x:c>
-      <x:c r="H56" s="16" t="str"/>
-    </x:row>
-    <x:row r="57" ht="75" customHeight="1">
-      <x:c r="A57" s="7" t="str">
-        <x:v>CA-060.03</x:v>
-      </x:c>
-      <x:c r="B57" s="7" t="str">
-        <x:v>校训朝向字距屋顶贴合检查</x:v>
-      </x:c>
-      <x:c r="C57" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D57" s="7" t="str">
-        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
-      </x:c>
-      <x:c r="E57" s="7" t="str">
-        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
-      </x:c>
-      <x:c r="F57" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G57" s="7" t="str">
-        <x:v>verification与final_save</x:v>
       </x:c>
       <x:c r="H57" s="16" t="str"/>
     </x:row>
     <x:row r="58" ht="75" customHeight="1">
       <x:c r="A58" s="7" t="str">
-        <x:v>CA-061.02</x:v>
+        <x:v>CA-057.04</x:v>
       </x:c>
       <x:c r="B58" s="7" t="str">
-        <x:v>大纲整理场景属性与实例保护验收</x:v>
+        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
       </x:c>
       <x:c r="C58" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D58" s="7" t="str">
-        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
       </x:c>
       <x:c r="E58" s="7" t="str">
-        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
-      </x:c>
-      <x:c r="F58" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G58" s="7" t="str">
-        <x:v>大纲verification</x:v>
+        <x:v>V2 verification</x:v>
       </x:c>
       <x:c r="H58" s="16" t="str"/>
     </x:row>
     <x:row r="59" ht="75" customHeight="1">
       <x:c r="A59" s="7" t="str">
+        <x:v>CA-058.03</x:v>
+      </x:c>
+      <x:c r="B59" s="7" t="str">
+        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="str">
+        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="str">
+        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
+        <x:v>遮阳棚verification</x:v>
+      </x:c>
+      <x:c r="H59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="58" customHeight="1">
+      <x:c r="A60" s="7" t="str">
+        <x:v>CA-059.03</x:v>
+      </x:c>
+      <x:c r="B60" s="7" t="str">
+        <x:v>棕榈落地树干碰撞与通道检查</x:v>
+      </x:c>
+      <x:c r="C60" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="str">
+        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="str">
+        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G60" s="7" t="str">
+        <x:v>palms_verification</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str"/>
+    </x:row>
+    <x:row r="61" ht="75" customHeight="1">
+      <x:c r="A61" s="7" t="str">
+        <x:v>CA-060.03</x:v>
+      </x:c>
+      <x:c r="B61" s="7" t="str">
+        <x:v>校训朝向字距屋顶贴合检查</x:v>
+      </x:c>
+      <x:c r="C61" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D61" s="7" t="str">
+        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="str">
+        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G61" s="7" t="str">
+        <x:v>verification与final_save</x:v>
+      </x:c>
+      <x:c r="H61" s="16" t="str"/>
+    </x:row>
+    <x:row r="62" ht="75" customHeight="1">
+      <x:c r="A62" s="7" t="str">
+        <x:v>CA-061.02</x:v>
+      </x:c>
+      <x:c r="B62" s="7" t="str">
+        <x:v>大纲整理场景属性与实例保护验收</x:v>
+      </x:c>
+      <x:c r="C62" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D62" s="7" t="str">
+        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="str">
+        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G62" s="7" t="str">
+        <x:v>大纲verification</x:v>
+      </x:c>
+      <x:c r="H62" s="16" t="str"/>
+    </x:row>
+    <x:row r="63" ht="75" customHeight="1">
+      <x:c r="A63" s="7" t="str">
         <x:v>CA-063.05</x:v>
       </x:c>
-      <x:c r="B59" s="7" t="str">
+      <x:c r="B63" s="7" t="str">
         <x:v>参考夜景保存与模拟运行检查</x:v>
       </x:c>
-      <x:c r="C59" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D59" s="7" t="str">
+      <x:c r="C63" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D63" s="7" t="str">
         <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
       </x:c>
-      <x:c r="E59" s="7" t="str">
+      <x:c r="E63" s="7" t="str">
         <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
       </x:c>
-      <x:c r="F59" s="14" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="G59" s="7" t="str">
+      <x:c r="F63" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G63" s="7" t="str">
         <x:v>final_verified与runtime_verified</x:v>
       </x:c>
-      <x:c r="H59" s="16" t="str"/>
-    </x:row>
-    <x:row r="60" ht="92" customHeight="1">
-      <x:c r="A60" s="7" t="str">
+      <x:c r="H63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="92" customHeight="1">
+      <x:c r="A64" s="7" t="str">
         <x:v>CA-064.07</x:v>
       </x:c>
-      <x:c r="B60" s="7" t="str">
+      <x:c r="B64" s="7" t="str">
         <x:v>三轮昼夜切换原夜景参数还原</x:v>
       </x:c>
-      <x:c r="C60" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D60" s="7" t="str">
+      <x:c r="C64" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="str">
         <x:v>初版三轮昼夜300灯精确还原保留。最新黄昏检查17:00至22:00各阶段，22:00全部300灯恢复原亮度，night_restored_exactly=true；正午零灯规则仍通过。</x:v>
       </x:c>
-      <x:c r="E60" s="7" t="str">
+      <x:c r="E64" s="7" t="str">
         <x:v>原夜空已因月升月落按用户要求修改，不再声称当前夜空shader与旧版完全一致；只认定各阶段参数验收。</x:v>
       </x:c>
-      <x:c r="F60" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G60" s="7" t="str">
+      <x:c r="F64" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
         <x:v>Daylight scene_verified三轮结果</x:v>
       </x:c>
-      <x:c r="H60" s="16" t="str"/>
-    </x:row>
-    <x:row r="61" ht="92" customHeight="1">
-      <x:c r="A61" s="7" t="str">
+      <x:c r="H64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65" ht="92" customHeight="1">
+      <x:c r="A65" s="7" t="str">
         <x:v>CA-064.08</x:v>
       </x:c>
-      <x:c r="B61" s="7" t="str">
+      <x:c r="B65" s="7" t="str">
         <x:v>当前昼夜十六项自动化环境回归</x:v>
       </x:c>
-      <x:c r="C61" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D61" s="7" t="str">
+      <x:c r="C65" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="str">
         <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
       </x:c>
-      <x:c r="E61" s="7" t="str">
+      <x:c r="E65" s="7" t="str">
         <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
       </x:c>
-      <x:c r="F61" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G61" s="7" t="str">
+      <x:c r="F65" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G65" s="7" t="str">
         <x:v>最新自动化index与最终聊天</x:v>
       </x:c>
-      <x:c r="H61" s="16" t="str"/>
-    </x:row>
-    <x:row r="62" ht="109" customHeight="1">
-      <x:c r="A62" s="7" t="str">
+      <x:c r="H65" s="16" t="str"/>
+    </x:row>
+    <x:row r="66" ht="109" customHeight="1">
+      <x:c r="A66" s="7" t="str">
         <x:v>CA-065.03</x:v>
       </x:c>
-      <x:c r="B62" s="7" t="str">
+      <x:c r="B66" s="7" t="str">
         <x:v>一键脚本原工程完整构建交付</x:v>
       </x:c>
-      <x:c r="C62" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D62" s="7" t="str">
+      <x:c r="C66" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="str">
         <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
       </x:c>
-      <x:c r="E62" s="7" t="str">
+      <x:c r="E66" s="7" t="str">
         <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
       </x:c>
-      <x:c r="F62" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G62" s="7" t="str">
+      <x:c r="F66" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G66" s="7" t="str">
         <x:v>ScenePackages build-info实际成功记录</x:v>
-      </x:c>
-      <x:c r="H62" s="16" t="str"/>
-    </x:row>
-    <x:row r="63" ht="92" customHeight="1">
-      <x:c r="A63" s="7" t="str">
-        <x:v>CA-066.02</x:v>
-      </x:c>
-      <x:c r="B63" s="7" t="str">
-        <x:v>时间面板调时暂停与保存基准检查</x:v>
-      </x:c>
-      <x:c r="C63" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D63" s="7" t="str">
-        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
-      </x:c>
-      <x:c r="E63" s="7" t="str">
-        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
-      </x:c>
-      <x:c r="F63" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G63" s="7" t="str">
-        <x:v>面板实操及夜景恢复检查</x:v>
-      </x:c>
-      <x:c r="H63" s="16" t="str"/>
-    </x:row>
-    <x:row r="64" ht="75" customHeight="1">
-      <x:c r="A64" s="7" t="str">
-        <x:v>CA-068.02</x:v>
-      </x:c>
-      <x:c r="B64" s="7" t="str">
-        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
-      </x:c>
-      <x:c r="C64" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D64" s="7" t="str">
-        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
-      </x:c>
-      <x:c r="E64" s="7" t="str">
-        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
-      </x:c>
-      <x:c r="F64" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G64" s="7" t="str">
-        <x:v>月亮运行796帧与重载报告</x:v>
-      </x:c>
-      <x:c r="H64" s="16" t="str"/>
-    </x:row>
-    <x:row r="65" ht="75" customHeight="1">
-      <x:c r="A65" s="7" t="str">
-        <x:v>CA-070.04</x:v>
-      </x:c>
-      <x:c r="B65" s="7" t="str">
-        <x:v>教学楼材质合批镜像与门结构保持</x:v>
-      </x:c>
-      <x:c r="C65" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D65" s="7" t="str">
-        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
-      </x:c>
-      <x:c r="E65" s="7" t="str">
-        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
-      </x:c>
-      <x:c r="F65" s="14" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="G65" s="7" t="str">
-        <x:v>真实材质与纯色门结构验证</x:v>
-      </x:c>
-      <x:c r="H65" s="16" t="str"/>
-    </x:row>
-    <x:row r="66" ht="92" customHeight="1">
-      <x:c r="A66" s="7" t="str">
-        <x:v>CA-071.05</x:v>
-      </x:c>
-      <x:c r="B66" s="7" t="str">
-        <x:v>草地全量朝向坐标材质及保存检查</x:v>
-      </x:c>
-      <x:c r="C66" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D66" s="7" t="str">
-        <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
-      </x:c>
-      <x:c r="E66" s="7" t="str">
-        <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
-      </x:c>
-      <x:c r="F66" s="14" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="G66" s="7" t="str">
-        <x:v>草地全量检查和67秒保存回执</x:v>
       </x:c>
       <x:c r="H66" s="16" t="str"/>
     </x:row>
     <x:row r="67" ht="92" customHeight="1">
       <x:c r="A67" s="7" t="str">
-        <x:v>CA-072.04</x:v>
+        <x:v>CA-066.02</x:v>
       </x:c>
       <x:c r="B67" s="7" t="str">
-        <x:v>150名White运行移动与行为保留</x:v>
+        <x:v>时间面板调时暂停与保存基准检查</x:v>
       </x:c>
       <x:c r="C67" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D67" s="7" t="str">
-        <x:v>运行全程150名White、控制器完整且导航目标非部分路径；150人全部移动并选择巡游目标，观察到体力消耗，保留设置及动画策略检查均通过。平均位移约29.81m，最小约2.80m。</x:v>
+        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
       </x:c>
       <x:c r="E67" s="7" t="str">
-        <x:v>完成该被动观察样本；不替代全校园逐路线、长期互相穿透和全体休息验证。</x:v>
-      </x:c>
-      <x:c r="F67" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G67" s="7" t="str">
-        <x:v>150人运行QA与最终保存确认</x:v>
+        <x:v>面板实操及夜景恢复检查</x:v>
       </x:c>
       <x:c r="H67" s="16" t="str"/>
     </x:row>
-    <x:row r="68" ht="92" customHeight="1">
+    <x:row r="68" ht="75" customHeight="1">
       <x:c r="A68" s="7" t="str">
-        <x:v>CA-073.07</x:v>
+        <x:v>CA-068.02</x:v>
       </x:c>
       <x:c r="B68" s="7" t="str">
-        <x:v>天气昼夜屋顶与停雨运行检查</x:v>
+        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
       </x:c>
       <x:c r="C68" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D68" s="7" t="str">
-        <x:v>正午阴天、正午降雨、夜间降雨、停雨4阶段运行errors为空、passed=true；停雨仍湿润后渐干，屋顶与室外304帧检查通过，材质重载无绑定错误。</x:v>
+        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
       </x:c>
       <x:c r="E68" s="7" t="str">
-        <x:v>屋顶边缘未全量检查；此项不等于发布包全路线实测。</x:v>
-      </x:c>
-      <x:c r="F68" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G68" s="7" t="str">
-        <x:v>天气运行和宽屋顶验证范围</x:v>
+        <x:v>月亮运行796帧与重载报告</x:v>
       </x:c>
       <x:c r="H68" s="16" t="str"/>
     </x:row>
-    <x:row r="69" ht="92" customHeight="1">
+    <x:row r="69" ht="75" customHeight="1">
       <x:c r="A69" s="7" t="str">
-        <x:v>CA-073.08</x:v>
+        <x:v>CA-070.04</x:v>
       </x:c>
       <x:c r="B69" s="7" t="str">
-        <x:v>最终阴雨调度及昼夜自动化回归</x:v>
+        <x:v>教学楼材质合批镜像与门结构保持</x:v>
       </x:c>
       <x:c r="C69" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D69" s="7" t="str">
-        <x:v>最终编译成功，最新自动化24项通过、0失败、0警告、0未运行；覆盖随机时长上限、中途反向、材质参数连续和昼夜联动。初版20项仅保留阶段依据。</x:v>
+        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
       </x:c>
       <x:c r="E69" s="7" t="str">
-        <x:v>测试不等于实际连续运行30分钟；随机时长上限已有多组参数自动化验证。</x:v>
-      </x:c>
-      <x:c r="F69" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G69" s="7" t="str">
-        <x:v>最终Automation报告24通过0失败</x:v>
+        <x:v>真实材质与纯色门结构验证</x:v>
       </x:c>
       <x:c r="H69" s="16" t="str"/>
     </x:row>
     <x:row r="70" ht="92" customHeight="1">
       <x:c r="A70" s="7" t="str">
+        <x:v>CA-071.05</x:v>
+      </x:c>
+      <x:c r="B70" s="7" t="str">
+        <x:v>草地全量朝向坐标材质及保存检查</x:v>
+      </x:c>
+      <x:c r="C70" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D70" s="7" t="str">
+        <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="str">
+        <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G70" s="7" t="str">
+        <x:v>草地全量检查和67秒保存回执</x:v>
+      </x:c>
+      <x:c r="H70" s="16" t="str"/>
+    </x:row>
+    <x:row r="71" ht="92" customHeight="1">
+      <x:c r="A71" s="7" t="str">
+        <x:v>CA-072.04</x:v>
+      </x:c>
+      <x:c r="B71" s="7" t="str">
+        <x:v>150名White运行移动与行为保留</x:v>
+      </x:c>
+      <x:c r="C71" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D71" s="7" t="str">
+        <x:v>运行全程150名White、控制器完整且导航目标非部分路径；150人全部移动并选择巡游目标，观察到体力消耗，保留设置及动画策略检查均通过。平均位移约29.81m，最小约2.80m。</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="str">
+        <x:v>完成该被动观察样本；不替代全校园逐路线、长期互相穿透和全体休息验证。</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G71" s="7" t="str">
+        <x:v>150人运行QA与最终保存确认</x:v>
+      </x:c>
+      <x:c r="H71" s="16" t="str"/>
+    </x:row>
+    <x:row r="72" ht="92" customHeight="1">
+      <x:c r="A72" s="7" t="str">
+        <x:v>CA-073.07</x:v>
+      </x:c>
+      <x:c r="B72" s="7" t="str">
+        <x:v>天气昼夜屋顶与停雨运行检查</x:v>
+      </x:c>
+      <x:c r="C72" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D72" s="7" t="str">
+        <x:v>正午阴天、正午降雨、夜间降雨、停雨4阶段运行errors为空、passed=true；停雨仍湿润后渐干，屋顶与室外304帧检查通过，材质重载无绑定错误。</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="str">
+        <x:v>屋顶边缘未全量检查；此项不等于发布包全路线实测。</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G72" s="7" t="str">
+        <x:v>天气运行和宽屋顶验证范围</x:v>
+      </x:c>
+      <x:c r="H72" s="16" t="str"/>
+    </x:row>
+    <x:row r="73" ht="75" customHeight="1">
+      <x:c r="A73" s="7" t="str">
+        <x:v>CA-073.08</x:v>
+      </x:c>
+      <x:c r="B73" s="7" t="str">
+        <x:v>晴雨调度及昼夜灯光自动化回归</x:v>
+      </x:c>
+      <x:c r="C73" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D73" s="7" t="str">
+        <x:v>10月8日最终27项通过、0失败、0警告、0未运行，新增晴天往返恢复与原版天空保持验证；此前20/24/26项结果保留阶段历史。</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="str">
+        <x:v>最终报告为编辑器自动化；不等于实际连续运行30分钟或10月9日新材质后的全场回归。</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G73" s="7" t="str">
+        <x:v>ClearWeatherFix最终Automation27通过0失败</x:v>
+      </x:c>
+      <x:c r="H73" s="16" t="str"/>
+    </x:row>
+    <x:row r="74" ht="92" customHeight="1">
+      <x:c r="A74" s="7" t="str">
         <x:v>CA-073.09</x:v>
       </x:c>
-      <x:c r="B70" s="7" t="str">
+      <x:c r="B74" s="7" t="str">
         <x:v>天气按钮点击与完整渐变播放</x:v>
       </x:c>
-      <x:c r="C70" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D70" s="7" t="str">
+      <x:c r="C74" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D74" s="7" t="str">
         <x:v>实际点击后的雨量、云层、湿度连续变化，最终点击报告passed=true，保存时长30秒，观测约38.2秒至过渡完成；详情切换反向、恢复及重启预览检查errors为空。</x:v>
       </x:c>
-      <x:c r="E70" s="7" t="str">
+      <x:c r="E74" s="7" t="str">
         <x:v>编辑器预览已验；Shipping按钮适用范围与成品运行另按版本判断。</x:v>
       </x:c>
-      <x:c r="F70" s="14" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="G70" s="7" t="str">
+      <x:c r="F74" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G74" s="7" t="str">
         <x:v>按钮点击、反向及最终预览状态</x:v>
       </x:c>
-      <x:c r="H70" s="16" t="str"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="1"/>
-      <x:c r="B71" s="1"/>
-      <x:c r="C71" s="1"/>
-      <x:c r="D71" s="1"/>
-      <x:c r="E71" s="1"/>
-      <x:c r="F71" s="1"/>
-      <x:c r="G71" s="1"/>
-      <x:c r="H71" s="1"/>
-    </x:row>
-    <x:row r="72" ht="34" customHeight="1">
-      <x:c r="A72" s="3" t="str">
+      <x:c r="H74" s="16" t="str"/>
+    </x:row>
+    <x:row r="75" ht="75" customHeight="1">
+      <x:c r="A75" s="7" t="str">
+        <x:v>CA-074.05</x:v>
+      </x:c>
+      <x:c r="B75" s="7" t="str">
+        <x:v>254个开关墙面定位与操作站位</x:v>
+      </x:c>
+      <x:c r="C75" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D75" s="7" t="str">
+        <x:v>最终交付确认安装位置、遮挡检查完成。全部254个真实E键测试从已校验站位执行，玩家胶囊保持碰撞，面板对准与原生提示焦点有效。</x:v>
+      </x:c>
+      <x:c r="E75" s="7" t="str">
+        <x:v>未把传送到站位测试扩大为全楼逐路线实走。</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G75" s="7" t="str">
+        <x:v>最终交付、站位与焦点逐项结果</x:v>
+      </x:c>
+      <x:c r="H75" s="16" t="str"/>
+    </x:row>
+    <x:row r="76" ht="92" customHeight="1">
+      <x:c r="A76" s="7" t="str">
+        <x:v>CA-074.06</x:v>
+      </x:c>
+      <x:c r="B76" s="7" t="str">
+        <x:v>全部墙壁开关508次E键交互</x:v>
+      </x:c>
+      <x:c r="C76" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D76" s="7" t="str">
+        <x:v>254个开关各切换并恢复一次，508次真实E输入全部通过；联动面板状态一致，无无关回路或门状态变化。为隔离NPC自动开门，150名学生的巡游临时关闭，验证后恢复。</x:v>
+      </x:c>
+      <x:c r="E76" s="7" t="str">
+        <x:v>这是输入与回路验收；不扩大为150人正常巡游时全流程回归或Shipping实测。</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G76" s="7" t="str">
+        <x:v>runtime_input passed=true、254项与508次最终确认</x:v>
+      </x:c>
+      <x:c r="H76" s="16" t="str"/>
+    </x:row>
+    <x:row r="77" ht="75" customHeight="1">
+      <x:c r="A77" s="7" t="str">
+        <x:v>CA-074.07</x:v>
+      </x:c>
+      <x:c r="B77" s="7" t="str">
+        <x:v>开关隔墙远距与门输入隔离抽查</x:v>
+      </x:c>
+      <x:c r="C77" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D77" s="7" t="str">
+        <x:v>behind_wall、too_far、look_away三类拒绝操作，以及A_Room_101/B_Room_403临近门正常打开共5个案例通过，errors为空。</x:v>
+      </x:c>
+      <x:c r="E77" s="7" t="str">
+        <x:v>该项仅记录5个抽查案例，全校门回归仍见CA-010。</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G77" s="7" t="str">
+        <x:v>runtime_access全部5例passed=true</x:v>
+      </x:c>
+      <x:c r="H77" s="16" t="str"/>
+    </x:row>
+    <x:row r="78" ht="92" customHeight="1">
+      <x:c r="A78" s="7" t="str">
+        <x:v>CA-075.05</x:v>
+      </x:c>
+      <x:c r="B78" s="7" t="str">
+        <x:v>动态云层间隔截图运动验证</x:v>
+      </x:c>
+      <x:c r="C78" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D78" s="7" t="str">
+        <x:v>相同机位间隔31.54秒的两帧，云层区域抑制雨线后RGB平均变化约5.35/5.35/5.47，cloud_motion_visible=true，最终聊天确认可见运动。</x:v>
+      </x:c>
+      <x:c r="E78" s="7" t="str">
+        <x:v>仅确认该样本中云层运动，不等于长时天气或性能验收。</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G78" s="7" t="str">
+        <x:v>motion_verification与最终两帧检查</x:v>
+      </x:c>
+      <x:c r="H78" s="16" t="str"/>
+    </x:row>
+    <x:row r="79" ht="75" customHeight="1">
+      <x:c r="A79" s="7" t="str">
+        <x:v>CA-075.08</x:v>
+      </x:c>
+      <x:c r="B79" s="7" t="str">
+        <x:v>白昼夜晚晴雨四组合恢复验证</x:v>
+      </x:c>
+      <x:c r="C79" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D79" s="7" t="str">
+        <x:v>12:00/22:00分别验证下雨与晴天，四组合检查通过，晴时覆盖参数归零且雨后湿地继续渐干；最终面板显示晴天并停在22:00。</x:v>
+      </x:c>
+      <x:c r="E79" s="7" t="str">
+        <x:v>27项自动化另见CA-073.08；此项为四组合场景预览，不能替代发布包实测。</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G79" s="7" t="str">
+        <x:v>scene_verification四组合与最终面板确认</x:v>
+      </x:c>
+      <x:c r="H79" s="16" t="str"/>
+    </x:row>
+    <x:row r="80" ht="92" customHeight="1">
+      <x:c r="A80" s="7" t="str">
+        <x:v>CA-076.09</x:v>
+      </x:c>
+      <x:c r="B80" s="7" t="str">
+        <x:v>食堂新材质保存与实例表现同步</x:v>
+      </x:c>
+      <x:c r="C80" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D80" s="7" t="str">
+        <x:v>主关卡保存确认；9052兼容实例组/102611实例在内存校验通过，77旧批次退出，810处新材质作为独立可见物体保留。最终保存校验已含补植后的结果，替代中途806处。</x:v>
+      </x:c>
+      <x:c r="E80" s="7" t="str">
+        <x:v>验证是保存和运行时表现预览，不是独立游戏或Shipping运行；临时预览恢复信息已保留。</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G80" s="7" t="str">
+        <x:v>saved=true、810绑定与verified_in_memory</x:v>
+      </x:c>
+      <x:c r="H80" s="16" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="1"/>
+      <x:c r="B81" s="1"/>
+      <x:c r="C81" s="1"/>
+      <x:c r="D81" s="1"/>
+      <x:c r="E81" s="1"/>
+      <x:c r="F81" s="1"/>
+      <x:c r="G81" s="1"/>
+      <x:c r="H81" s="1"/>
+    </x:row>
+    <x:row r="82" ht="34" customHeight="1">
+      <x:c r="A82" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B72" s="21" t="str">
+      <x:c r="B82" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C72" s="21"/>
-      <x:c r="D72" s="21"/>
-      <x:c r="E72" s="21"/>
-      <x:c r="F72" s="21"/>
-      <x:c r="G72" s="21"/>
-      <x:c r="H72" s="21"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="1"/>
-      <x:c r="B73" s="1"/>
-      <x:c r="C73" s="1"/>
-      <x:c r="D73" s="1"/>
-      <x:c r="E73" s="1"/>
-      <x:c r="F73" s="1"/>
-      <x:c r="G73" s="1"/>
-      <x:c r="H73" s="1"/>
+      <x:c r="C82" s="21"/>
+      <x:c r="D82" s="21"/>
+      <x:c r="E82" s="21"/>
+      <x:c r="F82" s="21"/>
+      <x:c r="G82" s="21"/>
+      <x:c r="H82" s="21"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="1"/>
+      <x:c r="B83" s="1"/>
+      <x:c r="C83" s="1"/>
+      <x:c r="D83" s="1"/>
+      <x:c r="E83" s="1"/>
+      <x:c r="F83" s="1"/>
+      <x:c r="G83" s="1"/>
+      <x:c r="H83" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B72:H72"/>
+    <x:mergeCell ref="B82:H82"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C70">
+  <x:conditionalFormatting sqref="C8:C80">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -2084,13 +2330,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C70">
+    <x:dataValidation type="list" sqref="C8:C80">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a0d206cc1894ca4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc475a950337c46e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/测试验收.xlsx
+++ b/ProjectProgress/表格/分类进展/测试验收.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R44f47bae12a6419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试验收" sheetId="1" r:id="R8d9913383bc246d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H80"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress10" displayName="CategoryProgress10" ref="A7:H92" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H92"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -470,23 +470,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C80,A5)</x:f>
-        <x:v>57</x:v>
+        <x:f>COUNTIF(C8:C92,A5)</x:f>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C80,D5)</x:f>
+        <x:f>COUNTIF(C8:C92,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C80,F5)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTIF(C8:C92,F5)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -550,7 +550,7 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="109" customHeight="1">
+    <x:row r="9" ht="92" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-010</x:v>
       </x:c>
@@ -561,16 +561,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>旧185控制器保存重开与四类门32项检查、White自动开门保留。高三楼新增120门扇/109交互组，328项运行及保存回读通过，旧185门未变。当前玩家已恢复第一人称，仍缺全校所有门同版本连续实走覆盖。</x:v>
+        <x:v>旧185控制器与高三楼328项门验收保留。10月10日A/B合并后48保留门及新家具版本的开合检查通过；仍缺全校所有门同版本连续实走覆盖，不能以24教室局部测试关闭。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>按所需全校范围核对未覆盖实例；高三门开关验收与29个厕位门洞不可通行分别见CA-056系列。</x:v>
+        <x:v>教室合并/重做局部回归见CA-079.05、CA-080.08；高三厕位门洞限制仍独立跟踪。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>高三门新增验收与第一人称恢复</x:v>
+        <x:v>最新48教室门局部验收与全校范围对照</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -801,16 +801,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>已知10月5日5批、10月6日3批及10月9日00:03共9批Shipping构建成功。最新包包含此前开关和晴雨修订的构建时序证据，但早于食堂写实改造；仍未发现这些具体包的启动、响应、退出或玩法运行验收。</x:v>
+        <x:v>已知原工程scene共11批Shipping构建成功，新增10月9日22:37和23:56两包，后者晚于PS5与补灯修订且带GameInput安装包，均早于10月10日教室合并/室内重做；仍无这两具体包启动响应退出及玩法实测。</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>按具体包核对实机记录；最新食堂改造未由00:03包覆盖，编辑器预览与自动化不能替代成品验收。</x:v>
+        <x:v>核对具体包实机结果和最新教室版本是否有后续构建；不再将“尚未重打包”的旧PS5答复永久固定，后续构建已有证据。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>新增Shipping成功及最新实现先后范围</x:v>
+        <x:v>新增两批成功构建及最新版本时序</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str"/>
     </x:row>
@@ -891,1434 +891,1722 @@
         <x:v>CA-076.11</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>食堂新材质后的完整昼夜晴雨回归</x:v>
+        <x:v>新铺装后的夜景与昼夜往返回归</x:v>
       </x:c>
       <x:c r="C23" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>本轮源说明保留昼夜天气接口，final_preview只记录10:30晴天四个天气参数归零。10月8日四组合与27测试早于10月9日新材质保存，尚无新绑定版本雨景、夜景与往返恢复记录。</x:v>
+        <x:v>10月9日全场新铺装雨天→停雨残留→完全干燥已实际通过，原雨景接口缺口已由CA-078.03关闭。仍缺新绑定版本夜景、昼夜往返恢复记录；10月8日四组合和27测试早于新材质。</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>核对新材质同版本的昼夜晴雨回归或接受范围；不由追踪任务启动编辑器验证。</x:v>
+        <x:v>仅核对未覆盖的夜景及昼夜往返，或确认所需验收范围；不再反复要求已经通过的新铺装渐干验证。</x:v>
       </x:c>
       <x:c r="F23" s="14" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>final_preview与先后版本范围对照</x:v>
+        <x:v>最新五阶段天气passed，夜景范围未覆盖</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>CA-001.07</x:v>
+        <x:v>CA-077.03</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>White 换装后 30 人运行与保存验收</x:v>
-      </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>DualSense USB与蓝牙实体输入验收</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
+        <x:v>本次未连接PS5手柄，最终检查明确hardware_input_tested=false。设备配置和GameInput初始化已通过，但USB/蓝牙移动、视角、跳跃及门灯输入未实测。</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
+        <x:v>核对实际连接方式下的实体手柄结果和重复输入情况；不由追踪任务运行游戏。</x:v>
       </x:c>
       <x:c r="F24" s="14" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
+        <x:v>最终聊天与hardware_input_tested=false</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>CA-006.05</x:v>
+        <x:v>CA-080.11</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
-      </x:c>
-      <x:c r="C25" s="20" t="str">
-        <x:v>已完成</x:v>
+        <x:v>教室参考图严格一致性最终验收</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
+        <x:v>24教室统一风格和模型、文字受光已交付并输出A/B最终图；实时视口仍有光照噪点，最终结果未提供严格参考一致性判定或用户验收。个人物品为用户允许省略范围。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
+        <x:v>核对最终画面在严格还原要求下是否接受或有后续修订；不把所有实现保存计作整体严格验收。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="d">
-        <x:v>2026-09-28T00:00:00.000Z</x:v>
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>男学生校园运行与四肢骨长检查</x:v>
+        <x:v>用户严格参考要求与最终图噪点限制</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>CA-006.06</x:v>
+        <x:v>CA-001.07</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+        <x:v>White 换装后 30 人运行与保存验收</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+        <x:v>最新修复版已导入并保存。20.33 秒、31 次采样中 30 名 White 均使用正确网格与材质，167 骨架保留；所有实例动画推进，待机、行走和转向验证通过。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+        <x:v>本阶段交付通过。编辑器下沉自动恢复验收另见 CA-035.02，不能代替全校门和跨区域回归。</x:v>
       </x:c>
       <x:c r="F26" s="14" t="d">
-        <x:v>2026-09-28T00:00:00.000Z</x:v>
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+        <x:v>White 衣服修复最终交付与 runtime_result passed</x:v>
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
-    <x:row r="27" ht="75" customHeight="1">
+    <x:row r="27" ht="92" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>CA-014.04</x:v>
+        <x:v>CA-006.05</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+        <x:v>男学生 30 人运行、动画切换与骨骼稳定验收</x:v>
       </x:c>
       <x:c r="C27" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+        <x:v>校园 PIE 约 12.485 游戏秒、24 次采样，30 名男学生全部移动，观察到 Walk 和 Idle，网格引用与骨骼缩放正确；最终四肢骨长记录稳定。</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+        <x:v>保留当前有限时长验收范围；后续模型或动画改动按相同实例复查。</x:v>
       </x:c>
       <x:c r="F27" s="14" t="d">
         <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+        <x:v>男学生校园运行与四肢骨长检查</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
       <x:c r="A28" s="7" t="str">
+        <x:v>CA-006.06</x:v>
+      </x:c>
+      <x:c r="B28" s="7" t="str">
+        <x:v>男学生 58 骨资产引用与编辑器收尾</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
+        <x:v>原位更新模型、基色与配套动作，沿用 58 骨架、材质和蓝图路径，蓝图编译保存。退出 PIE 后全部 30 个编辑器待机实例已检查，临时预览对象移除、模拟停止。</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>后续替换保持模型、贴图与配套 Walk、Idle 版本一致，保存引用和收尾记录。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>男学生资产沿用、编辑器实例与清理验收</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="75" customHeight="1">
+      <x:c r="A29" s="7" t="str">
+        <x:v>CA-014.04</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="str">
+        <x:v>综合楼全部楼梯与演奏台真实角色通行验收</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
+        <x:v>真实角色移动输入完成东西翼 1 至 5 层往返、中央阶梯、前后入口及演奏台路线；10/10 路线、82/82 端点、708/708 踏步采样通过。</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>保留已通过的路线基线；建筑改动后复测对应路线。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>综合楼运行与逐级踏步验收记录</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="92" customHeight="1">
+      <x:c r="A30" s="7" t="str">
         <x:v>CA-015.02</x:v>
       </x:c>
-      <x:c r="B28" s="7" t="str">
+      <x:c r="B30" s="7" t="str">
         <x:v>教学楼 A B 一至四层往返验收</x:v>
       </x:c>
-      <x:c r="C28" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D28" s="7" t="str">
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
         <x:v>当前第一人称角色完成 4/4 条一至四层往返路线，88 个端点和 792 处踏步高度/法线检查通过；含平台转弯，未使用跳跃或飞行；资产和关卡已保存。</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="str">
+      <x:c r="E30" s="7" t="str">
         <x:v>后续楼梯调整复测上下楼及平台转弯。</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="d">
-        <x:v>2026-09-26T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G28" s="7" t="str">
-        <x:v>教学楼运行及踏步验收记录</x:v>
-      </x:c>
-      <x:c r="H28" s="16" t="str"/>
-    </x:row>
-    <x:row r="29" ht="92" customHeight="1">
-      <x:c r="A29" s="7" t="str">
-        <x:v>CA-016.02</x:v>
-      </x:c>
-      <x:c r="B29" s="7" t="str">
-        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
-      </x:c>
-      <x:c r="C29" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
-        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
-      </x:c>
-      <x:c r="E29" s="7" t="str">
-        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="d">
-        <x:v>2026-09-26T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G29" s="7" t="str">
-        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
-      </x:c>
-      <x:c r="H29" s="16" t="str"/>
-    </x:row>
-    <x:row r="30" ht="75" customHeight="1">
-      <x:c r="A30" s="7" t="str">
-        <x:v>CA-017.03</x:v>
-      </x:c>
-      <x:c r="B30" s="7" t="str">
-        <x:v>镜像修复保存与重新运行持久性</x:v>
-      </x:c>
-      <x:c r="C30" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="str">
-        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
-      </x:c>
-      <x:c r="E30" s="7" t="str">
-        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
       </x:c>
       <x:c r="F30" s="14" t="d">
         <x:v>2026-09-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+        <x:v>教学楼运行及踏步验收记录</x:v>
       </x:c>
       <x:c r="H30" s="16" t="str"/>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
       <x:c r="A31" s="7" t="str">
+        <x:v>CA-016.02</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>教师楼走廊碰撞与真实角色往返验收</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>编辑器和 PIE 中 128 处误阻挡消失，256 次实体双向射线、72 次角色胶囊扫掠、216 个楼面支撑采样通过；当前角色四层共 4 条往返路线完成。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>保留四层路线和支撑面基线，结构变动后复测。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>教师走廊编辑器/PIE 检查与运行记录</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>CA-017.03</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>镜像修复保存与重新运行持久性</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>重新进入 PIE 自动同步复用全部 9,495 批次，创建与退役均为零；5,534 实例位置最大误差约 2.3×10^-13 cm，缩放误差零。</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>场景或自动实例化脚本变化后重复保存及重新运行核查。</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>教学楼 B 修复记录：重新进入 PIE 验证</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="92" customHeight="1">
+      <x:c r="A33" s="7" t="str">
         <x:v>CA-019.03</x:v>
       </x:c>
-      <x:c r="B31" s="7" t="str">
+      <x:c r="B33" s="7" t="str">
         <x:v>礼堂重启加载、灯光及绿化迁移完整性验收</x:v>
       </x:c>
-      <x:c r="C31" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D31" s="7" t="str">
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
         <x:v>完整重启 UE 并重新加载后，97 组网格和 8 盏室内灯存在；303 个迁移绿化实例数量保留，位置误差 0 cm；验证通过、关卡已保存且无脏地图。</x:v>
       </x:c>
-      <x:c r="E31" s="7" t="str">
+      <x:c r="E33" s="7" t="str">
         <x:v>保留加载与迁移完整性基线，后续修改核对最新保存记录。</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="d">
+      <x:c r="F33" s="14" t="d">
         <x:v>2026-09-24T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G31" s="7" t="str">
+      <x:c r="G33" s="7" t="str">
         <x:v>礼堂最终验证及完整重启复核</x:v>
       </x:c>
-      <x:c r="H31" s="16" t="str"/>
-    </x:row>
-    <x:row r="32" ht="92" customHeight="1">
-      <x:c r="A32" s="7" t="str">
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34" ht="92" customHeight="1">
+      <x:c r="A34" s="7" t="str">
         <x:v>CA-020.02</x:v>
       </x:c>
-      <x:c r="B32" s="7" t="str">
+      <x:c r="B34" s="7" t="str">
         <x:v>升旗广场台阶、铺装和通道射线验收</x:v>
       </x:c>
-      <x:c r="C32" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D32" s="7" t="str">
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
         <x:v>六级台阶、三处铺装及三处后方/两侧通道共 12 项射线检查通过；后方净距 556.5 cm，73 构件尺寸核对通过并保存，未保存关卡数为 0。</x:v>
       </x:c>
-      <x:c r="E32" s="7" t="str">
+      <x:c r="E34" s="7" t="str">
         <x:v>该记录覆盖尺寸与射线检查；后续实际角色通行结论需使用对应运行证据。</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="d">
+      <x:c r="F34" s="14" t="d">
         <x:v>2026-09-24T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G32" s="7" t="str">
+      <x:c r="G34" s="7" t="str">
         <x:v>升旗广场最终射线与保存验证</x:v>
       </x:c>
-      <x:c r="H32" s="16" t="str"/>
-    </x:row>
-    <x:row r="33" ht="109" customHeight="1">
-      <x:c r="A33" s="7" t="str">
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="109" customHeight="1">
+      <x:c r="A35" s="7" t="str">
         <x:v>CA-024.02</x:v>
       </x:c>
-      <x:c r="B33" s="7" t="str">
+      <x:c r="B35" s="7" t="str">
         <x:v>中央庭院道路数值与射线标高验收</x:v>
       </x:c>
-      <x:c r="C33" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D33" s="7" t="str">
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
         <x:v>离线检查覆盖 138,942 个位置。
 最大设计坡度约 4.848%；UE 的 1,355 条路面射线全部命中。
 最大标高误差约 0.0285 cm，无记录中的大误差；主要接口另有跨界采样。</x:v>
       </x:c>
-      <x:c r="E33" s="7" t="str">
+      <x:c r="E35" s="7" t="str">
         <x:v>完成范围为数值和射线标高；真实角色简单碰撞通行见独立待确认项。</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="d">
+      <x:c r="F35" s="14" t="d">
         <x:v>2026-09-22T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G33" s="7" t="str">
+      <x:c r="G35" s="7" t="str">
         <x:v>道路标高验证与保存回执</x:v>
-      </x:c>
-      <x:c r="H33" s="16" t="str"/>
-    </x:row>
-    <x:row r="34" ht="92" customHeight="1">
-      <x:c r="A34" s="7" t="str">
-        <x:v>CA-030.02</x:v>
-      </x:c>
-      <x:c r="B34" s="7" t="str">
-        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
-      </x:c>
-      <x:c r="C34" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D34" s="7" t="str">
-        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
-      </x:c>
-      <x:c r="E34" s="7" t="str">
-        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="d">
-        <x:v>2026-09-27T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G34" s="7" t="str">
-        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
-      </x:c>
-      <x:c r="H34" s="16" t="str"/>
-    </x:row>
-    <x:row r="35" ht="92" customHeight="1">
-      <x:c r="A35" s="7" t="str">
-        <x:v>CA-031.02</x:v>
-      </x:c>
-      <x:c r="B35" s="7" t="str">
-        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
-      </x:c>
-      <x:c r="C35" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="str">
-        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
-      </x:c>
-      <x:c r="E35" s="7" t="str">
-        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="d">
-        <x:v>2026-09-26T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G35" s="7" t="str">
-        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
       </x:c>
       <x:c r="H35" s="16" t="str"/>
     </x:row>
     <x:row r="36" ht="92" customHeight="1">
       <x:c r="A36" s="7" t="str">
-        <x:v>CA-033.02</x:v>
+        <x:v>CA-030.02</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
-        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+        <x:v>综合楼与食堂入口角色尺寸通路检查</x:v>
       </x:c>
       <x:c r="C36" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D36" s="7" t="str">
-        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+        <x:v>两处入口各 4 条通路按角色宽约 70 cm、高约 180 cm 检查，未发现阻挡；门内外地面支撑正常并保存。证据为碰撞检查，未扩展为全校园行走验收。</x:v>
       </x:c>
       <x:c r="E36" s="7" t="str">
-        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+        <x:v>入口或地面变化后复查通道宽高和地面支撑。</x:v>
       </x:c>
       <x:c r="F36" s="14" t="d">
         <x:v>2026-09-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G36" s="7" t="str">
-        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+        <x:v>入口移除聊天最终碰撞与支撑验证</x:v>
       </x:c>
       <x:c r="H36" s="16" t="str"/>
     </x:row>
     <x:row r="37" ht="92" customHeight="1">
       <x:c r="A37" s="7" t="str">
+        <x:v>CA-031.02</x:v>
+      </x:c>
+      <x:c r="B37" s="7" t="str">
+        <x:v>Purple 修复截图中的建筑可见性恢复</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="str">
+        <x:v>编辑器 Game View 曾隐藏已有建筑组件；已从 true 恢复到 false，并用相同相机截图确认建筑立面完整。面部材质维持已保存的修复结果。</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="str">
+        <x:v>该截图视图问题已恢复；后续截图核对视图状态与相机，不将隐藏组件误判为资产丢失。</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>编辑器 Game View 恢复与同相机画面核对</x:v>
+      </x:c>
+      <x:c r="H37" s="16" t="str"/>
+    </x:row>
+    <x:row r="38" ht="92" customHeight="1">
+      <x:c r="A38" s="7" t="str">
+        <x:v>CA-033.02</x:v>
+      </x:c>
+      <x:c r="B38" s="7" t="str">
+        <x:v>Purple 身体恢复后 30 人待机和行走验收</x:v>
+      </x:c>
+      <x:c r="C38" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="str">
+        <x:v>聊天最终结果明确 UE 中 30 个 Purple 同步更新，完整身体恢复，待机和实际走路检查通过，修复结果已保存；这是该次有限范围验收。</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="str">
+        <x:v>不将该局部验收视为资产整理后的全校园回归；相关完整回归见 CA-010。</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>Purple 身体恢复最终交付与待机、行走效果图</x:v>
+      </x:c>
+      <x:c r="H38" s="16" t="str"/>
+    </x:row>
+    <x:row r="39" ht="92" customHeight="1">
+      <x:c r="A39" s="7" t="str">
         <x:v>CA-035.02</x:v>
       </x:c>
-      <x:c r="B37" s="7" t="str">
+      <x:c r="B39" s="7" t="str">
         <x:v>White 打开关卡与退出运行复发验收</x:v>
       </x:c>
-      <x:c r="C37" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D37" s="7" t="str">
+      <x:c r="C39" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D39" s="7" t="str">
         <x:v>map_opened 与 end_pie 均实际触发 refreshed：count=matched=30、skipped=0、positions_preserved=true；聊天最终确认重新打开及停止运行后正常站立。</x:v>
       </x:c>
-      <x:c r="E37" s="7" t="str">
+      <x:c r="E39" s="7" t="str">
         <x:v>本次覆盖保存、打开关卡与退出运行复发条件；未来初始化逻辑变化后按该范围回归。</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="d">
+      <x:c r="F39" s="14" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G37" s="7" t="str">
+      <x:c r="G39" s="7" t="str">
         <x:v>map_hook_verified、end_pie_verified 及最终截图交付</x:v>
       </x:c>
-      <x:c r="H37" s="16" t="str"/>
-    </x:row>
-    <x:row r="38" ht="109" customHeight="1">
-      <x:c r="A38" s="7" t="str">
+      <x:c r="H39" s="16" t="str"/>
+    </x:row>
+    <x:row r="40" ht="109" customHeight="1">
+      <x:c r="A40" s="7" t="str">
         <x:v>CA-038.02</x:v>
       </x:c>
-      <x:c r="B38" s="7" t="str">
+      <x:c r="B40" s="7" t="str">
         <x:v>scene 标准 Shipping 发布构建验收</x:v>
       </x:c>
-      <x:c r="C38" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D38" s="7" t="str">
+      <x:c r="C40" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="str">
         <x:v>保留10月3日副本完整发布及用户验收。10月4日原工程Win64 Shipping完整构建退出0，第一人称包D3D12启动响应、实际画面及退出0通过。10月5日脚本build-info再次succeeded，但该包运行验收独立见CA-065.04。</x:v>
       </x:c>
-      <x:c r="E38" s="7" t="str">
+      <x:c r="E40" s="7" t="str">
         <x:v>阶段构建验收已完成；新脚本包运行与最新白天修订同步分别判断。</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="d">
+      <x:c r="F40" s="14" t="d">
         <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G38" s="7" t="str">
+      <x:c r="G40" s="7" t="str">
         <x:v>原工程完整Shipping构建与版本化验收</x:v>
       </x:c>
-      <x:c r="H38" s="16" t="str"/>
-    </x:row>
-    <x:row r="39" ht="75" customHeight="1">
-      <x:c r="A39" s="7" t="str">
+      <x:c r="H40" s="16" t="str"/>
+    </x:row>
+    <x:row r="41" ht="75" customHeight="1">
+      <x:c r="A41" s="7" t="str">
         <x:v>CA-040.09</x:v>
       </x:c>
-      <x:c r="B39" s="7" t="str">
+      <x:c r="B41" s="7" t="str">
         <x:v>综合楼后方16处地面碰撞采样</x:v>
       </x:c>
-      <x:c r="C39" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D39" s="7" t="str">
+      <x:c r="C41" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="str">
         <x:v>validation 记录 16 处地面采样全部通过、errors 为空，新地表边界误差约 0.0011 cm；聊天确认园路连接后门及周边步道。</x:v>
       </x:c>
-      <x:c r="E39" s="7" t="str">
+      <x:c r="E41" s="7" t="str">
         <x:v>该阶段为点采样检查，不能替代 CA-040.10 的角色实走。</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G39" s="7" t="str">
-        <x:v>validation traces 16/16 与最终交付</x:v>
-      </x:c>
-      <x:c r="H39" s="16" t="str"/>
-    </x:row>
-    <x:row r="40" ht="75" customHeight="1">
-      <x:c r="A40" s="7" t="str">
-        <x:v>CA-041.03</x:v>
-      </x:c>
-      <x:c r="B40" s="7" t="str">
-        <x:v>scene远景设置保存与前景保护验收</x:v>
-      </x:c>
-      <x:c r="C40" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D40" s="7" t="str">
-        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
-      </x:c>
-      <x:c r="E40" s="7" t="str">
-        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G40" s="7" t="str">
-        <x:v>verification 设置保存与前景、源资产校验</x:v>
-      </x:c>
-      <x:c r="H40" s="16" t="str"/>
-    </x:row>
-    <x:row r="41" ht="92" customHeight="1">
-      <x:c r="A41" s="7" t="str">
-        <x:v>CA-043.05</x:v>
-      </x:c>
-      <x:c r="B41" s="7" t="str">
-        <x:v>校园风动保存与实例合批完整性</x:v>
-      </x:c>
-      <x:c r="C41" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D41" s="7" t="str">
-        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
-      </x:c>
-      <x:c r="E41" s="7" t="str">
-        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
       </x:c>
       <x:c r="F41" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G41" s="7" t="str">
-        <x:v>风动保存回读与合批检查</x:v>
+        <x:v>validation traces 16/16 与最终交付</x:v>
       </x:c>
       <x:c r="H41" s="16" t="str"/>
     </x:row>
     <x:row r="42" ht="75" customHeight="1">
       <x:c r="A42" s="7" t="str">
-        <x:v>CA-044.03</x:v>
+        <x:v>CA-041.03</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
-        <x:v>跑道花坛修复碰撞与保存验收</x:v>
+        <x:v>scene远景设置保存与前景保护验收</x:v>
       </x:c>
       <x:c r="C42" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D42" s="7" t="str">
-        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
+        <x:v>保存后回读188个目标组件，19个排除范围组件和66个源网格资产保持原设置；错误、脏地图和脏资产列表为空。</x:v>
       </x:c>
       <x:c r="E42" s="7" t="str">
-        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
+        <x:v>验收覆盖设置持久化及排除范围保护；不代表渲染警告、显示帧率或整体性能目标已通过。</x:v>
       </x:c>
       <x:c r="F42" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G42" s="7" t="str">
-        <x:v>verification_report与最终保存交付</x:v>
+        <x:v>verification 设置保存与前景、源资产校验</x:v>
       </x:c>
       <x:c r="H42" s="16" t="str"/>
     </x:row>
     <x:row r="43" ht="92" customHeight="1">
       <x:c r="A43" s="7" t="str">
-        <x:v>CA-045.04</x:v>
+        <x:v>CA-043.05</x:v>
       </x:c>
       <x:c r="B43" s="7" t="str">
-        <x:v>第一第三人称手柄模拟输入验收</x:v>
+        <x:v>校园风动保存与实例合批完整性</x:v>
       </x:c>
       <x:c r="C43" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D43" s="7" t="str">
-        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
+        <x:v>1,009组件、22,094植被实例覆盖完成；168材质版本、82主材质编译通过，392固定槽不变。保存检查保留9,409批次和104,618实例，合批语义11项检查通过。</x:v>
       </x:c>
       <x:c r="E43" s="7" t="str">
-        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
+        <x:v>覆盖校园可见植被，隐藏归档及校外远景不在范围内。</x:v>
       </x:c>
       <x:c r="F43" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G43" s="7" t="str">
-        <x:v>模拟输入记录与用户新版验收</x:v>
+        <x:v>风动保存回读与合批检查</x:v>
       </x:c>
       <x:c r="H43" s="16" t="str"/>
     </x:row>
-    <x:row r="44" ht="92" customHeight="1">
+    <x:row r="44" ht="75" customHeight="1">
       <x:c r="A44" s="7" t="str">
-        <x:v>CA-046.05</x:v>
+        <x:v>CA-044.03</x:v>
       </x:c>
       <x:c r="B44" s="7" t="str">
-        <x:v>150人及最终天气版本Shipping构建</x:v>
+        <x:v>跑道花坛修复碰撞与保存验收</x:v>
       </x:c>
       <x:c r="C44" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D44" s="7" t="str">
-        <x:v>150人10月6日10:57交付后11:00–11:07完整Shipping成功；最终天气15:40交付后17:47–17:54再构建成功，build-info指向原工程scene，exe存在。</x:v>
+        <x:v>网格边界与朝向检查通过；简单和复杂碰撞采样、原视角及俯视确认后完成保存，verification success=true。</x:v>
       </x:c>
       <x:c r="E44" s="7" t="str">
-        <x:v>构建成功不等于成品玩法、实际帧率或长时天气验收，见CA-065.04。</x:v>
+        <x:v>该项覆盖花坛修复局部验收，不等于全校园通行。</x:v>
       </x:c>
       <x:c r="F44" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G44" s="7" t="str">
-        <x:v>后续完整构建状态与版本时序</x:v>
+        <x:v>verification_report与最终保存交付</x:v>
       </x:c>
       <x:c r="H44" s="16" t="str"/>
     </x:row>
     <x:row r="45" ht="92" customHeight="1">
       <x:c r="A45" s="7" t="str">
-        <x:v>CA-046.06</x:v>
+        <x:v>CA-045.04</x:v>
       </x:c>
       <x:c r="B45" s="7" t="str">
-        <x:v>五栋楼开关与晴雨修订后Shipping构建</x:v>
+        <x:v>第一第三人称手柄模拟输入验收</x:v>
       </x:c>
       <x:c r="C45" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D45" s="7" t="str">
-        <x:v>原工程scene于10月8日23:54至10月9日00:03完整Shipping构建succeeded，晚于开关和晴空恢复交付；exe路径有效。该包早于10月9日食堂写实改造。</x:v>
+        <x:v>初版36项模拟输入通过；反转修订后第一、第三人称各16项通过。迁移测试使用NullRHI，实体手柄未由自动化实测；用户随后确认新版验证通过。</x:v>
       </x:c>
       <x:c r="E45" s="7" t="str">
-        <x:v>仅确认构建时序，不能认定包含后续食堂材质；具体包实际运行见CA-065.04。</x:v>
+        <x:v>保留模拟输入与用户验收范围，不推断实体硬件逐项覆盖。</x:v>
       </x:c>
       <x:c r="F45" s="14" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G45" s="7" t="str">
-        <x:v>新build-info成功状态与交付时序</x:v>
+        <x:v>模拟输入记录与用户新版验收</x:v>
       </x:c>
       <x:c r="H45" s="16" t="str"/>
     </x:row>
     <x:row r="46" ht="92" customHeight="1">
       <x:c r="A46" s="7" t="str">
+        <x:v>CA-046.05</x:v>
+      </x:c>
+      <x:c r="B46" s="7" t="str">
+        <x:v>150人及最终天气版本Shipping构建</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="str">
+        <x:v>150人10月6日10:57交付后11:00–11:07完整Shipping成功；最终天气15:40交付后17:47–17:54再构建成功，build-info指向原工程scene，exe存在。</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="str">
+        <x:v>构建成功不等于成品玩法、实际帧率或长时天气验收，见CA-065.04。</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>后续完整构建状态与版本时序</x:v>
+      </x:c>
+      <x:c r="H46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="92" customHeight="1">
+      <x:c r="A47" s="7" t="str">
+        <x:v>CA-046.06</x:v>
+      </x:c>
+      <x:c r="B47" s="7" t="str">
+        <x:v>五栋楼开关与晴雨修订后Shipping构建</x:v>
+      </x:c>
+      <x:c r="C47" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="str">
+        <x:v>原工程scene于10月8日23:54至10月9日00:03完整Shipping构建succeeded，晚于开关和晴空恢复交付；exe路径有效。该包早于10月9日食堂写实改造。</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="str">
+        <x:v>仅确认构建时序，不能认定包含后续食堂材质；具体包实际运行见CA-065.04。</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
+        <x:v>新build-info成功状态与交付时序</x:v>
+      </x:c>
+      <x:c r="H47" s="16" t="str"/>
+    </x:row>
+    <x:row r="48" ht="109" customHeight="1">
+      <x:c r="A48" s="7" t="str">
+        <x:v>CA-046.07</x:v>
+      </x:c>
+      <x:c r="B48" s="7" t="str">
+        <x:v>全场铺装统一后Shipping构建</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="str">
+        <x:v>2026-10-09 22:31至22:37原工程scene Win64 Shipping完整build/cook/stage/package成功，exe有效。时间晚于全场铺装渐干交付，早于灯光修复。两包均早于10月10日教室合并与室内重做。</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="str">
+        <x:v>只确认构建及先后范围；具体包实际运行仍见CA-065.04，不能凭构建时间声称功能全部实机通过。</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
+        <x:v>build-info succeeded及可执行文件检查</x:v>
+      </x:c>
+      <x:c r="H48" s="16" t="str"/>
+    </x:row>
+    <x:row r="49" ht="109" customHeight="1">
+      <x:c r="A49" s="7" t="str">
+        <x:v>CA-046.08</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="str">
+        <x:v>DualSense与补灯修复后Shipping构建</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="str">
+        <x:v>2026-10-09 23:50至23:56原工程scene Win64 Shipping完整build/cook/stage/package成功，exe有效。时间晚于PS5和补灯交付，并发现GameInputRedist安装包。两包均早于10月10日教室合并与室内重做。</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="str">
+        <x:v>只确认构建及先后范围；具体包实际运行仍见CA-065.04，不能凭构建时间声称功能全部实机通过。</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>build-info succeeded及可执行文件检查</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="92" customHeight="1">
+      <x:c r="A50" s="7" t="str">
         <x:v>CA-047.03</x:v>
       </x:c>
-      <x:c r="B46" s="7" t="str">
+      <x:c r="B50" s="7" t="str">
         <x:v>食堂两侧一至二层真实往返验收</x:v>
       </x:c>
-      <x:c r="C46" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D46" s="7" t="str">
+      <x:c r="C50" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="str">
         <x:v>东西两路各10端点完整往返passed=true，真实第一人称add_movement_input；仅起点定位，无跳跃、飞行或移动参数改动。后续White上楼复测亦通过。</x:v>
       </x:c>
-      <x:c r="E46" s="7" t="str">
+      <x:c r="E50" s="7" t="str">
         <x:v>本项为食堂楼梯路线，不替代其他建筑或全场回归。</x:v>
       </x:c>
-      <x:c r="F46" s="14" t="d">
+      <x:c r="F50" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G46" s="7" t="str">
+      <x:c r="G50" s="7" t="str">
         <x:v>playtest_final与White校园路线</x:v>
       </x:c>
-      <x:c r="H46" s="16" t="str"/>
-    </x:row>
-    <x:row r="47" ht="75" customHeight="1">
-      <x:c r="A47" s="7" t="str">
+      <x:c r="H50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="75" customHeight="1">
+      <x:c r="A51" s="7" t="str">
         <x:v>CA-048.02</x:v>
       </x:c>
-      <x:c r="B47" s="7" t="str">
+      <x:c r="B51" s="7" t="str">
         <x:v>行政楼植被清理重载与保留位置验收</x:v>
       </x:c>
-      <x:c r="C47" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D47" s="7" t="str">
+      <x:c r="C51" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="str">
         <x:v>重载检查138,397静态组件组，楼内残留为空，剩余变换符合预期，errors与dirty_maps为空，备份已保留。</x:v>
       </x:c>
-      <x:c r="E47" s="7" t="str">
+      <x:c r="E51" s="7" t="str">
         <x:v>该检查不替代行政庭院角色通行CA-029。</x:v>
       </x:c>
-      <x:c r="F47" s="14" t="d">
+      <x:c r="F51" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G47" s="7" t="str">
+      <x:c r="G51" s="7" t="str">
         <x:v>reload_verification与重载效果</x:v>
       </x:c>
-      <x:c r="H47" s="16" t="str"/>
-    </x:row>
-    <x:row r="48" ht="75" customHeight="1">
-      <x:c r="A48" s="7" t="str">
+      <x:c r="H51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="75" customHeight="1">
+      <x:c r="A52" s="7" t="str">
         <x:v>CA-052.06</x:v>
       </x:c>
-      <x:c r="B48" s="7" t="str">
+      <x:c r="B52" s="7" t="str">
         <x:v>White十九组高度与蒙皮接触验收</x:v>
       </x:c>
-      <x:c r="C48" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D48" s="7" t="str">
+      <x:c r="C52" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="str">
         <x:v>19组真实碰撞样例通过，覆盖0.5–300cm、臀高临界及旋转/缩放；6,534帧、552蒙皮采样，座面最大误差0.103cm，背部0.0008cm。</x:v>
       </x:c>
-      <x:c r="E48" s="7" t="str">
+      <x:c r="E52" s="7" t="str">
         <x:v>只覆盖有限样例和选定接触点；不能保证任意高度拓扑都适合坐下。</x:v>
       </x:c>
-      <x:c r="F48" s="14" t="d">
+      <x:c r="F52" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G48" s="7" t="str">
+      <x:c r="G52" s="7" t="str">
         <x:v>qa_final_summary高度与接触结果</x:v>
-      </x:c>
-      <x:c r="H48" s="16" t="str"/>
-    </x:row>
-    <x:row r="49" ht="75" customHeight="1">
-      <x:c r="A49" s="7" t="str">
-        <x:v>CA-052.07</x:v>
-      </x:c>
-      <x:c r="B49" s="7" t="str">
-        <x:v>White自动休息冷却与中断恢复验收</x:v>
-      </x:c>
-      <x:c r="C49" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D49" s="7" t="str">
-        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
-      </x:c>
-      <x:c r="E49" s="7" t="str">
-        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
-      </x:c>
-      <x:c r="F49" s="14" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G49" s="7" t="str">
-        <x:v>qa_final_summary行为结果</x:v>
-      </x:c>
-      <x:c r="H49" s="16" t="str"/>
-    </x:row>
-    <x:row r="50" ht="75" customHeight="1">
-      <x:c r="A50" s="7" t="str">
-        <x:v>CA-052.08</x:v>
-      </x:c>
-      <x:c r="B50" s="7" t="str">
-        <x:v>White不安全休息表面拒绝验收</x:v>
-      </x:c>
-      <x:c r="C50" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D50" s="7" t="str">
-        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
-      </x:c>
-      <x:c r="E50" s="7" t="str">
-        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
-      </x:c>
-      <x:c r="F50" s="14" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G50" s="7" t="str">
-        <x:v>表面安全测试与限制</x:v>
-      </x:c>
-      <x:c r="H50" s="16" t="str"/>
-    </x:row>
-    <x:row r="51" ht="92" customHeight="1">
-      <x:c r="A51" s="7" t="str">
-        <x:v>CA-053.06</x:v>
-      </x:c>
-      <x:c r="B51" s="7" t="str">
-        <x:v>White完整体力循环与座位异常验收</x:v>
-      </x:c>
-      <x:c r="C51" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D51" s="7" t="str">
-        <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
-      </x:c>
-      <x:c r="E51" s="7" t="str">
-        <x:v>保留该阶段临时角色验收；最新150人休息抽查2人通过、1人超时，见CA-072.05。</x:v>
-      </x:c>
-      <x:c r="F51" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G51" s="7" t="str">
-        <x:v>qa_stamina_result与最终交付</x:v>
-      </x:c>
-      <x:c r="H51" s="16" t="str"/>
-    </x:row>
-    <x:row r="52" ht="92" customHeight="1">
-      <x:c r="A52" s="7" t="str">
-        <x:v>CA-053.09</x:v>
-      </x:c>
-      <x:c r="B52" s="7" t="str">
-        <x:v>唯一White十二条跨校园实走验收</x:v>
-      </x:c>
-      <x:c r="C52" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D52" s="7" t="str">
-        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
-      </x:c>
-      <x:c r="E52" s="7" t="str">
-        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
-      </x:c>
-      <x:c r="F52" s="14" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G52" s="7" t="str">
-        <x:v>suite_result与final_result</x:v>
       </x:c>
       <x:c r="H52" s="16" t="str"/>
     </x:row>
     <x:row r="53" ht="75" customHeight="1">
       <x:c r="A53" s="7" t="str">
-        <x:v>CA-053.10</x:v>
+        <x:v>CA-052.07</x:v>
       </x:c>
       <x:c r="B53" s="7" t="str">
-        <x:v>White全校园随机选点覆盖抽样</x:v>
+        <x:v>White自动休息冷却与中断恢复验收</x:v>
       </x:c>
       <x:c r="C53" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D53" s="7" t="str">
-        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
+        <x:v>4组行为测试通过：自动触发、待机后起身、冷却再次触发、入座中断及支撑物删除/移动后的取消恢复。</x:v>
       </x:c>
       <x:c r="E53" s="7" t="str">
-        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
+        <x:v>体力模式满值起身和续行另见CA-053.06、CA-053.09。</x:v>
       </x:c>
       <x:c r="F53" s="14" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G53" s="7" t="str">
-        <x:v>final_result随机覆盖与解释</x:v>
+        <x:v>qa_final_summary行为结果</x:v>
       </x:c>
       <x:c r="H53" s="16" t="str"/>
     </x:row>
-    <x:row r="54" ht="92" customHeight="1">
+    <x:row r="54" ht="75" customHeight="1">
       <x:c r="A54" s="7" t="str">
-        <x:v>CA-054.02</x:v>
+        <x:v>CA-052.08</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
-        <x:v>唯一White与观察入口阶段运行验收</x:v>
+        <x:v>White不安全休息表面拒绝验收</x:v>
       </x:c>
       <x:c r="C54" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D54" s="7" t="str">
-        <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
+        <x:v>6组表面测试通过：无碰撞、NoRest、过窄低座、已占用和无脚下支撑拒绝；10cm厚高墙可进入倚靠。36项保护资产哈希一致。</x:v>
       </x:c>
       <x:c r="E54" s="7" t="str">
-        <x:v>本项保留人数精简和观察入口阶段验收；当前学生人数见CA-002、第一人称入口见CA-055。</x:v>
+        <x:v>不足0.5cm按地面处理，高座双脚可悬垂，不伸长肢体强行落地。</x:v>
       </x:c>
       <x:c r="F54" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
+        <x:v>表面安全测试与限制</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str"/>
+    </x:row>
+    <x:row r="55" ht="92" customHeight="1">
+      <x:c r="A55" s="7" t="str">
+        <x:v>CA-053.06</x:v>
+      </x:c>
+      <x:c r="B55" s="7" t="str">
+        <x:v>White完整体力循环与座位异常验收</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D55" s="7" t="str">
+        <x:v>实际scene临时测试White走到真实长椅、坐稳回满并恢复行走；最近座位被占用、目标失效三案例valid=true，C++座位预约测试及花坛旁4长椅实测通过。</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="str">
+        <x:v>保留该阶段临时角色验收；最新150人休息抽查2人通过、1人超时，见CA-072.05。</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="d">
         <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G54" s="7" t="str">
-        <x:v>原观察验证与后续第一人称运行结果</x:v>
-      </x:c>
-      <x:c r="H54" s="16" t="str"/>
-    </x:row>
-    <x:row r="55" ht="109" customHeight="1">
-      <x:c r="A55" s="7" t="str">
-        <x:v>CA-055</x:v>
-      </x:c>
-      <x:c r="B55" s="7" t="str">
-        <x:v>第一人称默认出生与十五项运行验收</x:v>
-      </x:c>
-      <x:c r="C55" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D55" s="7" t="str">
-        <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
-      </x:c>
-      <x:c r="E55" s="7" t="str">
-        <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
-      </x:c>
-      <x:c r="F55" s="14" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
-      </x:c>
       <x:c r="G55" s="7" t="str">
-        <x:v>startup_runtime_report与新包画面</x:v>
+        <x:v>qa_stamina_result与最终交付</x:v>
       </x:c>
       <x:c r="H55" s="16" t="str"/>
     </x:row>
-    <x:row r="56" ht="75" customHeight="1">
+    <x:row r="56" ht="92" customHeight="1">
       <x:c r="A56" s="7" t="str">
-        <x:v>CA-056.02</x:v>
+        <x:v>CA-053.09</x:v>
       </x:c>
       <x:c r="B56" s="7" t="str">
-        <x:v>高三楼门三百二十八项运行验收</x:v>
+        <x:v>唯一White十二条跨校园实走验收</x:v>
       </x:c>
       <x:c r="C56" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D56" s="7" t="str">
-        <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
+        <x:v>12条真实行走全部通过：教室门、食堂、综合楼五层、两教学楼到教师楼四层、休息续行、北区宿舍及宿舍/高三楼五层往返。临时3倍时间测试后恢复正常参数。</x:v>
       </x:c>
       <x:c r="E56" s="7" t="str">
-        <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
+        <x:v>不代表所有校园道路逐条通过，湖畔副楼仅确认一楼。</x:v>
       </x:c>
       <x:c r="F56" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G56" s="7" t="str">
-        <x:v>runtime_verification与completion</x:v>
+        <x:v>suite_result与final_result</x:v>
       </x:c>
       <x:c r="H56" s="16" t="str"/>
     </x:row>
-    <x:row r="57" ht="58" customHeight="1">
+    <x:row r="57" ht="75" customHeight="1">
       <x:c r="A57" s="7" t="str">
-        <x:v>CA-056.03</x:v>
+        <x:v>CA-053.10</x:v>
       </x:c>
       <x:c r="B57" s="7" t="str">
-        <x:v>高三门保存回读与原门保护验收</x:v>
+        <x:v>White全校园随机选点覆盖抽样</x:v>
       </x:c>
       <x:c r="C57" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D57" s="7" t="str">
-        <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
+        <x:v>正常时间32次原生随机目标均完整路径且超旧16米出生半径，14个北区、9个高Z位置；路径37.7–420.3米，未传送或写内部目标状态。</x:v>
       </x:c>
       <x:c r="E57" s="7" t="str">
-        <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
+        <x:v>Z高度为抽样指标，不能替代具体建筑楼梯实走。</x:v>
       </x:c>
       <x:c r="F57" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G57" s="7" t="str">
-        <x:v>persisted_verification</x:v>
+        <x:v>final_result随机覆盖与解释</x:v>
       </x:c>
       <x:c r="H57" s="16" t="str"/>
     </x:row>
-    <x:row r="58" ht="75" customHeight="1">
+    <x:row r="58" ht="92" customHeight="1">
       <x:c r="A58" s="7" t="str">
-        <x:v>CA-057.04</x:v>
+        <x:v>CA-054.02</x:v>
       </x:c>
       <x:c r="B58" s="7" t="str">
-        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
+        <x:v>唯一White与观察入口阶段运行验收</x:v>
       </x:c>
       <x:c r="C58" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D58" s="7" t="str">
-        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
+        <x:v>人数精简时正常PIE确认单White、108座椅及观察移动通过。后续第一人称验收确认White与座椅仍保留，玩家控制BP_FirstPersonCharacter；旧观察测试只作为阶段历史。</x:v>
       </x:c>
       <x:c r="E58" s="7" t="str">
-        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
+        <x:v>本项保留人数精简和观察入口阶段验收；当前学生人数见CA-002、第一人称入口见CA-055。</x:v>
       </x:c>
       <x:c r="F58" s="14" t="d">
-        <x:v>2026-10-04T00:00:00.000Z</x:v>
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G58" s="7" t="str">
-        <x:v>V2 verification</x:v>
+        <x:v>原观察验证与后续第一人称运行结果</x:v>
       </x:c>
       <x:c r="H58" s="16" t="str"/>
     </x:row>
-    <x:row r="59" ht="75" customHeight="1">
+    <x:row r="59" ht="109" customHeight="1">
       <x:c r="A59" s="7" t="str">
-        <x:v>CA-058.03</x:v>
+        <x:v>CA-055</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
-        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
+        <x:v>第一人称默认出生与十五项运行验收</x:v>
       </x:c>
       <x:c r="C59" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D59" s="7" t="str">
-        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
+        <x:v>实际scene默认出生控制BP_FirstPersonCharacter，15项控制/相机、WASD碰撞移动、跳跃落地和AI/座椅检查通过，cleanup_passed=true。视角调用原生DoLook，未实测实体输入或鼠标映射。</x:v>
       </x:c>
       <x:c r="E59" s="7" t="str">
-        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
+        <x:v>保留局部输入验收范围；全校连续回归见CA-010.02。</x:v>
       </x:c>
       <x:c r="F59" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G59" s="7" t="str">
-        <x:v>遮阳棚verification</x:v>
+        <x:v>startup_runtime_report与新包画面</x:v>
       </x:c>
       <x:c r="H59" s="16" t="str"/>
     </x:row>
-    <x:row r="60" ht="58" customHeight="1">
+    <x:row r="60" ht="75" customHeight="1">
       <x:c r="A60" s="7" t="str">
-        <x:v>CA-059.03</x:v>
+        <x:v>CA-056.02</x:v>
       </x:c>
       <x:c r="B60" s="7" t="str">
-        <x:v>棕榈落地树干碰撞与通道检查</x:v>
+        <x:v>高三楼门三百二十八项运行验收</x:v>
       </x:c>
       <x:c r="C60" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D60" s="7" t="str">
-        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
+        <x:v>328项运行检查通过，runtime/interaction_passed=true，errors为空，玩家和QA设置已恢复。</x:v>
       </x:c>
       <x:c r="E60" s="7" t="str">
-        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
+        <x:v>范围为高三新增门交互；不替代全校园连续实走或实体手柄测试。</x:v>
       </x:c>
       <x:c r="F60" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G60" s="7" t="str">
-        <x:v>palms_verification</x:v>
+        <x:v>runtime_verification与completion</x:v>
       </x:c>
       <x:c r="H60" s="16" t="str"/>
     </x:row>
-    <x:row r="61" ht="75" customHeight="1">
+    <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" s="7" t="str">
-        <x:v>CA-060.03</x:v>
+        <x:v>CA-056.03</x:v>
       </x:c>
       <x:c r="B61" s="7" t="str">
-        <x:v>校训朝向字距屋顶贴合检查</x:v>
+        <x:v>高三门保存回读与原门保护验收</x:v>
       </x:c>
       <x:c r="C61" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D61" s="7" t="str">
-        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
+        <x:v>保存回读passed=true，120门扇/114控制器/252活动部件保持；原185控制器未改变。</x:v>
       </x:c>
       <x:c r="E61" s="7" t="str">
-        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
+        <x:v>后续改门时复核转轴、联动和现有门保护。</x:v>
       </x:c>
       <x:c r="F61" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G61" s="7" t="str">
-        <x:v>verification与final_save</x:v>
+        <x:v>persisted_verification</x:v>
       </x:c>
       <x:c r="H61" s="16" t="str"/>
     </x:row>
     <x:row r="62" ht="75" customHeight="1">
       <x:c r="A62" s="7" t="str">
-        <x:v>CA-061.02</x:v>
+        <x:v>CA-057.04</x:v>
       </x:c>
       <x:c r="B62" s="7" t="str">
-        <x:v>大纲整理场景属性与实例保护验收</x:v>
+        <x:v>长廊第二版三十八项尺寸通行检查</x:v>
       </x:c>
       <x:c r="C62" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D62" s="7" t="str">
-        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+        <x:v>V2 verification为38/38 passed，覆盖纵向与横向通路、齐平地面及尺寸。记录为数值/碰撞探测，不扩展为完整角色实走。</x:v>
       </x:c>
       <x:c r="E62" s="7" t="str">
-        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+        <x:v>全场路线验收仍独立见CA-010.02。</x:v>
       </x:c>
       <x:c r="F62" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G62" s="7" t="str">
-        <x:v>大纲verification</x:v>
+        <x:v>V2 verification</x:v>
       </x:c>
       <x:c r="H62" s="16" t="str"/>
     </x:row>
     <x:row r="63" ht="75" customHeight="1">
       <x:c r="A63" s="7" t="str">
-        <x:v>CA-063.05</x:v>
+        <x:v>CA-058.03</x:v>
       </x:c>
       <x:c r="B63" s="7" t="str">
-        <x:v>参考夜景保存与模拟运行检查</x:v>
+        <x:v>遮阳棚台面通路与旗杆间距检查</x:v>
       </x:c>
       <x:c r="C63" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D63" s="7" t="str">
-        <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
+        <x:v>导入部件、柱脚贴合、棚下通路、实体屋顶和柱碰撞检查passed，旗杆间隙约27.5cm，dirty_map_packages为空。</x:v>
       </x:c>
       <x:c r="E63" s="7" t="str">
-        <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
+        <x:v>记录为指定位置碰撞检查，不宣称全场角色通行。</x:v>
       </x:c>
       <x:c r="F63" s="14" t="d">
         <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G63" s="7" t="str">
+        <x:v>遮阳棚verification</x:v>
+      </x:c>
+      <x:c r="H63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="58" customHeight="1">
+      <x:c r="A64" s="7" t="str">
+        <x:v>CA-059.03</x:v>
+      </x:c>
+      <x:c r="B64" s="7" t="str">
+        <x:v>棕榈落地树干碰撞与通道检查</x:v>
+      </x:c>
+      <x:c r="C64" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="str">
+        <x:v>根部落地、树干碰撞、纵横通道检查全部passed，level_saved=true且dirty_maps为空。</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="str">
+        <x:v>指定射线和位置检查不等同所有角色路线验收。</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
+        <x:v>palms_verification</x:v>
+      </x:c>
+      <x:c r="H64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65" ht="75" customHeight="1">
+      <x:c r="A65" s="7" t="str">
+        <x:v>CA-060.03</x:v>
+      </x:c>
+      <x:c r="B65" s="7" t="str">
+        <x:v>校训朝向字距屋顶贴合检查</x:v>
+      </x:c>
+      <x:c r="C65" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="str">
+        <x:v>最终朝向、字距和屋顶贴合完成检查，新增8个Actor，原138484个Actor保留，geometry_closed=true。</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="str">
+        <x:v>后续调整检查文字朝向与屋顶贴合。</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G65" s="7" t="str">
+        <x:v>verification与final_save</x:v>
+      </x:c>
+      <x:c r="H65" s="16" t="str"/>
+    </x:row>
+    <x:row r="66" ht="75" customHeight="1">
+      <x:c r="A66" s="7" t="str">
+        <x:v>CA-061.02</x:v>
+      </x:c>
+      <x:c r="B66" s="7" t="str">
+        <x:v>大纲整理场景属性与实例保护验收</x:v>
+      </x:c>
+      <x:c r="C66" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="str">
+        <x:v>138492 Actor前后数一致，added/removed/non_folder_changes为空，9374自动实例组全部复用。位置、父子、显示和碰撞未改变。</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="str">
+        <x:v>无变化同步耗141.98秒属于操作样本，等待优化另见CA-032.03。</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G66" s="7" t="str">
+        <x:v>大纲verification</x:v>
+      </x:c>
+      <x:c r="H66" s="16" t="str"/>
+    </x:row>
+    <x:row r="67" ht="75" customHeight="1">
+      <x:c r="A67" s="7" t="str">
+        <x:v>CA-063.05</x:v>
+      </x:c>
+      <x:c r="B67" s="7" t="str">
+        <x:v>参考夜景保存与模拟运行检查</x:v>
+      </x:c>
+      <x:c r="C67" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D67" s="7" t="str">
+        <x:v>scene保存，Simulate确认74新灯、41灯具、固定曝光和对象可见激活；先前预览显存崩溃已恢复，效果图交付。</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="str">
+        <x:v>这是夜景运行与保存检查，实际帧耗/显存余量未验，见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G67" s="7" t="str">
         <x:v>final_verified与runtime_verified</x:v>
       </x:c>
-      <x:c r="H63" s="16" t="str"/>
-    </x:row>
-    <x:row r="64" ht="92" customHeight="1">
-      <x:c r="A64" s="7" t="str">
+      <x:c r="H67" s="16" t="str"/>
+    </x:row>
+    <x:row r="68" ht="92" customHeight="1">
+      <x:c r="A68" s="7" t="str">
         <x:v>CA-064.07</x:v>
       </x:c>
-      <x:c r="B64" s="7" t="str">
+      <x:c r="B68" s="7" t="str">
         <x:v>三轮昼夜切换原夜景参数还原</x:v>
       </x:c>
-      <x:c r="C64" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D64" s="7" t="str">
+      <x:c r="C68" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D68" s="7" t="str">
         <x:v>初版三轮昼夜300灯精确还原保留。最新黄昏检查17:00至22:00各阶段，22:00全部300灯恢复原亮度，night_restored_exactly=true；正午零灯规则仍通过。</x:v>
       </x:c>
-      <x:c r="E64" s="7" t="str">
+      <x:c r="E68" s="7" t="str">
         <x:v>原夜空已因月升月落按用户要求修改，不再声称当前夜空shader与旧版完全一致；只认定各阶段参数验收。</x:v>
-      </x:c>
-      <x:c r="F64" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G64" s="7" t="str">
-        <x:v>Daylight scene_verified三轮结果</x:v>
-      </x:c>
-      <x:c r="H64" s="16" t="str"/>
-    </x:row>
-    <x:row r="65" ht="92" customHeight="1">
-      <x:c r="A65" s="7" t="str">
-        <x:v>CA-064.08</x:v>
-      </x:c>
-      <x:c r="B65" s="7" t="str">
-        <x:v>当前昼夜十六项自动化环境回归</x:v>
-      </x:c>
-      <x:c r="C65" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D65" s="7" t="str">
-        <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
-      </x:c>
-      <x:c r="E65" s="7" t="str">
-        <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
-      </x:c>
-      <x:c r="F65" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G65" s="7" t="str">
-        <x:v>最新自动化index与最终聊天</x:v>
-      </x:c>
-      <x:c r="H65" s="16" t="str"/>
-    </x:row>
-    <x:row r="66" ht="109" customHeight="1">
-      <x:c r="A66" s="7" t="str">
-        <x:v>CA-065.03</x:v>
-      </x:c>
-      <x:c r="B66" s="7" t="str">
-        <x:v>一键脚本原工程完整构建交付</x:v>
-      </x:c>
-      <x:c r="C66" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D66" s="7" t="str">
-        <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
-      </x:c>
-      <x:c r="E66" s="7" t="str">
-        <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
-      </x:c>
-      <x:c r="F66" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G66" s="7" t="str">
-        <x:v>ScenePackages build-info实际成功记录</x:v>
-      </x:c>
-      <x:c r="H66" s="16" t="str"/>
-    </x:row>
-    <x:row r="67" ht="92" customHeight="1">
-      <x:c r="A67" s="7" t="str">
-        <x:v>CA-066.02</x:v>
-      </x:c>
-      <x:c r="B67" s="7" t="str">
-        <x:v>时间面板调时暂停与保存基准检查</x:v>
-      </x:c>
-      <x:c r="C67" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D67" s="7" t="str">
-        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
-      </x:c>
-      <x:c r="E67" s="7" t="str">
-        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
-      </x:c>
-      <x:c r="F67" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G67" s="7" t="str">
-        <x:v>面板实操及夜景恢复检查</x:v>
-      </x:c>
-      <x:c r="H67" s="16" t="str"/>
-    </x:row>
-    <x:row r="68" ht="75" customHeight="1">
-      <x:c r="A68" s="7" t="str">
-        <x:v>CA-068.02</x:v>
-      </x:c>
-      <x:c r="B68" s="7" t="str">
-        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
-      </x:c>
-      <x:c r="C68" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D68" s="7" t="str">
-        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
-      </x:c>
-      <x:c r="E68" s="7" t="str">
-        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
       </x:c>
       <x:c r="F68" s="14" t="d">
         <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G68" s="7" t="str">
-        <x:v>月亮运行796帧与重载报告</x:v>
+        <x:v>Daylight scene_verified三轮结果</x:v>
       </x:c>
       <x:c r="H68" s="16" t="str"/>
     </x:row>
-    <x:row r="69" ht="75" customHeight="1">
+    <x:row r="69" ht="92" customHeight="1">
       <x:c r="A69" s="7" t="str">
-        <x:v>CA-070.04</x:v>
+        <x:v>CA-064.08</x:v>
       </x:c>
       <x:c r="B69" s="7" t="str">
-        <x:v>教学楼材质合批镜像与门结构保持</x:v>
+        <x:v>当前昼夜十六项自动化环境回归</x:v>
       </x:c>
       <x:c r="C69" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D69" s="7" t="str">
-        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
+        <x:v>阶段9项、时间面板12项、月亮15项均保留。最新黄昏回归passed16、failed0、skipped0，覆盖时钟、预算、月亮、预览恢复与日落连续性。</x:v>
       </x:c>
       <x:c r="E69" s="7" t="str">
-        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
+        <x:v>测试在编辑器进行；当前发布及成品运行分别见CA-046.04、CA-065.04。</x:v>
       </x:c>
       <x:c r="F69" s="14" t="d">
         <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G69" s="7" t="str">
-        <x:v>真实材质与纯色门结构验证</x:v>
+        <x:v>最新自动化index与最终聊天</x:v>
       </x:c>
       <x:c r="H69" s="16" t="str"/>
     </x:row>
-    <x:row r="70" ht="92" customHeight="1">
+    <x:row r="70" ht="109" customHeight="1">
       <x:c r="A70" s="7" t="str">
-        <x:v>CA-071.05</x:v>
+        <x:v>CA-065.03</x:v>
       </x:c>
       <x:c r="B70" s="7" t="str">
-        <x:v>草地全量朝向坐标材质及保存检查</x:v>
+        <x:v>一键脚本原工程完整构建交付</x:v>
       </x:c>
       <x:c r="C70" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D70" s="7" t="str">
-        <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
+        <x:v>00:32–00:39首批原工程完整构建交付有效。新增09:52–10:02、11:47–11:54、16:37–16:45、18:16–18:23四批均succeeded，执行原工程Win64 Shipping build/cook/stage/package。</x:v>
       </x:c>
       <x:c r="E70" s="7" t="str">
-        <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
+        <x:v>记录仅证明构建与文件检查；成品实际运行仍见CA-065.04。</x:v>
       </x:c>
       <x:c r="F70" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G70" s="7" t="str">
-        <x:v>草地全量检查和67秒保存回执</x:v>
+        <x:v>ScenePackages build-info实际成功记录</x:v>
       </x:c>
       <x:c r="H70" s="16" t="str"/>
     </x:row>
     <x:row r="71" ht="92" customHeight="1">
       <x:c r="A71" s="7" t="str">
-        <x:v>CA-072.04</x:v>
+        <x:v>CA-066.02</x:v>
       </x:c>
       <x:c r="B71" s="7" t="str">
-        <x:v>150名White运行移动与行为保留</x:v>
+        <x:v>时间面板调时暂停与保存基准检查</x:v>
       </x:c>
       <x:c r="C71" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D71" s="7" t="str">
-        <x:v>运行全程150名White、控制器完整且导航目标非部分路径；150人全部移动并选择巡游目标，观察到体力消耗，保留设置及动画策略检查均通过。平均位移约29.81m，最小约2.80m。</x:v>
+        <x:v>原生输入09:37、滑条与播放暂停实测通过；包保持clean，恢复按钮还原原夜景且运行起始时间不变，passed=true。旧18:00禁灯测试是当时阶段，现按新黄昏规则。</x:v>
       </x:c>
       <x:c r="E71" s="7" t="str">
-        <x:v>完成该被动观察样本；不替代全校园逐路线、长期互相穿透和全体休息验证。</x:v>
+        <x:v>最新规则的预览恢复回归已并入CA-064.08。</x:v>
       </x:c>
       <x:c r="F71" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G71" s="7" t="str">
-        <x:v>150人运行QA与最终保存确认</x:v>
+        <x:v>面板实操及夜景恢复检查</x:v>
       </x:c>
       <x:c r="H71" s="16" t="str"/>
     </x:row>
-    <x:row r="72" ht="92" customHeight="1">
+    <x:row r="72" ht="75" customHeight="1">
       <x:c r="A72" s="7" t="str">
-        <x:v>CA-073.07</x:v>
+        <x:v>CA-068.02</x:v>
       </x:c>
       <x:c r="B72" s="7" t="str">
-        <x:v>天气昼夜屋顶与停雨运行检查</x:v>
+        <x:v>月亮轨道与两轮昼夜运行检查</x:v>
       </x:c>
       <x:c r="C72" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D72" s="7" t="str">
-        <x:v>正午阴天、正午降雨、夜间降雨、停雨4阶段运行errors为空、passed=true；停雨仍湿润后渐干，屋顶与室外304帧检查通过，材质重载无绑定错误。</x:v>
+        <x:v>796帧、18:45至第二轮正午等9时点运行验证passed、failures为空；月盘方向与月光一致，正午月亮隐藏及天空正常，重载passed。</x:v>
       </x:c>
       <x:c r="E72" s="7" t="str">
-        <x:v>屋顶边缘未全量检查；此项不等于发布包全路线实测。</x:v>
+        <x:v>按已记录两轮与时点范围验收，不扩大为发布包全路径实测。</x:v>
       </x:c>
       <x:c r="F72" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G72" s="7" t="str">
-        <x:v>天气运行和宽屋顶验证范围</x:v>
+        <x:v>月亮运行796帧与重载报告</x:v>
       </x:c>
       <x:c r="H72" s="16" t="str"/>
     </x:row>
     <x:row r="73" ht="75" customHeight="1">
       <x:c r="A73" s="7" t="str">
-        <x:v>CA-073.08</x:v>
+        <x:v>CA-070.04</x:v>
       </x:c>
       <x:c r="B73" s="7" t="str">
-        <x:v>晴雨调度及昼夜灯光自动化回归</x:v>
+        <x:v>教学楼材质合批镜像与门结构保持</x:v>
       </x:c>
       <x:c r="C73" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D73" s="7" t="str">
-        <x:v>10月8日最终27项通过、0失败、0警告、0未运行，新增晴天往返恢复与原版天空保持验证；此前20/24/26项结果保留阶段历史。</x:v>
+        <x:v>真实材质后1350自动批次、10307实例和18手工ISM保持，2084网格检查无问题；纯色门后几何与门父关系保持，918组件passed。</x:v>
       </x:c>
       <x:c r="E73" s="7" t="str">
-        <x:v>最终报告为编辑器自动化；不等于实际连续运行30分钟或10月9日新材质后的全场回归。</x:v>
+        <x:v>只覆盖记录的位置缩放、引用、数量、三角和包围盒；未逐实例比较变换或顶点索引。不能替代全校交互回归CA-010。</x:v>
       </x:c>
       <x:c r="F73" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G73" s="7" t="str">
-        <x:v>ClearWeatherFix最终Automation27通过0失败</x:v>
+        <x:v>真实材质与纯色门结构验证</x:v>
       </x:c>
       <x:c r="H73" s="16" t="str"/>
     </x:row>
     <x:row r="74" ht="92" customHeight="1">
       <x:c r="A74" s="7" t="str">
-        <x:v>CA-073.09</x:v>
+        <x:v>CA-071.05</x:v>
       </x:c>
       <x:c r="B74" s="7" t="str">
-        <x:v>天气按钮点击与完整渐变播放</x:v>
+        <x:v>草地全量朝向坐标材质及保存检查</x:v>
       </x:c>
       <x:c r="C74" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D74" s="7" t="str">
-        <x:v>实际点击后的雨量、云层、湿度连续变化，最终点击报告passed=true，保存时长30秒，观测约38.2秒至过渡完成；详情切换反向、恢复及重启预览检查errors为空。</x:v>
+        <x:v>424175实例全量直立yaw检查通过；最大抽样世界位置误差约1.1e-13cm，3LOD单材质、颜色和WPO、关闭碰撞导航阴影均验证，scene saved=true。</x:v>
       </x:c>
       <x:c r="E74" s="7" t="str">
-        <x:v>编辑器预览已验；Shipping按钮适用范围与成品运行另按版本判断。</x:v>
+        <x:v>验收覆盖实例数据与近景范围，不扩大为全校园真实角色路线或帧率验收。</x:v>
       </x:c>
       <x:c r="F74" s="14" t="d">
         <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G74" s="7" t="str">
-        <x:v>按钮点击、反向及最终预览状态</x:v>
+        <x:v>草地全量检查和67秒保存回执</x:v>
       </x:c>
       <x:c r="H74" s="16" t="str"/>
     </x:row>
-    <x:row r="75" ht="75" customHeight="1">
+    <x:row r="75" ht="92" customHeight="1">
       <x:c r="A75" s="7" t="str">
-        <x:v>CA-074.05</x:v>
+        <x:v>CA-072.04</x:v>
       </x:c>
       <x:c r="B75" s="7" t="str">
-        <x:v>254个开关墙面定位与操作站位</x:v>
+        <x:v>150名White运行移动与行为保留</x:v>
       </x:c>
       <x:c r="C75" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D75" s="7" t="str">
-        <x:v>最终交付确认安装位置、遮挡检查完成。全部254个真实E键测试从已校验站位执行，玩家胶囊保持碰撞，面板对准与原生提示焦点有效。</x:v>
+        <x:v>运行全程150名White、控制器完整且导航目标非部分路径；150人全部移动并选择巡游目标，观察到体力消耗，保留设置及动画策略检查均通过。平均位移约29.81m，最小约2.80m。</x:v>
       </x:c>
       <x:c r="E75" s="7" t="str">
-        <x:v>未把传送到站位测试扩大为全楼逐路线实走。</x:v>
+        <x:v>完成该被动观察样本；不替代全校园逐路线、长期互相穿透和全体休息验证。</x:v>
       </x:c>
       <x:c r="F75" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G75" s="7" t="str">
-        <x:v>最终交付、站位与焦点逐项结果</x:v>
+        <x:v>150人运行QA与最终保存确认</x:v>
       </x:c>
       <x:c r="H75" s="16" t="str"/>
     </x:row>
     <x:row r="76" ht="92" customHeight="1">
       <x:c r="A76" s="7" t="str">
-        <x:v>CA-074.06</x:v>
+        <x:v>CA-073.07</x:v>
       </x:c>
       <x:c r="B76" s="7" t="str">
-        <x:v>全部墙壁开关508次E键交互</x:v>
+        <x:v>天气昼夜屋顶与停雨运行检查</x:v>
       </x:c>
       <x:c r="C76" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D76" s="7" t="str">
-        <x:v>254个开关各切换并恢复一次，508次真实E输入全部通过；联动面板状态一致，无无关回路或门状态变化。为隔离NPC自动开门，150名学生的巡游临时关闭，验证后恢复。</x:v>
+        <x:v>正午阴天、正午降雨、夜间降雨、停雨4阶段运行errors为空、passed=true；停雨仍湿润后渐干，屋顶与室外304帧检查通过，材质重载无绑定错误。</x:v>
       </x:c>
       <x:c r="E76" s="7" t="str">
-        <x:v>这是输入与回路验收；不扩大为150人正常巡游时全流程回归或Shipping实测。</x:v>
+        <x:v>屋顶边缘未全量检查；此项不等于发布包全路线实测。</x:v>
       </x:c>
       <x:c r="F76" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G76" s="7" t="str">
-        <x:v>runtime_input passed=true、254项与508次最终确认</x:v>
+        <x:v>天气运行和宽屋顶验证范围</x:v>
       </x:c>
       <x:c r="H76" s="16" t="str"/>
     </x:row>
     <x:row r="77" ht="75" customHeight="1">
       <x:c r="A77" s="7" t="str">
-        <x:v>CA-074.07</x:v>
+        <x:v>CA-073.08</x:v>
       </x:c>
       <x:c r="B77" s="7" t="str">
-        <x:v>开关隔墙远距与门输入隔离抽查</x:v>
+        <x:v>晴雨调度及昼夜灯光自动化回归</x:v>
       </x:c>
       <x:c r="C77" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D77" s="7" t="str">
-        <x:v>behind_wall、too_far、look_away三类拒绝操作，以及A_Room_101/B_Room_403临近门正常打开共5个案例通过，errors为空。</x:v>
+        <x:v>10月8日最终27项通过、0失败、0警告、0未运行，新增晴天往返恢复与原版天空保持验证；此前20/24/26项结果保留阶段历史。</x:v>
       </x:c>
       <x:c r="E77" s="7" t="str">
-        <x:v>该项仅记录5个抽查案例，全校门回归仍见CA-010。</x:v>
+        <x:v>最终报告为编辑器自动化；不等于实际连续运行30分钟或10月9日新材质后的全场回归。</x:v>
       </x:c>
       <x:c r="F77" s="14" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G77" s="7" t="str">
-        <x:v>runtime_access全部5例passed=true</x:v>
+        <x:v>ClearWeatherFix最终Automation27通过0失败</x:v>
       </x:c>
       <x:c r="H77" s="16" t="str"/>
     </x:row>
     <x:row r="78" ht="92" customHeight="1">
       <x:c r="A78" s="7" t="str">
-        <x:v>CA-075.05</x:v>
+        <x:v>CA-073.09</x:v>
       </x:c>
       <x:c r="B78" s="7" t="str">
-        <x:v>动态云层间隔截图运动验证</x:v>
+        <x:v>天气按钮点击与完整渐变播放</x:v>
       </x:c>
       <x:c r="C78" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D78" s="7" t="str">
-        <x:v>相同机位间隔31.54秒的两帧，云层区域抑制雨线后RGB平均变化约5.35/5.35/5.47，cloud_motion_visible=true，最终聊天确认可见运动。</x:v>
+        <x:v>实际点击后的雨量、云层、湿度连续变化，最终点击报告passed=true，保存时长30秒，观测约38.2秒至过渡完成；详情切换反向、恢复及重启预览检查errors为空。</x:v>
       </x:c>
       <x:c r="E78" s="7" t="str">
-        <x:v>仅确认该样本中云层运动，不等于长时天气或性能验收。</x:v>
+        <x:v>编辑器预览已验；Shipping按钮适用范围与成品运行另按版本判断。</x:v>
       </x:c>
       <x:c r="F78" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G78" s="7" t="str">
-        <x:v>motion_verification与最终两帧检查</x:v>
+        <x:v>按钮点击、反向及最终预览状态</x:v>
       </x:c>
       <x:c r="H78" s="16" t="str"/>
     </x:row>
     <x:row r="79" ht="75" customHeight="1">
       <x:c r="A79" s="7" t="str">
-        <x:v>CA-075.08</x:v>
+        <x:v>CA-074.05</x:v>
       </x:c>
       <x:c r="B79" s="7" t="str">
-        <x:v>白昼夜晚晴雨四组合恢复验证</x:v>
+        <x:v>254个开关墙面定位与操作站位</x:v>
       </x:c>
       <x:c r="C79" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D79" s="7" t="str">
-        <x:v>12:00/22:00分别验证下雨与晴天，四组合检查通过，晴时覆盖参数归零且雨后湿地继续渐干；最终面板显示晴天并停在22:00。</x:v>
+        <x:v>最终交付确认安装位置、遮挡检查完成。全部254个真实E键测试从已校验站位执行，玩家胶囊保持碰撞，面板对准与原生提示焦点有效。</x:v>
       </x:c>
       <x:c r="E79" s="7" t="str">
-        <x:v>27项自动化另见CA-073.08；此项为四组合场景预览，不能替代发布包实测。</x:v>
+        <x:v>未把传送到站位测试扩大为全楼逐路线实走。</x:v>
       </x:c>
       <x:c r="F79" s="14" t="d">
         <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G79" s="7" t="str">
-        <x:v>scene_verification四组合与最终面板确认</x:v>
+        <x:v>最终交付、站位与焦点逐项结果</x:v>
       </x:c>
       <x:c r="H79" s="16" t="str"/>
     </x:row>
     <x:row r="80" ht="92" customHeight="1">
       <x:c r="A80" s="7" t="str">
-        <x:v>CA-076.09</x:v>
+        <x:v>CA-074.06</x:v>
       </x:c>
       <x:c r="B80" s="7" t="str">
-        <x:v>食堂新材质保存与实例表现同步</x:v>
+        <x:v>灯光修复后真实E输入与明暗回归</x:v>
       </x:c>
       <x:c r="C80" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D80" s="7" t="str">
-        <x:v>主关卡保存确认；9052兼容实例组/102611实例在内存校验通过，77旧批次退出，810处新材质作为独立可见物体保留。最终保存校验已含补植后的结果，替代中途806处。</x:v>
+        <x:v>10月8日508次状态输入保留历史。用户随后看到提示但无照明变化；10月9日补灯后15个代表点30次E输入、30次实体灯和发光边沿全部通过，另有16次视口E按键及五栋楼明暗截图。</x:v>
       </x:c>
       <x:c r="E80" s="7" t="str">
-        <x:v>验证是保存和运行时表现预览，不是独立游戏或Shipping运行；临时预览恢复信息已保留。</x:v>
+        <x:v>全161回路状态检查另见CA-074.09；不将15代表点外推为当前全部254面板再次逐项按键。教室合并后的局部回归另见CA-079、CA-080。</x:v>
       </x:c>
       <x:c r="F80" s="14" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G80" s="7" t="str">
+        <x:v>直接用户纠正与新completion的15案例30按键</x:v>
+      </x:c>
+      <x:c r="H80" s="16" t="str"/>
+    </x:row>
+    <x:row r="81" ht="75" customHeight="1">
+      <x:c r="A81" s="7" t="str">
+        <x:v>CA-074.07</x:v>
+      </x:c>
+      <x:c r="B81" s="7" t="str">
+        <x:v>开关隔墙远距与门输入隔离抽查</x:v>
+      </x:c>
+      <x:c r="C81" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D81" s="7" t="str">
+        <x:v>behind_wall、too_far、look_away三类拒绝操作，以及A_Room_101/B_Room_403临近门正常打开共5个案例通过，errors为空。</x:v>
+      </x:c>
+      <x:c r="E81" s="7" t="str">
+        <x:v>该项仅记录5个抽查案例，全校门回归仍见CA-010。</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G81" s="7" t="str">
+        <x:v>runtime_access全部5例passed=true</x:v>
+      </x:c>
+      <x:c r="H81" s="16" t="str"/>
+    </x:row>
+    <x:row r="82" ht="75" customHeight="1">
+      <x:c r="A82" s="7" t="str">
+        <x:v>CA-074.09</x:v>
+      </x:c>
+      <x:c r="B82" s="7" t="str">
+        <x:v>补灯后161回路开关与重载检查</x:v>
+      </x:c>
+      <x:c r="C82" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D82" s="7" t="str">
+        <x:v>161回路逐项验证至少有真实灯光、初始关闭及开关状态一致；重载1195灯均初始不可见且保存原亮度。3个原生测试通过。</x:v>
+      </x:c>
+      <x:c r="E82" s="7" t="str">
+        <x:v>逐回路程序验证与真实E输入是不同验收；不视作150人巡游或Shipping整体回归。</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G82" s="7" t="str">
+        <x:v>runtime_circuits passed及reload_verified</x:v>
+      </x:c>
+      <x:c r="H82" s="16" t="str"/>
+    </x:row>
+    <x:row r="83" ht="92" customHeight="1">
+      <x:c r="A83" s="7" t="str">
+        <x:v>CA-075.05</x:v>
+      </x:c>
+      <x:c r="B83" s="7" t="str">
+        <x:v>动态云层间隔截图运动验证</x:v>
+      </x:c>
+      <x:c r="C83" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D83" s="7" t="str">
+        <x:v>相同机位间隔31.54秒的两帧，云层区域抑制雨线后RGB平均变化约5.35/5.35/5.47，cloud_motion_visible=true，最终聊天确认可见运动。</x:v>
+      </x:c>
+      <x:c r="E83" s="7" t="str">
+        <x:v>仅确认该样本中云层运动，不等于长时天气或性能验收。</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G83" s="7" t="str">
+        <x:v>motion_verification与最终两帧检查</x:v>
+      </x:c>
+      <x:c r="H83" s="16" t="str"/>
+    </x:row>
+    <x:row r="84" ht="75" customHeight="1">
+      <x:c r="A84" s="7" t="str">
+        <x:v>CA-075.08</x:v>
+      </x:c>
+      <x:c r="B84" s="7" t="str">
+        <x:v>白昼夜晚晴雨四组合恢复验证</x:v>
+      </x:c>
+      <x:c r="C84" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D84" s="7" t="str">
+        <x:v>12:00/22:00分别验证下雨与晴天，四组合检查通过，晴时覆盖参数归零且雨后湿地继续渐干；最终面板显示晴天并停在22:00。</x:v>
+      </x:c>
+      <x:c r="E84" s="7" t="str">
+        <x:v>27项自动化另见CA-073.08；此项为四组合场景预览，不能替代发布包实测。</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G84" s="7" t="str">
+        <x:v>scene_verification四组合与最终面板确认</x:v>
+      </x:c>
+      <x:c r="H84" s="16" t="str"/>
+    </x:row>
+    <x:row r="85" ht="92" customHeight="1">
+      <x:c r="A85" s="7" t="str">
+        <x:v>CA-076.09</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="str">
+        <x:v>食堂新材质保存与实例表现同步</x:v>
+      </x:c>
+      <x:c r="C85" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D85" s="7" t="str">
+        <x:v>主关卡保存确认；9052兼容实例组/102611实例在内存校验通过，77旧批次退出，810处新材质作为独立可见物体保留。最终保存校验已含补植后的结果，替代中途806处。</x:v>
+      </x:c>
+      <x:c r="E85" s="7" t="str">
+        <x:v>验证是保存和运行时表现预览，不是独立游戏或Shipping运行；临时预览恢复信息已保留。</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G85" s="7" t="str">
         <x:v>saved=true、810绑定与verified_in_memory</x:v>
       </x:c>
-      <x:c r="H80" s="16" t="str"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="1"/>
-      <x:c r="B81" s="1"/>
-      <x:c r="C81" s="1"/>
-      <x:c r="D81" s="1"/>
-      <x:c r="E81" s="1"/>
-      <x:c r="F81" s="1"/>
-      <x:c r="G81" s="1"/>
-      <x:c r="H81" s="1"/>
-    </x:row>
-    <x:row r="82" ht="34" customHeight="1">
-      <x:c r="A82" s="3" t="str">
+      <x:c r="H85" s="16" t="str"/>
+    </x:row>
+    <x:row r="86" ht="92" customHeight="1">
+      <x:c r="A86" s="7" t="str">
+        <x:v>CA-078.03</x:v>
+      </x:c>
+      <x:c r="B86" s="7" t="str">
+        <x:v>新铺装雨停残留水渍到完全干燥</x:v>
+      </x:c>
+      <x:c r="C86" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D86" s="7" t="str">
+        <x:v>自然推进序列通过：湿度0→1，停雨雨量0而湿度0.83249→0.33249→0；90秒干燥设置保持。缝修正后最终雨停湿度0.86284继续归零，控制器恢复正常启用。</x:v>
+      </x:c>
+      <x:c r="E86" s="7" t="str">
+        <x:v>后两张机位变化，未作逐像素A/B；该天气过程已验证，夜景与昼夜往返仍分别判断。</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G86" s="7" t="str">
+        <x:v>weather_qa passed及final_weather_preview</x:v>
+      </x:c>
+      <x:c r="H86" s="16" t="str"/>
+    </x:row>
+    <x:row r="87" ht="92" customHeight="1">
+      <x:c r="A87" s="7" t="str">
+        <x:v>CA-078.05</x:v>
+      </x:c>
+      <x:c r="B87" s="7" t="str">
+        <x:v>全场新铺装保存绑定与实例同步</x:v>
+      </x:c>
+      <x:c r="C87" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D87" s="7" t="str">
+        <x:v>最终正常保存1036绑定与71默认槽验证，目标旧材质0，8961兼容实例组/101786实例通过内存校验，旧生成批次残留0，无关5910槽保留。</x:v>
+      </x:c>
+      <x:c r="E87" s="7" t="str">
+        <x:v>保存及同步是阶段验收；不视作最新教室改造后全校运行或Shipping实测。</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G87" s="7" t="str">
+        <x:v>saved与verified_in_memory</x:v>
+      </x:c>
+      <x:c r="H87" s="16" t="str"/>
+    </x:row>
+    <x:row r="88" ht="75" customHeight="1">
+      <x:c r="A88" s="7" t="str">
+        <x:v>CA-079.05</x:v>
+      </x:c>
+      <x:c r="B88" s="7" t="str">
+        <x:v>合并教室拆墙通行与48门洞封补碰撞</x:v>
+      </x:c>
+      <x:c r="C88" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D88" s="7" t="str">
+        <x:v>重开后实际运行检查：24间原隔墙位置角色可通行，48处封补门洞碰撞正常，保留48扇门开合通过。</x:v>
+      </x:c>
+      <x:c r="E88" s="7" t="str">
+        <x:v>只覆盖合并的24教室；全校连续门路线仍见CA-010。后续室内新家具碰撞见CA-080.08。</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G88" s="7" t="str">
+        <x:v>合并runtime与重开后最终确认</x:v>
+      </x:c>
+      <x:c r="H88" s="16" t="str"/>
+    </x:row>
+    <x:row r="89" ht="92" customHeight="1">
+      <x:c r="A89" s="7" t="str">
+        <x:v>CA-079.06</x:v>
+      </x:c>
+      <x:c r="B89" s="7" t="str">
+        <x:v>教室合并持久化与旧实例批次退出</x:v>
+      </x:c>
+      <x:c r="C89" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D89" s="7" t="str">
+        <x:v>scene保存重开验证合并布局不回退。8741兼容实例组/99352实例校验，243新组、8498复用，463旧批次退出；新封补构件保留独立完整碰撞。</x:v>
+      </x:c>
+      <x:c r="E89" s="7" t="str">
+        <x:v>该同步包含实际资产变化，164.49秒不能与无变化同步直接比较优化倍率。</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G89" s="7" t="str">
+        <x:v>reload_verified与ism_sync verified_in_memory</x:v>
+      </x:c>
+      <x:c r="H89" s="16" t="str"/>
+    </x:row>
+    <x:row r="90" ht="75" customHeight="1">
+      <x:c r="A90" s="7" t="str">
+        <x:v>CA-080.07</x:v>
+      </x:c>
+      <x:c r="B90" s="7" t="str">
+        <x:v>室内新实例坐标持久化与保存</x:v>
+      </x:c>
+      <x:c r="C90" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D90" s="7" t="str">
+        <x:v>456自定义实例组件、2808实例及24教室设施位置核对，场景和共享资产保存，重开456组位置层级正确，编辑器同步钩子恢复。</x:v>
+      </x:c>
+      <x:c r="E90" s="7" t="str">
+        <x:v>全局8427组/95713实例同步有161.12秒记录，但包含32新组、346旧组退出，不作为无变化优化。</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G90" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H90" s="16" t="str"/>
+    </x:row>
+    <x:row r="91" ht="75" customHeight="1">
+      <x:c r="A91" s="7" t="str">
+        <x:v>CA-080.08</x:v>
+      </x:c>
+      <x:c r="B91" s="7" t="str">
+        <x:v>新教室家具碰撞主通道与48门开合</x:v>
+      </x:c>
+      <x:c r="C91" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D91" s="7" t="str">
+        <x:v>最新24教室桌椅简化碰撞与两条主通道检查通过，48门请求开合均通过，运行结果passed=true；最终记录确认门与家具测试完成。</x:v>
+      </x:c>
+      <x:c r="E91" s="7" t="str">
+        <x:v>教室局部验收不代替全校逐路线实走，范围仍见CA-010和CA-010.02。</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G91" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H91" s="16" t="str"/>
+    </x:row>
+    <x:row r="92" ht="75" customHeight="1">
+      <x:c r="A92" s="7" t="str">
+        <x:v>CA-080.09</x:v>
+      </x:c>
+      <x:c r="B92" s="7" t="str">
+        <x:v>新教室24回路昼夜开关48案例</x:v>
+      </x:c>
+      <x:c r="C92" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D92" s="7" t="str">
+        <x:v>24教室各在白天和夜晚进行关、开、恢复共48案例，432现有灯主从同步与强度比例检查passed=true，未增加灯数。</x:v>
+      </x:c>
+      <x:c r="E92" s="7" t="str">
+        <x:v>本项为教室局部昼夜开关；不外推雨天、全部五栋楼或Shipping实测。</x:v>
+      </x:c>
+      <x:c r="F92" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G92" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H92" s="16" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="1"/>
+      <x:c r="B93" s="1"/>
+      <x:c r="C93" s="1"/>
+      <x:c r="D93" s="1"/>
+      <x:c r="E93" s="1"/>
+      <x:c r="F93" s="1"/>
+      <x:c r="G93" s="1"/>
+      <x:c r="H93" s="1"/>
+    </x:row>
+    <x:row r="94" ht="34" customHeight="1">
+      <x:c r="A94" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B82" s="21" t="str">
+      <x:c r="B94" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C82" s="21"/>
-      <x:c r="D82" s="21"/>
-      <x:c r="E82" s="21"/>
-      <x:c r="F82" s="21"/>
-      <x:c r="G82" s="21"/>
-      <x:c r="H82" s="21"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="1"/>
-      <x:c r="B83" s="1"/>
-      <x:c r="C83" s="1"/>
-      <x:c r="D83" s="1"/>
-      <x:c r="E83" s="1"/>
-      <x:c r="F83" s="1"/>
-      <x:c r="G83" s="1"/>
-      <x:c r="H83" s="1"/>
+      <x:c r="C94" s="21"/>
+      <x:c r="D94" s="21"/>
+      <x:c r="E94" s="21"/>
+      <x:c r="F94" s="21"/>
+      <x:c r="G94" s="21"/>
+      <x:c r="H94" s="21"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="1"/>
+      <x:c r="B95" s="1"/>
+      <x:c r="C95" s="1"/>
+      <x:c r="D95" s="1"/>
+      <x:c r="E95" s="1"/>
+      <x:c r="F95" s="1"/>
+      <x:c r="G95" s="1"/>
+      <x:c r="H95" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B82:H82"/>
+    <x:mergeCell ref="B94:H94"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C80">
+  <x:conditionalFormatting sqref="C8:C92">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -2330,13 +2618,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C80">
+    <x:dataValidation type="list" sqref="C8:C92">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc475a950337c46e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145858bf9aad401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>